--- a/config/brand_info_config.xlsx
+++ b/config/brand_info_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wushan/models/SLBR-Visible-Watermark-Removal/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1611279C-788D-F74E-8B74-E29E97C6D2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D04367-F642-2648-A5F4-A599F411A409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{1B5E55EE-582A-EF4F-97A0-18A8C46CF48F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1942" uniqueCount="1645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1943" uniqueCount="1646">
   <si>
     <t>Steel City Enterprises, Inc.</t>
   </si>
@@ -76869,6 +76869,9 @@
   </si>
   <si>
     <t>https://amybrownart.com/</t>
+  </si>
+  <si>
+    <t>https://www.nbcuniversal.com/</t>
   </si>
 </sst>
 </file>
@@ -87175,7 +87178,9 @@
       </c>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
-      <c r="D843" s="1"/>
+      <c r="D843" s="1" t="s">
+        <v>1645</v>
+      </c>
       <c r="E843" t="s">
         <v>1635</v>
       </c>

--- a/config/brand_info_config.xlsx
+++ b/config/brand_info_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wushan/models/SLBR-Visible-Watermark-Removal/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D04367-F642-2648-A5F4-A599F411A409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96C8A94-779B-7745-B6FD-A21FEAF0BA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{1B5E55EE-582A-EF4F-97A0-18A8C46CF48F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1943" uniqueCount="1646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="1649">
   <si>
     <t>Steel City Enterprises, Inc.</t>
   </si>
@@ -76873,12 +76873,23 @@
   <si>
     <t>https://www.nbcuniversal.com/</t>
   </si>
+  <si>
+    <t>Andrew Dobell</t>
+  </si>
+  <si>
+    <t>https://www.andrewdobellauthor.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>品牌简介: Andrew Dobell是一名有超过20年经验的数字艺术家与内容创作者，擅长通过图像合成技术将自然主义与幻想元素结合，创造出兼具现实感与电影质感的视觉作品。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -76994,6 +77005,12 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FF171717"/>
+      <name val="Geist"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -77020,7 +77037,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -77052,6 +77069,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -87185,11 +87208,18 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="844" spans="1:5">
-      <c r="A844" s="1"/>
+    <row r="844" spans="1:5" ht="34">
+      <c r="A844" s="11" t="s">
+        <v>1646</v>
+      </c>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
-      <c r="D844" s="1"/>
+      <c r="D844" s="7" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E844" s="12" t="s">
+        <v>1648</v>
+      </c>
     </row>
     <row r="845" spans="1:5">
       <c r="A845" s="1"/>
@@ -91161,6 +91191,7 @@
     <hyperlink ref="E827" r:id="rId77" display="http://www.sega.com/" xr:uid="{081EDCD5-1F94-CC41-A4EC-612AF63A4822}"/>
     <hyperlink ref="A842" r:id="rId78" display="http://saibeiip.com/" xr:uid="{2E496384-8EB3-8247-8179-79F45DF84CA6}"/>
     <hyperlink ref="E842" r:id="rId79" display="http://saibeiip.com/" xr:uid="{062BB250-86D1-5C4B-87AC-FDDF63E776C3}"/>
+    <hyperlink ref="D844" r:id="rId80" xr:uid="{960EBD0F-E7EB-3946-8641-5C2574B22DD0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/config/brand_info_config.xlsx
+++ b/config/brand_info_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wushan/models/SLBR-Visible-Watermark-Removal/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96C8A94-779B-7745-B6FD-A21FEAF0BA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B83B2E-CF35-A645-BF30-4475CABD8562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{1B5E55EE-582A-EF4F-97A0-18A8C46CF48F}"/>
   </bookViews>
@@ -77415,7 +77415,7 @@
   <dimension ref="A1:E1492"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" customWidth="1"/>
+    <col min="1" max="1" width="73.83203125" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.5" customWidth="1"/>

--- a/config/brand_info_config.xlsx
+++ b/config/brand_info_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wushan/models/SLBR-Visible-Watermark-Removal/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0537B8-EB2F-A949-ABA5-64F10F31800D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405AED8C-CCED-064A-8B3F-395C4042C55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{1B5E55EE-582A-EF4F-97A0-18A8C46CF48F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1954" uniqueCount="1655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="1659">
   <si>
     <t>Steel City Enterprises, Inc.</t>
   </si>
@@ -21190,21 +21190,6 @@
     <t>https://fineartbydaniel.com</t>
   </si>
   <si>
-    <r>
-      <t>Daniel John Watts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，是一位兼具多重身份的独立创作者，同时担任艺术家、插画师、平面设计师、作家及摄影师。</t>
-    </r>
-  </si>
-  <si>
     <t>https://www.dansungallery.com</t>
   </si>
   <si>
@@ -32273,21 +32258,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Gold’s Gym </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>是世界上最著名的健身俱乐部之一，以其专业的健身设备、丰富的健身课程和高质量的服务而闻名。</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Goorin Bros. Inc. </t>
     </r>
     <r>
@@ -76999,6 +76969,81 @@
         <charset val="134"/>
       </rPr>
       <t>系列被广泛商业应用，近期因其发起的版权维权而备受关注。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tiagomachado.com/</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gold’s Gym </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是世界上最著名的健身俱乐部之一，以其专业的健身设备、丰富的健身课程和高质量的服务而闻名。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.goldsgym.com/</t>
+  </si>
+  <si>
+    <t>http://maniecka-gawel.de/</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Daniel John Watts </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是美国百老汇演员及托尼奖提名者，以在《蒂娜》中饰演艾克</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>特纳而闻名。他毕业于埃隆大学，出演过《汉密尔顿》及影视剧《企鹅人》。同时，他也是一位致力于诗歌与音乐创作的口语艺术家</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color theme="10"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://wattswords.com </t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -77553,16 +77598,16 @@
         <v>868</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -77570,10 +77615,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="5" t="s">
@@ -77588,12 +77633,12 @@
       <c r="C3" s="2"/>
       <c r="D3" s="4"/>
       <c r="E3" s="10" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -77698,7 +77743,7 @@
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
@@ -77711,7 +77756,7 @@
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="5" t="s">
@@ -77726,7 +77771,7 @@
       <c r="C15" s="2"/>
       <c r="D15" s="4"/>
       <c r="E15" s="5" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="51">
@@ -77735,11 +77780,11 @@
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="9" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="10" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -77781,7 +77826,7 @@
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
@@ -77790,7 +77835,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -77805,7 +77850,7 @@
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4" t="s">
@@ -77818,7 +77863,7 @@
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="5" t="s">
@@ -77831,7 +77876,7 @@
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4" t="s">
@@ -77855,7 +77900,7 @@
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="9" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="5" t="s">
@@ -77868,7 +77913,7 @@
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="5" t="s">
@@ -77912,10 +77957,10 @@
         <v>618</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="5" t="s">
@@ -77928,10 +77973,10 @@
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>895</v>
@@ -77965,7 +78010,7 @@
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4" t="s">
@@ -77978,7 +78023,7 @@
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4" t="s">
@@ -77991,7 +78036,7 @@
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4" t="s">
@@ -78015,7 +78060,7 @@
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4" t="s">
@@ -78028,7 +78073,7 @@
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4" t="s">
@@ -78041,7 +78086,7 @@
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="5" t="s">
@@ -78076,7 +78121,7 @@
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="4" t="s">
@@ -78089,7 +78134,7 @@
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4" t="s">
@@ -78113,7 +78158,7 @@
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="5" t="s">
@@ -78170,7 +78215,7 @@
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4" t="s">
@@ -78273,7 +78318,7 @@
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4" t="s">
@@ -78308,7 +78353,7 @@
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="5" t="s">
@@ -78376,7 +78421,7 @@
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4" t="s">
@@ -78411,7 +78456,7 @@
       </c>
       <c r="B73" s="2"/>
       <c r="C73" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="5" t="s">
@@ -78424,7 +78469,7 @@
       </c>
       <c r="B74" s="2"/>
       <c r="C74" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="5" t="s">
@@ -78448,7 +78493,7 @@
       </c>
       <c r="B76" s="2"/>
       <c r="C76" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D76" s="7" t="s">
         <v>931</v>
@@ -78496,7 +78541,7 @@
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D80" s="4"/>
       <c r="E80" s="4" t="s">
@@ -78597,7 +78642,7 @@
       </c>
       <c r="B89" s="2"/>
       <c r="C89" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>943</v>
@@ -78612,7 +78657,7 @@
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="4" t="s">
@@ -78658,7 +78703,7 @@
       </c>
       <c r="B94" s="2"/>
       <c r="C94" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="5" t="s">
@@ -78682,7 +78727,7 @@
       </c>
       <c r="B96" s="2"/>
       <c r="C96" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="4" t="s">
@@ -78695,7 +78740,7 @@
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D97" s="4"/>
       <c r="E97" s="4" t="s">
@@ -78818,7 +78863,7 @@
       </c>
       <c r="B108" s="2"/>
       <c r="C108" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D108" s="4"/>
       <c r="E108" s="4" t="s">
@@ -78831,7 +78876,7 @@
       </c>
       <c r="B109" s="2"/>
       <c r="C109" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D109" s="4"/>
       <c r="E109" s="4" t="s">
@@ -78877,7 +78922,7 @@
       </c>
       <c r="B113" s="2"/>
       <c r="C113" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D113" s="4"/>
       <c r="E113" s="5" t="s">
@@ -78969,7 +79014,7 @@
       </c>
       <c r="B121" s="2"/>
       <c r="C121" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D121" s="4"/>
       <c r="E121" s="4" t="s">
@@ -79092,7 +79137,7 @@
       </c>
       <c r="B132" s="2"/>
       <c r="C132" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D132" s="7" t="s">
         <v>980</v>
@@ -79195,7 +79240,7 @@
       </c>
       <c r="B141" s="2"/>
       <c r="C141" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D141" s="4"/>
       <c r="E141" s="4" t="s">
@@ -79219,7 +79264,7 @@
       </c>
       <c r="B143" s="2"/>
       <c r="C143" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D143" s="4"/>
       <c r="E143" s="4" t="s">
@@ -79276,7 +79321,7 @@
       </c>
       <c r="B148" s="2"/>
       <c r="C148" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D148" s="4"/>
       <c r="E148" s="4" t="s">
@@ -79318,7 +79363,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -79344,7 +79389,7 @@
       </c>
       <c r="B154" s="2"/>
       <c r="C154" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D154" s="4"/>
       <c r="E154" s="4" t="s">
@@ -79401,7 +79446,7 @@
       </c>
       <c r="B159" s="2"/>
       <c r="C159" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D159" s="4"/>
       <c r="E159" s="4" t="s">
@@ -79443,7 +79488,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -79610,11 +79655,13 @@
       </c>
       <c r="B178" s="2"/>
       <c r="C178" s="9" t="s">
-        <v>1614</v>
-      </c>
-      <c r="D178" s="3"/>
+        <v>1612</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>1658</v>
+      </c>
       <c r="E178" s="4" t="s">
-        <v>1021</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -79623,13 +79670,13 @@
       </c>
       <c r="B179" s="2"/>
       <c r="C179" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D179" s="7" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E179" s="7" t="s">
         <v>1022</v>
-      </c>
-      <c r="E179" s="7" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -79638,11 +79685,11 @@
       </c>
       <c r="B180" s="2"/>
       <c r="C180" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D180" s="4"/>
       <c r="E180" s="4" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -79651,11 +79698,11 @@
       </c>
       <c r="B181" s="2"/>
       <c r="C181" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D181" s="4"/>
       <c r="E181" s="5" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -79664,13 +79711,13 @@
       </c>
       <c r="B182" s="2"/>
       <c r="C182" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D182" s="7" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E182" s="7" t="s">
         <v>1026</v>
-      </c>
-      <c r="E182" s="7" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -79679,11 +79726,11 @@
       </c>
       <c r="B183" s="2"/>
       <c r="C183" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D183" s="4"/>
       <c r="E183" s="4" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -79692,11 +79739,11 @@
       </c>
       <c r="B184" s="2"/>
       <c r="C184" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D184" s="4"/>
       <c r="E184" s="4" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -79707,7 +79754,7 @@
       <c r="C185" s="2"/>
       <c r="D185" s="4"/>
       <c r="E185" s="4" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -79729,7 +79776,7 @@
       <c r="C187" s="2"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -79740,7 +79787,7 @@
       <c r="C188" s="2"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -79749,11 +79796,11 @@
       </c>
       <c r="B189" s="2"/>
       <c r="C189" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D189" s="4"/>
       <c r="E189" s="4" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -79764,7 +79811,7 @@
       <c r="C190" s="2"/>
       <c r="D190" s="4"/>
       <c r="E190" s="5" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -79773,7 +79820,7 @@
       </c>
       <c r="B191" s="2"/>
       <c r="C191" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D191" s="4"/>
       <c r="E191" s="5" t="s">
@@ -79788,7 +79835,7 @@
       <c r="C192" s="2"/>
       <c r="D192" s="4"/>
       <c r="E192" s="4" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -79798,23 +79845,23 @@
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
       <c r="D193" s="7" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E193" s="7" t="s">
         <v>1036</v>
-      </c>
-      <c r="E193" s="7" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B194" s="2"/>
       <c r="C194" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D194" s="4"/>
       <c r="E194" s="4" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -79823,7 +79870,7 @@
       </c>
       <c r="B195" s="2"/>
       <c r="C195" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D195" s="4"/>
       <c r="E195" s="5" t="s">
@@ -79832,13 +79879,13 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
       <c r="D196" s="4"/>
       <c r="E196" s="4" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -79849,7 +79896,7 @@
       <c r="C197" s="2"/>
       <c r="D197" s="4"/>
       <c r="E197" s="4" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -79858,11 +79905,11 @@
       </c>
       <c r="B198" s="2"/>
       <c r="C198" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D198" s="4"/>
       <c r="E198" s="4" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -79871,11 +79918,11 @@
       </c>
       <c r="B199" s="2"/>
       <c r="C199" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D199" s="4"/>
       <c r="E199" s="4" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -79886,7 +79933,7 @@
       <c r="C200" s="2"/>
       <c r="D200" s="3"/>
       <c r="E200" s="4" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -79908,7 +79955,7 @@
       <c r="C202" s="2"/>
       <c r="D202" s="4"/>
       <c r="E202" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -79919,7 +79966,7 @@
       <c r="C203" s="2"/>
       <c r="D203" s="4"/>
       <c r="E203" s="5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -79941,7 +79988,7 @@
       <c r="C205" s="2"/>
       <c r="D205" s="4"/>
       <c r="E205" s="4" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -79952,7 +79999,7 @@
       <c r="C206" s="2"/>
       <c r="D206" s="4"/>
       <c r="E206" s="4" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -79963,7 +80010,7 @@
       <c r="C207" s="2"/>
       <c r="D207" s="4"/>
       <c r="E207" s="4" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -79974,7 +80021,7 @@
       <c r="C208" s="2"/>
       <c r="D208" s="3"/>
       <c r="E208" s="4" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -79983,11 +80030,11 @@
       </c>
       <c r="B209" s="2"/>
       <c r="C209" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D209" s="4"/>
       <c r="E209" s="5" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -79998,7 +80045,7 @@
       <c r="C210" s="2"/>
       <c r="D210" s="4"/>
       <c r="E210" s="4" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -80007,11 +80054,11 @@
       </c>
       <c r="B211" s="2"/>
       <c r="C211" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D211" s="4"/>
       <c r="E211" s="4" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -80033,7 +80080,7 @@
       <c r="C213" s="2"/>
       <c r="D213" s="4"/>
       <c r="E213" s="4" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -80044,7 +80091,7 @@
       <c r="C214" s="2"/>
       <c r="D214" s="4"/>
       <c r="E214" s="5" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -80066,7 +80113,7 @@
       <c r="C216" s="2"/>
       <c r="D216" s="4"/>
       <c r="E216" s="4" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -80077,7 +80124,7 @@
       <c r="C217" s="2"/>
       <c r="D217" s="4"/>
       <c r="E217" s="4" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -80088,7 +80135,7 @@
       <c r="C218" s="2"/>
       <c r="D218" s="4"/>
       <c r="E218" s="4" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -80121,7 +80168,7 @@
       <c r="C221" s="2"/>
       <c r="D221" s="4"/>
       <c r="E221" s="4" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -80130,11 +80177,11 @@
       </c>
       <c r="B222" s="2"/>
       <c r="C222" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D222" s="4"/>
       <c r="E222" s="4" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -80145,7 +80192,7 @@
       <c r="C223" s="2"/>
       <c r="D223" s="4"/>
       <c r="E223" s="5" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -80156,7 +80203,7 @@
       <c r="C224" s="2"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -80167,7 +80214,7 @@
       <c r="C225" s="2"/>
       <c r="D225" s="4"/>
       <c r="E225" s="4" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -80176,11 +80223,11 @@
       </c>
       <c r="B226" s="2"/>
       <c r="C226" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D226" s="4"/>
       <c r="E226" s="4" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -80189,7 +80236,7 @@
       </c>
       <c r="B227" s="2"/>
       <c r="C227" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D227" s="4"/>
       <c r="E227" s="5" t="s">
@@ -80202,11 +80249,11 @@
       </c>
       <c r="B228" s="2"/>
       <c r="C228" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D228" s="4"/>
       <c r="E228" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -80215,11 +80262,11 @@
       </c>
       <c r="B229" s="2"/>
       <c r="C229" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D229" s="4"/>
       <c r="E229" s="4" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -80228,11 +80275,11 @@
       </c>
       <c r="B230" s="2"/>
       <c r="C230" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D230" s="4"/>
       <c r="E230" s="4" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -80243,7 +80290,7 @@
       <c r="C231" s="2"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -80254,7 +80301,7 @@
       <c r="C232" s="2"/>
       <c r="D232" s="4"/>
       <c r="E232" s="5" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -80265,7 +80312,7 @@
       <c r="C233" s="2"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -80276,7 +80323,7 @@
       <c r="C234" s="2"/>
       <c r="D234" s="4"/>
       <c r="E234" s="5" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -80287,7 +80334,7 @@
       <c r="C235" s="2"/>
       <c r="D235" s="4"/>
       <c r="E235" s="4" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -80298,7 +80345,7 @@
       <c r="C236" s="2"/>
       <c r="D236" s="4"/>
       <c r="E236" s="5" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -80309,7 +80356,7 @@
       <c r="C237" s="2"/>
       <c r="D237" s="4"/>
       <c r="E237" s="5" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -80320,7 +80367,7 @@
       <c r="C238" s="2"/>
       <c r="D238" s="4"/>
       <c r="E238" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -80331,7 +80378,7 @@
       <c r="C239" s="2"/>
       <c r="D239" s="4"/>
       <c r="E239" s="4" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -80342,7 +80389,7 @@
       <c r="C240" s="2"/>
       <c r="D240" s="4"/>
       <c r="E240" s="4" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -80353,7 +80400,7 @@
       <c r="C241" s="2"/>
       <c r="D241" s="4"/>
       <c r="E241" s="4" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -80373,11 +80420,11 @@
       </c>
       <c r="B243" s="2"/>
       <c r="C243" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D243" s="4"/>
       <c r="E243" s="5" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -80386,11 +80433,11 @@
       </c>
       <c r="B244" s="2"/>
       <c r="C244" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D244" s="4"/>
       <c r="E244" s="4" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -80399,11 +80446,11 @@
       </c>
       <c r="B245" s="2"/>
       <c r="C245" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D245" s="4"/>
       <c r="E245" s="5" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -80412,11 +80459,11 @@
       </c>
       <c r="B246" s="2"/>
       <c r="C246" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D246" s="4"/>
       <c r="E246" s="4" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -80426,10 +80473,10 @@
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
       <c r="D247" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E247" s="5" t="s">
         <v>1083</v>
-      </c>
-      <c r="E247" s="5" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -80440,7 +80487,7 @@
       <c r="C248" s="2"/>
       <c r="D248" s="4"/>
       <c r="E248" s="4" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -80451,7 +80498,7 @@
       <c r="C249" s="2"/>
       <c r="D249" s="4"/>
       <c r="E249" s="4" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -80460,11 +80507,11 @@
       </c>
       <c r="B250" s="2"/>
       <c r="C250" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D250" s="4"/>
       <c r="E250" s="5" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -80475,7 +80522,7 @@
       <c r="C251" s="2"/>
       <c r="D251" s="4"/>
       <c r="E251" s="4" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -80486,7 +80533,7 @@
       <c r="C252" s="2"/>
       <c r="D252" s="4"/>
       <c r="E252" s="4" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -80497,22 +80544,22 @@
       <c r="C253" s="2"/>
       <c r="D253" s="4"/>
       <c r="E253" s="4" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="2" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="B254" s="2"/>
       <c r="C254" s="9" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="E254" s="4" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -80523,7 +80570,7 @@
       <c r="C255" s="2"/>
       <c r="D255" s="4"/>
       <c r="E255" s="4" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -80534,7 +80581,7 @@
       <c r="C256" s="2"/>
       <c r="D256" s="4"/>
       <c r="E256" s="4" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -80545,7 +80592,7 @@
       <c r="C257" s="2"/>
       <c r="D257" s="4"/>
       <c r="E257" s="5" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -80556,7 +80603,7 @@
       <c r="C258" s="2"/>
       <c r="D258" s="4"/>
       <c r="E258" s="4" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -80587,7 +80634,7 @@
       </c>
       <c r="B261" s="2"/>
       <c r="C261" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D261" s="4"/>
       <c r="E261" s="5" t="s">
@@ -80602,7 +80649,7 @@
       <c r="C262" s="2"/>
       <c r="D262" s="4"/>
       <c r="E262" s="4" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -80613,7 +80660,7 @@
       <c r="C263" s="2"/>
       <c r="D263" s="4"/>
       <c r="E263" s="4" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -80624,7 +80671,7 @@
       <c r="C264" s="2"/>
       <c r="D264" s="4"/>
       <c r="E264" s="4" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -80646,7 +80693,7 @@
       <c r="C266" s="2"/>
       <c r="D266" s="4"/>
       <c r="E266" s="4" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -80657,7 +80704,7 @@
       <c r="C267" s="2"/>
       <c r="D267" s="4"/>
       <c r="E267" s="5" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -80673,15 +80720,15 @@
     </row>
     <row r="269" spans="1:5">
       <c r="A269" s="2" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B269" s="2"/>
       <c r="C269" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D269" s="4"/>
       <c r="E269" s="4" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -80692,7 +80739,7 @@
       <c r="C270" s="2"/>
       <c r="D270" s="4"/>
       <c r="E270" s="4" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -80703,7 +80750,7 @@
       <c r="C271" s="2"/>
       <c r="D271" s="4"/>
       <c r="E271" s="5" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -80712,11 +80759,11 @@
       </c>
       <c r="B272" s="2"/>
       <c r="C272" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D272" s="4"/>
       <c r="E272" s="4" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -80725,7 +80772,7 @@
       </c>
       <c r="B273" s="2"/>
       <c r="C273" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D273" s="4"/>
       <c r="E273" s="5" t="s">
@@ -80740,7 +80787,7 @@
       <c r="C274" s="2"/>
       <c r="D274" s="4"/>
       <c r="E274" s="5" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -80749,11 +80796,11 @@
       </c>
       <c r="B275" s="2"/>
       <c r="C275" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D275" s="4"/>
       <c r="E275" s="5" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -80775,7 +80822,7 @@
       <c r="C277" s="2"/>
       <c r="D277" s="4"/>
       <c r="E277" s="4" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -80786,7 +80833,7 @@
       <c r="C278" s="2"/>
       <c r="D278" s="4"/>
       <c r="E278" s="4" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -80797,7 +80844,7 @@
       <c r="C279" s="2"/>
       <c r="D279" s="4"/>
       <c r="E279" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -80808,7 +80855,7 @@
       <c r="C280" s="2"/>
       <c r="D280" s="4"/>
       <c r="E280" s="4" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -80819,7 +80866,7 @@
       <c r="C281" s="2"/>
       <c r="D281" s="4"/>
       <c r="E281" s="4" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -80828,11 +80875,11 @@
       </c>
       <c r="B282" s="2"/>
       <c r="C282" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D282" s="4"/>
       <c r="E282" s="4" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -80841,11 +80888,11 @@
       </c>
       <c r="B283" s="2"/>
       <c r="C283" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D283" s="4"/>
       <c r="E283" s="4" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -80854,11 +80901,11 @@
       </c>
       <c r="B284" s="2"/>
       <c r="C284" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D284" s="4"/>
       <c r="E284" s="4" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -80869,20 +80916,20 @@
       <c r="C285" s="2"/>
       <c r="D285" s="4"/>
       <c r="E285" s="4" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="286" spans="1:5">
       <c r="A286" s="2" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
       <c r="D286" s="4" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="E286" s="5" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -80893,20 +80940,22 @@
       <c r="C287" s="2"/>
       <c r="D287" s="4"/>
       <c r="E287" s="5" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="288" spans="1:5">
       <c r="A288" s="2" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="B288" s="2"/>
       <c r="C288" s="9" t="s">
-        <v>1614</v>
-      </c>
-      <c r="D288" s="3"/>
+        <v>1612</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>1653</v>
+      </c>
       <c r="E288" s="4" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -80915,11 +80964,13 @@
       </c>
       <c r="B289" s="2"/>
       <c r="C289" s="9" t="s">
-        <v>1653</v>
-      </c>
-      <c r="D289" s="4"/>
+        <v>1651</v>
+      </c>
+      <c r="D289" s="4" t="s">
+        <v>1655</v>
+      </c>
       <c r="E289" s="4" t="s">
-        <v>1118</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -80930,7 +80981,7 @@
       <c r="C290" s="2"/>
       <c r="D290" s="4"/>
       <c r="E290" s="4" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -80939,11 +80990,13 @@
       </c>
       <c r="B291" s="2"/>
       <c r="C291" s="9" t="s">
-        <v>1614</v>
-      </c>
-      <c r="D291" s="3"/>
+        <v>1612</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>1656</v>
+      </c>
       <c r="E291" s="4" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -80952,13 +81005,13 @@
       </c>
       <c r="B292" s="2"/>
       <c r="C292" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D292" s="7" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="E292" s="7" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -80967,11 +81020,11 @@
       </c>
       <c r="B293" s="2"/>
       <c r="C293" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D293" s="4"/>
       <c r="E293" s="5" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -80982,7 +81035,7 @@
       <c r="C294" s="2"/>
       <c r="D294" s="4"/>
       <c r="E294" s="4" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -80993,7 +81046,7 @@
       <c r="C295" s="2"/>
       <c r="D295" s="4"/>
       <c r="E295" s="5" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -81012,10 +81065,10 @@
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
       <c r="D297" s="7" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="E297" s="6" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -81035,7 +81088,7 @@
       <c r="C299" s="2"/>
       <c r="D299" s="4"/>
       <c r="E299" s="4" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -81057,7 +81110,7 @@
       <c r="C301" s="2"/>
       <c r="D301" s="4"/>
       <c r="E301" s="5" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -81068,7 +81121,7 @@
       <c r="C302" s="2"/>
       <c r="D302" s="4"/>
       <c r="E302" s="5" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -81079,7 +81132,7 @@
       <c r="C303" s="2"/>
       <c r="D303" s="4"/>
       <c r="E303" s="4" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -81101,18 +81154,18 @@
       <c r="C305" s="2"/>
       <c r="D305" s="4"/>
       <c r="E305" s="5" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="306" spans="1:5">
       <c r="A306" s="2" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
       <c r="D306" s="4"/>
       <c r="E306" s="5" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -81123,7 +81176,7 @@
       <c r="C307" s="2"/>
       <c r="D307" s="4"/>
       <c r="E307" s="4" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -81134,7 +81187,7 @@
       <c r="C308" s="2"/>
       <c r="D308" s="4"/>
       <c r="E308" s="5" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -81145,7 +81198,7 @@
       <c r="C309" s="2"/>
       <c r="D309" s="4"/>
       <c r="E309" s="4" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -81167,7 +81220,7 @@
       <c r="C311" s="2"/>
       <c r="D311" s="4"/>
       <c r="E311" s="5" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -81178,18 +81231,18 @@
       <c r="C312" s="2"/>
       <c r="D312" s="4"/>
       <c r="E312" s="4" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="313" spans="1:5">
       <c r="A313" s="2" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
       <c r="D313" s="4"/>
       <c r="E313" s="4" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -81210,10 +81263,10 @@
       <c r="B315" s="2"/>
       <c r="C315" s="2"/>
       <c r="D315" s="7" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="E315" s="7" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -81224,7 +81277,7 @@
       <c r="C316" s="2"/>
       <c r="D316" s="4"/>
       <c r="E316" s="4" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -81246,7 +81299,7 @@
       <c r="C318" s="2"/>
       <c r="D318" s="4"/>
       <c r="E318" s="5" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -81268,7 +81321,7 @@
       <c r="C320" s="2"/>
       <c r="D320" s="4"/>
       <c r="E320" s="5" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -81279,7 +81332,7 @@
       <c r="C321" s="2"/>
       <c r="D321" s="4"/>
       <c r="E321" s="5" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -81288,11 +81341,11 @@
       </c>
       <c r="B322" s="2"/>
       <c r="C322" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D322" s="4"/>
       <c r="E322" s="4" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -81303,7 +81356,7 @@
       <c r="C323" s="2"/>
       <c r="D323" s="4"/>
       <c r="E323" s="4" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -81312,11 +81365,11 @@
       </c>
       <c r="B324" s="2"/>
       <c r="C324" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D324" s="4"/>
       <c r="E324" s="4" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -81325,11 +81378,11 @@
       </c>
       <c r="B325" s="2"/>
       <c r="C325" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D325" s="4"/>
       <c r="E325" s="4" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -81340,7 +81393,7 @@
       <c r="C326" s="2"/>
       <c r="D326" s="4"/>
       <c r="E326" s="4" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -81362,7 +81415,7 @@
       <c r="C328" s="2"/>
       <c r="D328" s="4"/>
       <c r="E328" s="4" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -81371,11 +81424,11 @@
       </c>
       <c r="B329" s="2"/>
       <c r="C329" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D329" s="4"/>
       <c r="E329" s="5" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -81386,7 +81439,7 @@
       <c r="C330" s="2"/>
       <c r="D330" s="4"/>
       <c r="E330" s="4" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -81397,7 +81450,7 @@
       <c r="C331" s="2"/>
       <c r="D331" s="4"/>
       <c r="E331" s="4" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -81408,7 +81461,7 @@
       <c r="C332" s="2"/>
       <c r="D332" s="4"/>
       <c r="E332" s="4" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -81419,7 +81472,7 @@
       <c r="C333" s="2"/>
       <c r="D333" s="4"/>
       <c r="E333" s="4" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -81430,7 +81483,7 @@
       <c r="C334" s="2"/>
       <c r="D334" s="4"/>
       <c r="E334" s="5" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -81441,7 +81494,7 @@
       <c r="C335" s="2"/>
       <c r="D335" s="4"/>
       <c r="E335" s="4" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -81450,11 +81503,11 @@
       </c>
       <c r="B336" s="2"/>
       <c r="C336" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D336" s="4"/>
       <c r="E336" s="5" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -81475,10 +81528,10 @@
       <c r="B338" s="2"/>
       <c r="C338" s="2"/>
       <c r="D338" s="7" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="E338" s="7" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -81489,7 +81542,7 @@
       <c r="C339" s="2"/>
       <c r="D339" s="4"/>
       <c r="E339" s="4" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -81520,7 +81573,7 @@
       <c r="C342" s="2"/>
       <c r="D342" s="4"/>
       <c r="E342" s="5" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -81531,7 +81584,7 @@
       <c r="C343" s="2"/>
       <c r="D343" s="4"/>
       <c r="E343" s="4" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -81542,7 +81595,7 @@
       <c r="C344" s="2"/>
       <c r="D344" s="4"/>
       <c r="E344" s="4" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -81553,7 +81606,7 @@
       <c r="C345" s="2"/>
       <c r="D345" s="4"/>
       <c r="E345" s="4" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -81562,11 +81615,11 @@
       </c>
       <c r="B346" s="2"/>
       <c r="C346" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D346" s="4"/>
       <c r="E346" s="4" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -81575,11 +81628,11 @@
       </c>
       <c r="B347" s="2"/>
       <c r="C347" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D347" s="3"/>
       <c r="E347" s="4" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -81590,7 +81643,7 @@
       <c r="C348" s="2"/>
       <c r="D348" s="4"/>
       <c r="E348" s="4" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -81612,7 +81665,7 @@
       <c r="C350" s="2"/>
       <c r="D350" s="4"/>
       <c r="E350" s="4" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -81622,10 +81675,10 @@
       <c r="B351" s="2"/>
       <c r="C351" s="2"/>
       <c r="D351" s="7" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="E351" s="7" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -81634,11 +81687,11 @@
       </c>
       <c r="B352" s="2"/>
       <c r="C352" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D352" s="4"/>
       <c r="E352" s="5" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -81647,11 +81700,11 @@
       </c>
       <c r="B353" s="2"/>
       <c r="C353" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D353" s="4"/>
       <c r="E353" s="4" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -81662,7 +81715,7 @@
       <c r="C354" s="2"/>
       <c r="D354" s="4"/>
       <c r="E354" s="4" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -81671,11 +81724,11 @@
       </c>
       <c r="B355" s="2"/>
       <c r="C355" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D355" s="4"/>
       <c r="E355" s="5" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -81684,11 +81737,11 @@
       </c>
       <c r="B356" s="2"/>
       <c r="C356" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D356" s="4"/>
       <c r="E356" s="5" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -81697,11 +81750,11 @@
       </c>
       <c r="B357" s="2"/>
       <c r="C357" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D357" s="4"/>
       <c r="E357" s="4" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -81710,11 +81763,11 @@
       </c>
       <c r="B358" s="2"/>
       <c r="C358" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D358" s="4"/>
       <c r="E358" s="4" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -81723,11 +81776,11 @@
       </c>
       <c r="B359" s="2"/>
       <c r="C359" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D359" s="4"/>
       <c r="E359" s="4" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -81736,11 +81789,11 @@
       </c>
       <c r="B360" s="2"/>
       <c r="C360" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D360" s="4"/>
       <c r="E360" s="4" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -81749,11 +81802,11 @@
       </c>
       <c r="B361" s="2"/>
       <c r="C361" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D361" s="4"/>
       <c r="E361" s="4" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -81762,11 +81815,11 @@
       </c>
       <c r="B362" s="2"/>
       <c r="C362" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D362" s="4"/>
       <c r="E362" s="4" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -81775,11 +81828,11 @@
       </c>
       <c r="B363" s="2"/>
       <c r="C363" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D363" s="4"/>
       <c r="E363" s="4" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -81790,7 +81843,7 @@
       <c r="C364" s="2"/>
       <c r="D364" s="4"/>
       <c r="E364" s="4" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -81801,7 +81854,7 @@
       <c r="C365" s="2"/>
       <c r="D365" s="4"/>
       <c r="E365" s="5" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -81821,11 +81874,11 @@
       </c>
       <c r="B367" s="2"/>
       <c r="C367" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D367" s="4"/>
       <c r="E367" s="4" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -81834,11 +81887,11 @@
       </c>
       <c r="B368" s="2"/>
       <c r="C368" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D368" s="4"/>
       <c r="E368" s="4" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -81849,7 +81902,7 @@
       <c r="C369" s="2"/>
       <c r="D369" s="4"/>
       <c r="E369" s="4" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -81858,11 +81911,11 @@
       </c>
       <c r="B370" s="2"/>
       <c r="C370" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D370" s="4"/>
       <c r="E370" s="5" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -81871,11 +81924,11 @@
       </c>
       <c r="B371" s="2"/>
       <c r="C371" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D371" s="4"/>
       <c r="E371" s="4" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -81884,11 +81937,11 @@
       </c>
       <c r="B372" s="2"/>
       <c r="C372" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D372" s="4"/>
       <c r="E372" s="4" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -81897,11 +81950,11 @@
       </c>
       <c r="B373" s="2"/>
       <c r="C373" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D373" s="4"/>
       <c r="E373" s="4" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -81912,7 +81965,7 @@
       <c r="C374" s="2"/>
       <c r="D374" s="4"/>
       <c r="E374" s="4" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -81923,7 +81976,7 @@
       <c r="C375" s="2"/>
       <c r="D375" s="4"/>
       <c r="E375" s="5" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -81932,11 +81985,11 @@
       </c>
       <c r="B376" s="2"/>
       <c r="C376" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D376" s="4"/>
       <c r="E376" s="4" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -81947,7 +82000,7 @@
       <c r="C377" s="2"/>
       <c r="D377" s="4"/>
       <c r="E377" s="4" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -81958,7 +82011,7 @@
       <c r="C378" s="2"/>
       <c r="D378" s="4"/>
       <c r="E378" s="5" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -81969,7 +82022,7 @@
       <c r="C379" s="2"/>
       <c r="D379" s="4"/>
       <c r="E379" s="5" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -81978,13 +82031,13 @@
       </c>
       <c r="B380" s="2"/>
       <c r="C380" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D380" s="7" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="E380" s="7" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -82002,11 +82055,11 @@
       </c>
       <c r="B382" s="2"/>
       <c r="C382" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D382" s="4"/>
       <c r="E382" s="5" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -82015,11 +82068,11 @@
       </c>
       <c r="B383" s="2"/>
       <c r="C383" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D383" s="4"/>
       <c r="E383" s="5" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -82030,7 +82083,7 @@
       <c r="C384" s="2"/>
       <c r="D384" s="4"/>
       <c r="E384" s="4" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -82041,7 +82094,7 @@
       <c r="C385" s="2"/>
       <c r="D385" s="4"/>
       <c r="E385" s="5" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -82052,7 +82105,7 @@
       <c r="C386" s="2"/>
       <c r="D386" s="4"/>
       <c r="E386" s="4" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -82063,7 +82116,7 @@
       <c r="C387" s="2"/>
       <c r="D387" s="4"/>
       <c r="E387" s="5" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -82081,11 +82134,11 @@
       </c>
       <c r="B389" s="2"/>
       <c r="C389" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D389" s="4"/>
       <c r="E389" s="5" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -82094,11 +82147,11 @@
       </c>
       <c r="B390" s="2"/>
       <c r="C390" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D390" s="4"/>
       <c r="E390" s="4" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -82109,7 +82162,7 @@
       <c r="C391" s="2"/>
       <c r="D391" s="4"/>
       <c r="E391" s="4" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -82120,7 +82173,7 @@
       <c r="C392" s="2"/>
       <c r="D392" s="4"/>
       <c r="E392" s="4" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -82129,11 +82182,11 @@
       </c>
       <c r="B393" s="2"/>
       <c r="C393" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D393" s="4"/>
       <c r="E393" s="4" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -82144,7 +82197,7 @@
       <c r="C394" s="2"/>
       <c r="D394" s="4"/>
       <c r="E394" s="5" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -82153,7 +82206,7 @@
       </c>
       <c r="B395" s="2"/>
       <c r="C395" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D395" s="4"/>
       <c r="E395" s="5" t="s">
@@ -82166,11 +82219,11 @@
       </c>
       <c r="B396" s="2"/>
       <c r="C396" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D396" s="4"/>
       <c r="E396" s="4" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -82179,11 +82232,11 @@
       </c>
       <c r="B397" s="2"/>
       <c r="C397" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D397" s="4"/>
       <c r="E397" s="4" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -82194,7 +82247,7 @@
       <c r="C398" s="2"/>
       <c r="D398" s="4"/>
       <c r="E398" s="4" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -82205,7 +82258,7 @@
       <c r="C399" s="2"/>
       <c r="D399" s="4"/>
       <c r="E399" s="4" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -82214,11 +82267,11 @@
       </c>
       <c r="B400" s="2"/>
       <c r="C400" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D400" s="4"/>
       <c r="E400" s="4" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -82229,7 +82282,7 @@
       <c r="C401" s="2"/>
       <c r="D401" s="4"/>
       <c r="E401" s="5" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -82240,7 +82293,7 @@
       <c r="C402" s="2"/>
       <c r="D402" s="4"/>
       <c r="E402" s="5" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -82251,7 +82304,7 @@
       <c r="C403" s="2"/>
       <c r="D403" s="4"/>
       <c r="E403" s="4" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -82262,7 +82315,7 @@
       <c r="C404" s="2"/>
       <c r="D404" s="3"/>
       <c r="E404" s="4" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -82271,11 +82324,11 @@
       </c>
       <c r="B405" s="2"/>
       <c r="C405" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D405" s="4"/>
       <c r="E405" s="4" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -82297,7 +82350,7 @@
       <c r="C407" s="2"/>
       <c r="D407" s="4"/>
       <c r="E407" s="4" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -82317,22 +82370,22 @@
       </c>
       <c r="B409" s="2"/>
       <c r="C409" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D409" s="4"/>
       <c r="E409" s="5" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="410" spans="1:5">
       <c r="A410" s="2" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="B410" s="2"/>
       <c r="C410" s="2"/>
       <c r="D410" s="4"/>
       <c r="E410" s="5" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -82342,10 +82395,10 @@
       <c r="B411" s="2"/>
       <c r="C411" s="2"/>
       <c r="D411" s="7" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="E411" s="7" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -82367,7 +82420,7 @@
       <c r="C413" s="2"/>
       <c r="D413" s="4"/>
       <c r="E413" s="4" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -82387,11 +82440,11 @@
       </c>
       <c r="B415" s="2"/>
       <c r="C415" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D415" s="4"/>
       <c r="E415" s="4" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -82402,7 +82455,7 @@
       <c r="C416" s="2"/>
       <c r="D416" s="4"/>
       <c r="E416" s="4" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -82413,7 +82466,7 @@
       <c r="C417" s="2"/>
       <c r="D417" s="4"/>
       <c r="E417" s="4" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -82424,7 +82477,7 @@
       <c r="C418" s="2"/>
       <c r="D418" s="4"/>
       <c r="E418" s="4" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -82435,7 +82488,7 @@
       <c r="C419" s="2"/>
       <c r="D419" s="4"/>
       <c r="E419" s="5" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -82455,11 +82508,11 @@
       </c>
       <c r="B421" s="2"/>
       <c r="C421" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D421" s="4"/>
       <c r="E421" s="4" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -82468,11 +82521,11 @@
       </c>
       <c r="B422" s="2"/>
       <c r="C422" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D422" s="4"/>
       <c r="E422" s="5" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -82481,11 +82534,11 @@
       </c>
       <c r="B423" s="2"/>
       <c r="C423" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D423" s="4"/>
       <c r="E423" s="5" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -82494,11 +82547,11 @@
       </c>
       <c r="B424" s="2"/>
       <c r="C424" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D424" s="4"/>
       <c r="E424" s="4" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -82520,7 +82573,7 @@
       <c r="C426" s="2"/>
       <c r="D426" s="4"/>
       <c r="E426" s="4" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -82531,7 +82584,7 @@
       <c r="C427" s="2"/>
       <c r="D427" s="3"/>
       <c r="E427" s="4" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -82553,7 +82606,7 @@
       <c r="C429" s="2"/>
       <c r="D429" s="4"/>
       <c r="E429" s="4" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -82564,7 +82617,7 @@
       <c r="C430" s="2"/>
       <c r="D430" s="3"/>
       <c r="E430" s="4" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -82573,11 +82626,11 @@
       </c>
       <c r="B431" s="2"/>
       <c r="C431" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D431" s="4"/>
       <c r="E431" s="4" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -82586,11 +82639,11 @@
       </c>
       <c r="B432" s="2"/>
       <c r="C432" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D432" s="4"/>
       <c r="E432" s="4" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -82623,7 +82676,7 @@
       <c r="C435" s="2"/>
       <c r="D435" s="4"/>
       <c r="E435" s="4" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -82634,7 +82687,7 @@
       <c r="C436" s="2"/>
       <c r="D436" s="4"/>
       <c r="E436" s="4" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -82643,11 +82696,11 @@
       </c>
       <c r="B437" s="2"/>
       <c r="C437" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D437" s="4"/>
       <c r="E437" s="4" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -82669,7 +82722,7 @@
       <c r="C439" s="2"/>
       <c r="D439" s="4"/>
       <c r="E439" s="5" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -82678,11 +82731,11 @@
       </c>
       <c r="B440" s="2"/>
       <c r="C440" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D440" s="4"/>
       <c r="E440" s="4" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -82693,7 +82746,7 @@
       <c r="C441" s="2"/>
       <c r="D441" s="4"/>
       <c r="E441" s="5" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -82704,7 +82757,7 @@
       <c r="C442" s="2"/>
       <c r="D442" s="4"/>
       <c r="E442" s="4" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -82715,18 +82768,18 @@
       <c r="C443" s="2"/>
       <c r="D443" s="4"/>
       <c r="E443" s="4" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="444" spans="1:5">
       <c r="A444" s="2" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="B444" s="2"/>
       <c r="C444" s="2"/>
       <c r="D444" s="4"/>
       <c r="E444" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -82737,7 +82790,7 @@
       <c r="C445" s="2"/>
       <c r="D445" s="4"/>
       <c r="E445" s="5" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -82748,7 +82801,7 @@
       <c r="C446" s="2"/>
       <c r="D446" s="4"/>
       <c r="E446" s="4" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -82759,7 +82812,7 @@
       <c r="C447" s="2"/>
       <c r="D447" s="4"/>
       <c r="E447" s="4" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -82770,7 +82823,7 @@
       <c r="C448" s="2"/>
       <c r="D448" s="4"/>
       <c r="E448" s="4" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -82792,7 +82845,7 @@
       <c r="C450" s="2"/>
       <c r="D450" s="4"/>
       <c r="E450" s="4" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -82801,7 +82854,7 @@
       </c>
       <c r="B451" s="2"/>
       <c r="C451" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D451" s="4"/>
       <c r="E451" s="5" t="s">
@@ -82814,11 +82867,11 @@
       </c>
       <c r="B452" s="2"/>
       <c r="C452" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D452" s="4"/>
       <c r="E452" s="4" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -82829,7 +82882,7 @@
       <c r="C453" s="2"/>
       <c r="D453" s="4"/>
       <c r="E453" s="4" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -82851,7 +82904,7 @@
       <c r="C455" s="2"/>
       <c r="D455" s="4"/>
       <c r="E455" s="4" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -82862,7 +82915,7 @@
       <c r="C456" s="2"/>
       <c r="D456" s="4"/>
       <c r="E456" s="4" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -82872,10 +82925,10 @@
       <c r="B457" s="2"/>
       <c r="C457" s="2"/>
       <c r="D457" s="7" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="E457" s="7" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -82884,11 +82937,11 @@
       </c>
       <c r="B458" s="2"/>
       <c r="C458" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D458" s="4"/>
       <c r="E458" s="4" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -82897,11 +82950,11 @@
       </c>
       <c r="B459" s="2"/>
       <c r="C459" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D459" s="4"/>
       <c r="E459" s="4" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -82910,11 +82963,11 @@
       </c>
       <c r="B460" s="2"/>
       <c r="C460" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D460" s="4"/>
       <c r="E460" s="4" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -82923,11 +82976,11 @@
       </c>
       <c r="B461" s="2"/>
       <c r="C461" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D461" s="4"/>
       <c r="E461" s="5" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -82938,7 +82991,7 @@
       <c r="C462" s="2"/>
       <c r="D462" s="4"/>
       <c r="E462" s="4" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -82947,11 +83000,11 @@
       </c>
       <c r="B463" s="2"/>
       <c r="C463" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D463" s="4"/>
       <c r="E463" s="4" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -82960,11 +83013,11 @@
       </c>
       <c r="B464" s="2"/>
       <c r="C464" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D464" s="4"/>
       <c r="E464" s="4" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="465" spans="1:5">
@@ -82973,11 +83026,11 @@
       </c>
       <c r="B465" s="2"/>
       <c r="C465" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D465" s="4"/>
       <c r="E465" s="4" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="466" spans="1:5">
@@ -82986,11 +83039,11 @@
       </c>
       <c r="B466" s="2"/>
       <c r="C466" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D466" s="4"/>
       <c r="E466" s="5" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -82999,11 +83052,11 @@
       </c>
       <c r="B467" s="2"/>
       <c r="C467" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D467" s="4"/>
       <c r="E467" s="4" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -83014,7 +83067,7 @@
       <c r="C468" s="2"/>
       <c r="D468" s="4"/>
       <c r="E468" s="5" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -83023,11 +83076,11 @@
       </c>
       <c r="B469" s="2"/>
       <c r="C469" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D469" s="4"/>
       <c r="E469" s="4" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -83036,11 +83089,11 @@
       </c>
       <c r="B470" s="2"/>
       <c r="C470" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D470" s="4"/>
       <c r="E470" s="4" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -83051,7 +83104,7 @@
       <c r="C471" s="2"/>
       <c r="D471" s="4"/>
       <c r="E471" s="5" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -83060,11 +83113,11 @@
       </c>
       <c r="B472" s="2"/>
       <c r="C472" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D472" s="4"/>
       <c r="E472" s="4" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -83073,11 +83126,11 @@
       </c>
       <c r="B473" s="2"/>
       <c r="C473" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D473" s="4"/>
       <c r="E473" s="4" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -83098,10 +83151,10 @@
       <c r="B475" s="2"/>
       <c r="C475" s="2"/>
       <c r="D475" s="7" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="E475" s="7" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -83111,10 +83164,10 @@
       <c r="B476" s="2"/>
       <c r="C476" s="2"/>
       <c r="D476" s="7" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="E476" s="7" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -83125,7 +83178,7 @@
       <c r="C477" s="2"/>
       <c r="D477" s="4"/>
       <c r="E477" s="5" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -83145,11 +83198,11 @@
       </c>
       <c r="B479" s="2"/>
       <c r="C479" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D479" s="4"/>
       <c r="E479" s="4" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -83158,11 +83211,11 @@
       </c>
       <c r="B480" s="2"/>
       <c r="C480" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D480" s="4"/>
       <c r="E480" s="5" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="481" spans="1:5">
@@ -83171,11 +83224,11 @@
       </c>
       <c r="B481" s="2"/>
       <c r="C481" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D481" s="4"/>
       <c r="E481" s="5" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="482" spans="1:5">
@@ -83206,7 +83259,7 @@
       <c r="C484" s="2"/>
       <c r="D484" s="4"/>
       <c r="E484" s="5" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -83217,20 +83270,20 @@
       <c r="C485" s="2"/>
       <c r="D485" s="4"/>
       <c r="E485" s="4" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="486" spans="1:5">
       <c r="A486" s="2" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="B486" s="2"/>
       <c r="C486" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D486" s="4"/>
       <c r="E486" s="4" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="487" spans="1:5">
@@ -83239,11 +83292,11 @@
       </c>
       <c r="B487" s="2"/>
       <c r="C487" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D487" s="4"/>
       <c r="E487" s="4" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -83252,11 +83305,11 @@
       </c>
       <c r="B488" s="2"/>
       <c r="C488" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D488" s="4"/>
       <c r="E488" s="5" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -83266,10 +83319,10 @@
       <c r="B489" s="2"/>
       <c r="C489" s="2"/>
       <c r="D489" s="7" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="E489" s="7" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -83278,11 +83331,11 @@
       </c>
       <c r="B490" s="2"/>
       <c r="C490" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D490" s="4"/>
       <c r="E490" s="5" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="491" spans="1:5">
@@ -83293,7 +83346,7 @@
       <c r="C491" s="2"/>
       <c r="D491" s="4"/>
       <c r="E491" s="4" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -83304,7 +83357,7 @@
       <c r="C492" s="2"/>
       <c r="D492" s="4"/>
       <c r="E492" s="4" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -83313,11 +83366,11 @@
       </c>
       <c r="B493" s="2"/>
       <c r="C493" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D493" s="4"/>
       <c r="E493" s="4" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="494" spans="1:5">
@@ -83328,7 +83381,7 @@
       <c r="C494" s="2"/>
       <c r="D494" s="4"/>
       <c r="E494" s="4" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="495" spans="1:5">
@@ -83339,7 +83392,7 @@
       <c r="C495" s="2"/>
       <c r="D495" s="4"/>
       <c r="E495" s="4" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -83350,7 +83403,7 @@
       <c r="C496" s="2"/>
       <c r="D496" s="4"/>
       <c r="E496" s="5" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -83361,7 +83414,7 @@
       <c r="C497" s="2"/>
       <c r="D497" s="4"/>
       <c r="E497" s="4" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -83383,7 +83436,7 @@
       <c r="C499" s="2"/>
       <c r="D499" s="4"/>
       <c r="E499" s="5" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -83403,11 +83456,11 @@
       </c>
       <c r="B501" s="2"/>
       <c r="C501" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D501" s="4"/>
       <c r="E501" s="5" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="502" spans="1:5" ht="17">
@@ -83416,13 +83469,13 @@
       </c>
       <c r="B502" s="2"/>
       <c r="C502" s="9" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="D502" s="13" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="E502" s="7" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="503" spans="1:5">
@@ -83442,11 +83495,11 @@
       </c>
       <c r="B504" s="2"/>
       <c r="C504" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D504" s="4"/>
       <c r="E504" s="4" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="505" spans="1:5">
@@ -83467,10 +83520,10 @@
       <c r="B506" s="2"/>
       <c r="C506" s="2"/>
       <c r="D506" s="7" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="E506" s="7" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="507" spans="1:5">
@@ -83481,7 +83534,7 @@
       <c r="C507" s="2"/>
       <c r="D507" s="4"/>
       <c r="E507" s="4" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="508" spans="1:5">
@@ -83490,11 +83543,11 @@
       </c>
       <c r="B508" s="2"/>
       <c r="C508" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D508" s="3"/>
       <c r="E508" s="4" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="509" spans="1:5">
@@ -83505,7 +83558,7 @@
       <c r="C509" s="2"/>
       <c r="D509" s="4"/>
       <c r="E509" s="4" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="510" spans="1:5">
@@ -83516,7 +83569,7 @@
       <c r="C510" s="2"/>
       <c r="D510" s="4"/>
       <c r="E510" s="4" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="511" spans="1:5">
@@ -83538,7 +83591,7 @@
       <c r="C512" s="2"/>
       <c r="D512" s="4"/>
       <c r="E512" s="4" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="513" spans="1:5">
@@ -83547,11 +83600,11 @@
       </c>
       <c r="B513" s="2"/>
       <c r="C513" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D513" s="4"/>
       <c r="E513" s="4" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="514" spans="1:5">
@@ -83562,7 +83615,7 @@
       <c r="C514" s="2"/>
       <c r="D514" s="4"/>
       <c r="E514" s="4" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="515" spans="1:5">
@@ -83572,10 +83625,10 @@
       <c r="B515" s="2"/>
       <c r="C515" s="2"/>
       <c r="D515" s="7" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="E515" s="7" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="516" spans="1:5">
@@ -83586,7 +83639,7 @@
       <c r="C516" s="2"/>
       <c r="D516" s="3"/>
       <c r="E516" s="4" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="517" spans="1:5">
@@ -83595,11 +83648,11 @@
       </c>
       <c r="B517" s="2"/>
       <c r="C517" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D517" s="3"/>
       <c r="E517" s="4" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="518" spans="1:5">
@@ -83610,7 +83663,7 @@
       <c r="C518" s="2"/>
       <c r="D518" s="4"/>
       <c r="E518" s="4" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="519" spans="1:5">
@@ -83621,7 +83674,7 @@
       <c r="C519" s="2"/>
       <c r="D519" s="4"/>
       <c r="E519" s="4" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="520" spans="1:5">
@@ -83632,7 +83685,7 @@
       <c r="C520" s="2"/>
       <c r="D520" s="4"/>
       <c r="E520" s="5" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="521" spans="1:5">
@@ -83642,10 +83695,10 @@
       <c r="B521" s="2"/>
       <c r="C521" s="2"/>
       <c r="D521" s="7" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="E521" s="7" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="522" spans="1:5">
@@ -83654,7 +83707,7 @@
       </c>
       <c r="B522" s="2"/>
       <c r="C522" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D522" s="4"/>
       <c r="E522" s="5" t="s">
@@ -83669,7 +83722,7 @@
       <c r="C523" s="2"/>
       <c r="D523" s="4"/>
       <c r="E523" s="4" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="524" spans="1:5">
@@ -83680,7 +83733,7 @@
       <c r="C524" s="2"/>
       <c r="D524" s="4"/>
       <c r="E524" s="5" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="525" spans="1:5">
@@ -83691,7 +83744,7 @@
       <c r="C525" s="2"/>
       <c r="D525" s="4"/>
       <c r="E525" s="4" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="526" spans="1:5">
@@ -83700,11 +83753,11 @@
       </c>
       <c r="B526" s="2"/>
       <c r="C526" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D526" s="4"/>
       <c r="E526" s="5" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="527" spans="1:5">
@@ -83715,7 +83768,7 @@
       <c r="C527" s="2"/>
       <c r="D527" s="4"/>
       <c r="E527" s="4" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="528" spans="1:5">
@@ -83726,7 +83779,7 @@
       <c r="C528" s="2"/>
       <c r="D528" s="4"/>
       <c r="E528" s="4" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="529" spans="1:5">
@@ -83737,7 +83790,7 @@
       <c r="C529" s="2"/>
       <c r="D529" s="4"/>
       <c r="E529" s="4" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="530" spans="1:5">
@@ -83748,7 +83801,7 @@
       <c r="C530" s="2"/>
       <c r="D530" s="4"/>
       <c r="E530" s="5" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="531" spans="1:5">
@@ -83758,10 +83811,10 @@
       <c r="B531" s="2"/>
       <c r="C531" s="2"/>
       <c r="D531" s="7" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="E531" s="7" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="532" spans="1:5">
@@ -83783,7 +83836,7 @@
       <c r="C533" s="2"/>
       <c r="D533" s="4"/>
       <c r="E533" s="4" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="534" spans="1:5">
@@ -83794,7 +83847,7 @@
       <c r="C534" s="2"/>
       <c r="D534" s="4"/>
       <c r="E534" s="4" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="535" spans="1:5">
@@ -83803,11 +83856,11 @@
       </c>
       <c r="B535" s="2"/>
       <c r="C535" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D535" s="4"/>
       <c r="E535" s="4" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="536" spans="1:5">
@@ -83816,11 +83869,11 @@
       </c>
       <c r="B536" s="2"/>
       <c r="C536" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D536" s="4"/>
       <c r="E536" s="4" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="537" spans="1:5">
@@ -83829,11 +83882,11 @@
       </c>
       <c r="B537" s="2"/>
       <c r="C537" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D537" s="4"/>
       <c r="E537" s="5" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="538" spans="1:5">
@@ -83842,11 +83895,11 @@
       </c>
       <c r="B538" s="2"/>
       <c r="C538" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D538" s="4"/>
       <c r="E538" s="4" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="539" spans="1:5">
@@ -83857,7 +83910,7 @@
       <c r="C539" s="2"/>
       <c r="D539" s="4"/>
       <c r="E539" s="5" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="540" spans="1:5">
@@ -83868,7 +83921,7 @@
       <c r="C540" s="2"/>
       <c r="D540" s="4"/>
       <c r="E540" s="4" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="541" spans="1:5">
@@ -83879,18 +83932,18 @@
       <c r="C541" s="2"/>
       <c r="D541" s="4"/>
       <c r="E541" s="4" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="542" spans="1:5">
       <c r="A542" s="2" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="B542" s="2"/>
       <c r="C542" s="2"/>
       <c r="D542" s="4"/>
       <c r="E542" s="5" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="543" spans="1:5">
@@ -83901,7 +83954,7 @@
       <c r="C543" s="2"/>
       <c r="D543" s="3"/>
       <c r="E543" s="4" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="544" spans="1:5">
@@ -83912,7 +83965,7 @@
       <c r="C544" s="2"/>
       <c r="D544" s="4"/>
       <c r="E544" s="5" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="545" spans="1:5">
@@ -83923,7 +83976,7 @@
       <c r="C545" s="2"/>
       <c r="D545" s="4"/>
       <c r="E545" s="4" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="546" spans="1:5">
@@ -83933,10 +83986,10 @@
       <c r="B546" s="2"/>
       <c r="C546" s="2"/>
       <c r="D546" s="7" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="E546" s="7" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="547" spans="1:5">
@@ -83947,7 +84000,7 @@
       <c r="C547" s="2"/>
       <c r="D547" s="4"/>
       <c r="E547" s="5" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="548" spans="1:5">
@@ -83958,7 +84011,7 @@
       <c r="C548" s="2"/>
       <c r="D548" s="4"/>
       <c r="E548" s="4" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="549" spans="1:5">
@@ -83969,7 +84022,7 @@
       <c r="C549" s="2"/>
       <c r="D549" s="4"/>
       <c r="E549" s="4" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="550" spans="1:5">
@@ -83980,7 +84033,7 @@
       <c r="C550" s="2"/>
       <c r="D550" s="4"/>
       <c r="E550" s="4" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="551" spans="1:5">
@@ -83991,7 +84044,7 @@
       <c r="C551" s="2"/>
       <c r="D551" s="4"/>
       <c r="E551" s="4" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="552" spans="1:5">
@@ -84002,7 +84055,7 @@
       <c r="C552" s="2"/>
       <c r="D552" s="4"/>
       <c r="E552" s="4" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="553" spans="1:5">
@@ -84013,7 +84066,7 @@
       <c r="C553" s="2"/>
       <c r="D553" s="4"/>
       <c r="E553" s="5" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="554" spans="1:5">
@@ -84046,7 +84099,7 @@
       <c r="C556" s="2"/>
       <c r="D556" s="4"/>
       <c r="E556" s="4" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="557" spans="1:5">
@@ -84057,7 +84110,7 @@
       <c r="C557" s="2"/>
       <c r="D557" s="4"/>
       <c r="E557" s="4" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="558" spans="1:5">
@@ -84066,11 +84119,11 @@
       </c>
       <c r="B558" s="2"/>
       <c r="C558" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D558" s="4"/>
       <c r="E558" s="4" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="559" spans="1:5">
@@ -84081,7 +84134,7 @@
       <c r="C559" s="2"/>
       <c r="D559" s="4"/>
       <c r="E559" s="4" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="560" spans="1:5">
@@ -84092,7 +84145,7 @@
       <c r="C560" s="2"/>
       <c r="D560" s="4"/>
       <c r="E560" s="5" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="561" spans="1:5">
@@ -84103,7 +84156,7 @@
       <c r="C561" s="2"/>
       <c r="D561" s="4"/>
       <c r="E561" s="4" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="562" spans="1:5">
@@ -84114,7 +84167,7 @@
       <c r="C562" s="2"/>
       <c r="D562" s="4"/>
       <c r="E562" s="4" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="563" spans="1:5">
@@ -84136,7 +84189,7 @@
       <c r="C564" s="2"/>
       <c r="D564" s="4"/>
       <c r="E564" s="4" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="565" spans="1:5">
@@ -84158,7 +84211,7 @@
       <c r="C566" s="2"/>
       <c r="D566" s="4"/>
       <c r="E566" s="5" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="567" spans="1:5">
@@ -84169,7 +84222,7 @@
       <c r="C567" s="2"/>
       <c r="D567" s="4"/>
       <c r="E567" s="5" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="568" spans="1:5">
@@ -84180,7 +84233,7 @@
       <c r="C568" s="2"/>
       <c r="D568" s="4"/>
       <c r="E568" s="5" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="569" spans="1:5">
@@ -84191,7 +84244,7 @@
       <c r="C569" s="2"/>
       <c r="D569" s="4"/>
       <c r="E569" s="4" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="570" spans="1:5">
@@ -84202,7 +84255,7 @@
       <c r="C570" s="2"/>
       <c r="D570" s="4"/>
       <c r="E570" s="4" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="571" spans="1:5">
@@ -84213,7 +84266,7 @@
       <c r="C571" s="2"/>
       <c r="D571" s="4"/>
       <c r="E571" s="4" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="572" spans="1:5">
@@ -84222,11 +84275,11 @@
       </c>
       <c r="B572" s="2"/>
       <c r="C572" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D572" s="4"/>
       <c r="E572" s="4" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="573" spans="1:5">
@@ -84235,11 +84288,11 @@
       </c>
       <c r="B573" s="2"/>
       <c r="C573" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D573" s="4"/>
       <c r="E573" s="4" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="574" spans="1:5">
@@ -84248,11 +84301,11 @@
       </c>
       <c r="B574" s="2"/>
       <c r="C574" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D574" s="4"/>
       <c r="E574" s="4" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="575" spans="1:5">
@@ -84261,11 +84314,11 @@
       </c>
       <c r="B575" s="2"/>
       <c r="C575" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D575" s="4"/>
       <c r="E575" s="4" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="576" spans="1:5">
@@ -84274,11 +84327,11 @@
       </c>
       <c r="B576" s="2"/>
       <c r="C576" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D576" s="4"/>
       <c r="E576" s="5" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="577" spans="1:5">
@@ -84289,7 +84342,7 @@
       <c r="C577" s="2"/>
       <c r="D577" s="4"/>
       <c r="E577" s="4" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="578" spans="1:5">
@@ -84298,11 +84351,11 @@
       </c>
       <c r="B578" s="2"/>
       <c r="C578" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D578" s="4"/>
       <c r="E578" s="4" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="579" spans="1:5">
@@ -84311,11 +84364,11 @@
       </c>
       <c r="B579" s="2"/>
       <c r="C579" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D579" s="3"/>
       <c r="E579" s="7" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="580" spans="1:5">
@@ -84326,7 +84379,7 @@
       <c r="C580" s="2"/>
       <c r="D580" s="4"/>
       <c r="E580" s="5" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="581" spans="1:5">
@@ -84348,18 +84401,18 @@
       <c r="C582" s="2"/>
       <c r="D582" s="4"/>
       <c r="E582" s="5" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="583" spans="1:5">
       <c r="A583" s="2" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="B583" s="2"/>
       <c r="C583" s="2"/>
       <c r="D583" s="4"/>
       <c r="E583" s="5" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="584" spans="1:5">
@@ -84381,7 +84434,7 @@
       <c r="C585" s="2"/>
       <c r="D585" s="4"/>
       <c r="E585" s="5" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="586" spans="1:5">
@@ -84390,11 +84443,11 @@
       </c>
       <c r="B586" s="2"/>
       <c r="C586" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D586" s="4"/>
       <c r="E586" s="4" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="587" spans="1:5">
@@ -84403,11 +84456,11 @@
       </c>
       <c r="B587" s="2"/>
       <c r="C587" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D587" s="4"/>
       <c r="E587" s="4" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="588" spans="1:5">
@@ -84418,7 +84471,7 @@
       <c r="C588" s="2"/>
       <c r="D588" s="4"/>
       <c r="E588" s="5" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="589" spans="1:5">
@@ -84429,7 +84482,7 @@
       <c r="C589" s="2"/>
       <c r="D589" s="4"/>
       <c r="E589" s="4" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="590" spans="1:5">
@@ -84438,13 +84491,13 @@
       </c>
       <c r="B590" s="2"/>
       <c r="C590" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D590" s="7" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="E590" s="4" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="591" spans="1:5">
@@ -84455,7 +84508,7 @@
       <c r="C591" s="2"/>
       <c r="D591" s="4"/>
       <c r="E591" s="5" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="592" spans="1:5">
@@ -84477,7 +84530,7 @@
       <c r="C593" s="2"/>
       <c r="D593" s="4"/>
       <c r="E593" s="4" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="594" spans="1:5">
@@ -84488,7 +84541,7 @@
       <c r="C594" s="2"/>
       <c r="D594" s="4"/>
       <c r="E594" s="5" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="595" spans="1:5">
@@ -84498,23 +84551,23 @@
       <c r="B595" s="2"/>
       <c r="C595" s="2"/>
       <c r="D595" s="7" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="E595" s="4" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="596" spans="1:5">
       <c r="A596" s="2" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="B596" s="2"/>
       <c r="C596" s="2"/>
       <c r="D596" s="7" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="E596" s="7" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="597" spans="1:5">
@@ -84541,17 +84594,17 @@
     </row>
     <row r="599" spans="1:5">
       <c r="A599" s="2" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="B599" s="2"/>
       <c r="C599" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D599" s="7" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="E599" s="4" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="600" spans="1:5">
@@ -84560,13 +84613,13 @@
       </c>
       <c r="B600" s="2"/>
       <c r="C600" s="9" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="D600" s="7" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="E600" s="4" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="601" spans="1:5">
@@ -84577,7 +84630,7 @@
       <c r="C601" s="2"/>
       <c r="D601" s="4"/>
       <c r="E601" s="5" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="602" spans="1:5">
@@ -84586,24 +84639,24 @@
       </c>
       <c r="B602" s="2"/>
       <c r="C602" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D602" s="4"/>
       <c r="E602" s="4" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="603" spans="1:5">
       <c r="A603" s="2" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="B603" s="2"/>
       <c r="C603" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D603" s="4"/>
       <c r="E603" s="4" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="604" spans="1:5">
@@ -84614,7 +84667,7 @@
       <c r="C604" s="2"/>
       <c r="D604" s="4"/>
       <c r="E604" s="4" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="605" spans="1:5">
@@ -84625,7 +84678,7 @@
       <c r="C605" s="2"/>
       <c r="D605" s="4"/>
       <c r="E605" s="5" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="606" spans="1:5">
@@ -84636,7 +84689,7 @@
       <c r="C606" s="2"/>
       <c r="D606" s="4"/>
       <c r="E606" s="4" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="607" spans="1:5">
@@ -84645,11 +84698,11 @@
       </c>
       <c r="B607" s="2"/>
       <c r="C607" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D607" s="4"/>
       <c r="E607" s="4" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="608" spans="1:5">
@@ -84660,7 +84713,7 @@
       <c r="C608" s="2"/>
       <c r="D608" s="4"/>
       <c r="E608" s="4" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="609" spans="1:5">
@@ -84671,7 +84724,7 @@
       <c r="C609" s="2"/>
       <c r="D609" s="4"/>
       <c r="E609" s="4" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="610" spans="1:5">
@@ -84682,7 +84735,7 @@
       <c r="C610" s="2"/>
       <c r="D610" s="4"/>
       <c r="E610" s="4" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="611" spans="1:5">
@@ -84704,7 +84757,7 @@
       <c r="C612" s="2"/>
       <c r="D612" s="4"/>
       <c r="E612" s="5" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="613" spans="1:5">
@@ -84715,7 +84768,7 @@
       <c r="C613" s="2"/>
       <c r="D613" s="4"/>
       <c r="E613" s="4" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="614" spans="1:5">
@@ -84726,7 +84779,7 @@
       <c r="C614" s="2"/>
       <c r="D614" s="4"/>
       <c r="E614" s="5" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="615" spans="1:5">
@@ -84748,7 +84801,7 @@
       <c r="C616" s="2"/>
       <c r="D616" s="4"/>
       <c r="E616" s="4" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="617" spans="1:5">
@@ -84770,7 +84823,7 @@
       <c r="C618" s="2"/>
       <c r="D618" s="4"/>
       <c r="E618" s="4" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="619" spans="1:5">
@@ -84781,7 +84834,7 @@
       <c r="C619" s="2"/>
       <c r="D619" s="4"/>
       <c r="E619" s="5" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="620" spans="1:5">
@@ -84792,7 +84845,7 @@
       <c r="C620" s="2"/>
       <c r="D620" s="4"/>
       <c r="E620" s="5" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="621" spans="1:5">
@@ -84801,11 +84854,11 @@
       </c>
       <c r="B621" s="2"/>
       <c r="C621" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D621" s="4"/>
       <c r="E621" s="4" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="622" spans="1:5">
@@ -84825,11 +84878,11 @@
       </c>
       <c r="B623" s="2"/>
       <c r="C623" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D623" s="4"/>
       <c r="E623" s="4" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="624" spans="1:5">
@@ -84838,11 +84891,11 @@
       </c>
       <c r="B624" s="2"/>
       <c r="C624" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D624" s="4"/>
       <c r="E624" s="4" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="625" spans="1:5">
@@ -84853,7 +84906,7 @@
       <c r="C625" s="2"/>
       <c r="D625" s="4"/>
       <c r="E625" s="4" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="626" spans="1:5">
@@ -84862,11 +84915,11 @@
       </c>
       <c r="B626" s="2"/>
       <c r="C626" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D626" s="4"/>
       <c r="E626" s="5" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="627" spans="1:5">
@@ -84875,11 +84928,11 @@
       </c>
       <c r="B627" s="2"/>
       <c r="C627" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D627" s="4"/>
       <c r="E627" s="4" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="628" spans="1:5">
@@ -84888,11 +84941,11 @@
       </c>
       <c r="B628" s="2"/>
       <c r="C628" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D628" s="4"/>
       <c r="E628" s="7" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="629" spans="1:5">
@@ -84901,11 +84954,11 @@
       </c>
       <c r="B629" s="2"/>
       <c r="C629" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D629" s="4"/>
       <c r="E629" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="630" spans="1:5">
@@ -84916,7 +84969,7 @@
       <c r="C630" s="2"/>
       <c r="D630" s="4"/>
       <c r="E630" s="5" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="631" spans="1:5">
@@ -84927,7 +84980,7 @@
       <c r="C631" s="2"/>
       <c r="D631" s="4"/>
       <c r="E631" s="5" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="632" spans="1:5">
@@ -84949,7 +85002,7 @@
       <c r="C633" s="2"/>
       <c r="D633" s="4"/>
       <c r="E633" s="5" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="634" spans="1:5">
@@ -84960,7 +85013,7 @@
       <c r="C634" s="2"/>
       <c r="D634" s="4"/>
       <c r="E634" s="4" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="635" spans="1:5">
@@ -84971,7 +85024,7 @@
       <c r="C635" s="2"/>
       <c r="D635" s="4"/>
       <c r="E635" s="5" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="636" spans="1:5">
@@ -84982,7 +85035,7 @@
       <c r="C636" s="2"/>
       <c r="D636" s="4"/>
       <c r="E636" s="5" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="637" spans="1:5">
@@ -84991,11 +85044,11 @@
       </c>
       <c r="B637" s="2"/>
       <c r="C637" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D637" s="4"/>
       <c r="E637" s="4" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="638" spans="1:5">
@@ -85006,7 +85059,7 @@
       <c r="C638" s="2"/>
       <c r="D638" s="4"/>
       <c r="E638" s="5" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="639" spans="1:5">
@@ -85061,7 +85114,7 @@
       <c r="C643" s="2"/>
       <c r="D643" s="4"/>
       <c r="E643" s="5" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="644" spans="1:5">
@@ -85072,7 +85125,7 @@
       <c r="C644" s="2"/>
       <c r="D644" s="4"/>
       <c r="E644" s="4" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="645" spans="1:5">
@@ -85094,7 +85147,7 @@
       <c r="C646" s="2"/>
       <c r="D646" s="4"/>
       <c r="E646" s="4" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="647" spans="1:5">
@@ -85127,7 +85180,7 @@
       <c r="C649" s="2"/>
       <c r="D649" s="4"/>
       <c r="E649" s="4" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="650" spans="1:5">
@@ -85182,7 +85235,7 @@
       <c r="C654" s="2"/>
       <c r="D654" s="4"/>
       <c r="E654" s="5" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="655" spans="1:5">
@@ -85204,7 +85257,7 @@
       <c r="C656" s="2"/>
       <c r="D656" s="4"/>
       <c r="E656" s="4" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="657" spans="1:5">
@@ -85215,7 +85268,7 @@
       <c r="C657" s="2"/>
       <c r="D657" s="4"/>
       <c r="E657" s="4" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="658" spans="1:5">
@@ -85226,7 +85279,7 @@
       <c r="C658" s="2"/>
       <c r="D658" s="4"/>
       <c r="E658" s="5" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="659" spans="1:5">
@@ -85237,7 +85290,7 @@
       <c r="C659" s="2"/>
       <c r="D659" s="4"/>
       <c r="E659" s="4" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="660" spans="1:5">
@@ -85259,7 +85312,7 @@
       <c r="C661" s="2"/>
       <c r="D661" s="4"/>
       <c r="E661" s="5" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="662" spans="1:5">
@@ -85270,7 +85323,7 @@
       <c r="C662" s="2"/>
       <c r="D662" s="4"/>
       <c r="E662" s="4" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="663" spans="1:5">
@@ -85281,7 +85334,7 @@
       <c r="C663" s="2"/>
       <c r="D663" s="4"/>
       <c r="E663" s="4" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="664" spans="1:5">
@@ -85292,7 +85345,7 @@
       <c r="C664" s="2"/>
       <c r="D664" s="4"/>
       <c r="E664" s="4" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="665" spans="1:5">
@@ -85303,7 +85356,7 @@
       <c r="C665" s="2"/>
       <c r="D665" s="4"/>
       <c r="E665" s="4" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="666" spans="1:5">
@@ -85314,7 +85367,7 @@
       <c r="C666" s="2"/>
       <c r="D666" s="4"/>
       <c r="E666" s="4" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="667" spans="1:5">
@@ -85325,7 +85378,7 @@
       <c r="C667" s="2"/>
       <c r="D667" s="4"/>
       <c r="E667" s="5" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="668" spans="1:5">
@@ -85336,7 +85389,7 @@
       <c r="C668" s="2"/>
       <c r="D668" s="4"/>
       <c r="E668" s="4" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="669" spans="1:5">
@@ -85347,7 +85400,7 @@
       <c r="C669" s="2"/>
       <c r="D669" s="4"/>
       <c r="E669" s="4" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="670" spans="1:5">
@@ -85356,11 +85409,11 @@
       </c>
       <c r="B670" s="2"/>
       <c r="C670" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D670" s="4"/>
       <c r="E670" s="4" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="671" spans="1:5">
@@ -85370,10 +85423,10 @@
       <c r="B671" s="2"/>
       <c r="C671" s="2"/>
       <c r="D671" s="7" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="E671" s="7" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="672" spans="1:5">
@@ -85384,7 +85437,7 @@
       <c r="C672" s="2"/>
       <c r="D672" s="4"/>
       <c r="E672" s="5" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="673" spans="1:5">
@@ -85406,7 +85459,7 @@
       <c r="C674" s="2"/>
       <c r="D674" s="4"/>
       <c r="E674" s="4" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="675" spans="1:5">
@@ -85435,7 +85488,7 @@
       <c r="C677" s="2"/>
       <c r="D677" s="4"/>
       <c r="E677" s="4" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="678" spans="1:5">
@@ -85444,11 +85497,11 @@
       </c>
       <c r="B678" s="2"/>
       <c r="C678" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D678" s="4"/>
       <c r="E678" s="4" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="679" spans="1:5">
@@ -85459,7 +85512,7 @@
       <c r="C679" s="2"/>
       <c r="D679" s="4"/>
       <c r="E679" s="4" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="680" spans="1:5">
@@ -85468,11 +85521,11 @@
       </c>
       <c r="B680" s="2"/>
       <c r="C680" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D680" s="4"/>
       <c r="E680" s="4" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="681" spans="1:5">
@@ -85481,11 +85534,11 @@
       </c>
       <c r="B681" s="2"/>
       <c r="C681" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D681" s="4"/>
       <c r="E681" s="4" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="682" spans="1:5">
@@ -85507,7 +85560,7 @@
       <c r="C683" s="2"/>
       <c r="D683" s="4"/>
       <c r="E683" s="5" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="684" spans="1:5">
@@ -85518,20 +85571,20 @@
       <c r="C684" s="2"/>
       <c r="D684" s="4"/>
       <c r="E684" s="5" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="685" spans="1:5">
       <c r="A685" s="2" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="B685" s="2"/>
       <c r="C685" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D685" s="4"/>
       <c r="E685" s="4" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="686" spans="1:5">
@@ -85540,11 +85593,11 @@
       </c>
       <c r="B686" s="2"/>
       <c r="C686" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D686" s="4"/>
       <c r="E686" s="4" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="687" spans="1:5">
@@ -85553,11 +85606,11 @@
       </c>
       <c r="B687" s="2"/>
       <c r="C687" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D687" s="4"/>
       <c r="E687" s="5" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="688" spans="1:5">
@@ -85568,7 +85621,7 @@
       <c r="C688" s="2"/>
       <c r="D688" s="4"/>
       <c r="E688" s="4" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="689" spans="1:5">
@@ -85590,7 +85643,7 @@
       <c r="C690" s="2"/>
       <c r="D690" s="4"/>
       <c r="E690" s="4" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="691" spans="1:5">
@@ -85599,11 +85652,11 @@
       </c>
       <c r="B691" s="2"/>
       <c r="C691" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D691" s="3"/>
       <c r="E691" s="4" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="692" spans="1:5">
@@ -85612,11 +85665,11 @@
       </c>
       <c r="B692" s="2"/>
       <c r="C692" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D692" s="4"/>
       <c r="E692" s="4" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="693" spans="1:5">
@@ -85625,11 +85678,11 @@
       </c>
       <c r="B693" s="2"/>
       <c r="C693" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D693" s="4"/>
       <c r="E693" s="4" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="694" spans="1:5">
@@ -85640,7 +85693,7 @@
       <c r="C694" s="2"/>
       <c r="D694" s="4"/>
       <c r="E694" s="4" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="695" spans="1:5">
@@ -85649,11 +85702,11 @@
       </c>
       <c r="B695" s="2"/>
       <c r="C695" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D695" s="4"/>
       <c r="E695" s="4" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="696" spans="1:5">
@@ -85686,7 +85739,7 @@
       <c r="C698" s="2"/>
       <c r="D698" s="4"/>
       <c r="E698" s="4" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="699" spans="1:5">
@@ -85697,7 +85750,7 @@
       <c r="C699" s="2"/>
       <c r="D699" s="3"/>
       <c r="E699" s="4" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="700" spans="1:5">
@@ -85708,7 +85761,7 @@
       <c r="C700" s="2"/>
       <c r="D700" s="4"/>
       <c r="E700" s="4" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="701" spans="1:5">
@@ -85721,7 +85774,7 @@
         <v>971</v>
       </c>
       <c r="E701" s="4" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="702" spans="1:5">
@@ -85741,11 +85794,11 @@
       </c>
       <c r="B703" s="2"/>
       <c r="C703" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D703" s="4"/>
       <c r="E703" s="5" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="704" spans="1:5">
@@ -85755,21 +85808,21 @@
       <c r="B704" s="2"/>
       <c r="C704" s="2"/>
       <c r="D704" s="7" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="E704" s="7" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="705" spans="1:5">
       <c r="A705" s="2" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="B705" s="2"/>
       <c r="C705" s="2"/>
       <c r="D705" s="4"/>
       <c r="E705" s="4" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="706" spans="1:5">
@@ -85780,7 +85833,7 @@
       <c r="C706" s="2"/>
       <c r="D706" s="4"/>
       <c r="E706" s="4" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="707" spans="1:5">
@@ -85791,7 +85844,7 @@
       <c r="C707" s="2"/>
       <c r="D707" s="4"/>
       <c r="E707" s="4" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="708" spans="1:5">
@@ -85802,7 +85855,7 @@
       <c r="C708" s="2"/>
       <c r="D708" s="4"/>
       <c r="E708" s="4" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="709" spans="1:5">
@@ -85813,7 +85866,7 @@
       <c r="C709" s="2"/>
       <c r="D709" s="4"/>
       <c r="E709" s="4" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="710" spans="1:5">
@@ -85824,7 +85877,7 @@
       <c r="C710" s="2"/>
       <c r="D710" s="4"/>
       <c r="E710" s="4" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="711" spans="1:5">
@@ -85833,11 +85886,11 @@
       </c>
       <c r="B711" s="2"/>
       <c r="C711" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D711" s="4"/>
       <c r="E711" s="4" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="712" spans="1:5">
@@ -85846,11 +85899,11 @@
       </c>
       <c r="B712" s="2"/>
       <c r="C712" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D712" s="4"/>
       <c r="E712" s="4" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="713" spans="1:5">
@@ -85859,11 +85912,11 @@
       </c>
       <c r="B713" s="2"/>
       <c r="C713" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D713" s="4"/>
       <c r="E713" s="5" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="714" spans="1:5">
@@ -85873,10 +85926,10 @@
       <c r="B714" s="2"/>
       <c r="C714" s="2"/>
       <c r="D714" s="7" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="E714" s="7" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="715" spans="1:5">
@@ -85887,7 +85940,7 @@
       <c r="C715" s="2"/>
       <c r="D715" s="4"/>
       <c r="E715" s="4" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="716" spans="1:5">
@@ -85898,7 +85951,7 @@
       <c r="C716" s="2"/>
       <c r="D716" s="4"/>
       <c r="E716" s="5" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="717" spans="1:5">
@@ -85909,7 +85962,7 @@
       <c r="C717" s="2"/>
       <c r="D717" s="4"/>
       <c r="E717" s="5" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="718" spans="1:5">
@@ -85920,7 +85973,7 @@
       <c r="C718" s="2"/>
       <c r="D718" s="4"/>
       <c r="E718" s="5" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="719" spans="1:5">
@@ -85931,18 +85984,18 @@
       <c r="C719" s="2"/>
       <c r="D719" s="4"/>
       <c r="E719" s="4" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="720" spans="1:5">
       <c r="A720" s="2" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B720" s="2"/>
       <c r="C720" s="2"/>
       <c r="D720" s="4"/>
       <c r="E720" s="5" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="721" spans="1:5">
@@ -85953,7 +86006,7 @@
       <c r="C721" s="2"/>
       <c r="D721" s="4"/>
       <c r="E721" s="4" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="722" spans="1:5">
@@ -85964,7 +86017,7 @@
       <c r="C722" s="2"/>
       <c r="D722" s="4"/>
       <c r="E722" s="4" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="723" spans="1:5">
@@ -85975,7 +86028,7 @@
       <c r="C723" s="2"/>
       <c r="D723" s="4"/>
       <c r="E723" s="4" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="724" spans="1:5">
@@ -85986,7 +86039,7 @@
       <c r="C724" s="2"/>
       <c r="D724" s="4"/>
       <c r="E724" s="4" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="725" spans="1:5">
@@ -85997,7 +86050,7 @@
       <c r="C725" s="2"/>
       <c r="D725" s="4"/>
       <c r="E725" s="5" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="726" spans="1:5">
@@ -86006,11 +86059,11 @@
       </c>
       <c r="B726" s="2"/>
       <c r="C726" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D726" s="4"/>
       <c r="E726" s="5" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="727" spans="1:5">
@@ -86019,11 +86072,11 @@
       </c>
       <c r="B727" s="2"/>
       <c r="C727" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D727" s="4"/>
       <c r="E727" s="4" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="728" spans="1:5">
@@ -86032,11 +86085,11 @@
       </c>
       <c r="B728" s="2"/>
       <c r="C728" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D728" s="3"/>
       <c r="E728" s="4" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="729" spans="1:5">
@@ -86045,11 +86098,11 @@
       </c>
       <c r="B729" s="2"/>
       <c r="C729" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D729" s="4"/>
       <c r="E729" s="4" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="730" spans="1:5">
@@ -86058,11 +86111,11 @@
       </c>
       <c r="B730" s="2"/>
       <c r="C730" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D730" s="4"/>
       <c r="E730" s="4" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="731" spans="1:5">
@@ -86084,7 +86137,7 @@
       <c r="C732" s="2"/>
       <c r="D732" s="4"/>
       <c r="E732" s="5" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="733" spans="1:5">
@@ -86095,7 +86148,7 @@
       <c r="C733" s="2"/>
       <c r="D733" s="4"/>
       <c r="E733" s="5" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="734" spans="1:5">
@@ -86106,7 +86159,7 @@
       <c r="C734" s="2"/>
       <c r="D734" s="4"/>
       <c r="E734" s="5" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="735" spans="1:5">
@@ -86117,7 +86170,7 @@
       <c r="C735" s="2"/>
       <c r="D735" s="4"/>
       <c r="E735" s="5" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="736" spans="1:5">
@@ -86128,7 +86181,7 @@
       <c r="C736" s="2"/>
       <c r="D736" s="4"/>
       <c r="E736" s="4" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="737" spans="1:5">
@@ -86137,11 +86190,11 @@
       </c>
       <c r="B737" s="2"/>
       <c r="C737" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D737" s="4"/>
       <c r="E737" s="4" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="738" spans="1:5">
@@ -86152,7 +86205,7 @@
       <c r="C738" s="2"/>
       <c r="D738" s="4"/>
       <c r="E738" s="5" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="739" spans="1:5">
@@ -86161,11 +86214,11 @@
       </c>
       <c r="B739" s="2"/>
       <c r="C739" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D739" s="4"/>
       <c r="E739" s="4" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="740" spans="1:5">
@@ -86176,7 +86229,7 @@
       <c r="C740" s="2"/>
       <c r="D740" s="4"/>
       <c r="E740" s="4" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="741" spans="1:5">
@@ -86187,7 +86240,7 @@
       <c r="C741" s="2"/>
       <c r="D741" s="4"/>
       <c r="E741" s="5" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="742" spans="1:5">
@@ -86209,7 +86262,7 @@
       <c r="C743" s="2"/>
       <c r="D743" s="4"/>
       <c r="E743" s="4" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="744" spans="1:5">
@@ -86220,7 +86273,7 @@
       <c r="C744" s="2"/>
       <c r="D744" s="4"/>
       <c r="E744" s="5" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="745" spans="1:5">
@@ -86230,10 +86283,10 @@
       <c r="B745" s="2"/>
       <c r="C745" s="2"/>
       <c r="D745" s="7" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="E745" s="7" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="746" spans="1:5">
@@ -86244,7 +86297,7 @@
       <c r="C746" s="2"/>
       <c r="D746" s="4"/>
       <c r="E746" s="5" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="747" spans="1:5">
@@ -86255,7 +86308,7 @@
       <c r="C747" s="2"/>
       <c r="D747" s="4"/>
       <c r="E747" s="4" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="748" spans="1:5">
@@ -86266,7 +86319,7 @@
       <c r="C748" s="2"/>
       <c r="D748" s="4"/>
       <c r="E748" s="4" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="749" spans="1:5">
@@ -86277,7 +86330,7 @@
       <c r="C749" s="2"/>
       <c r="D749" s="4"/>
       <c r="E749" s="4" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="750" spans="1:5">
@@ -86288,7 +86341,7 @@
       <c r="C750" s="2"/>
       <c r="D750" s="4"/>
       <c r="E750" s="5" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="751" spans="1:5">
@@ -86299,18 +86352,18 @@
       <c r="C751" s="2"/>
       <c r="D751" s="4"/>
       <c r="E751" s="5" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="752" spans="1:5">
       <c r="A752" s="2" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="B752" s="2"/>
       <c r="C752" s="2"/>
       <c r="D752" s="4"/>
       <c r="E752" s="5" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="753" spans="1:5">
@@ -86321,7 +86374,7 @@
       <c r="C753" s="2"/>
       <c r="D753" s="4"/>
       <c r="E753" s="5" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="754" spans="1:5">
@@ -86332,7 +86385,7 @@
       <c r="C754" s="2"/>
       <c r="D754" s="4"/>
       <c r="E754" s="4" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="755" spans="1:5">
@@ -86352,11 +86405,11 @@
       </c>
       <c r="B756" s="2"/>
       <c r="C756" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D756" s="4"/>
       <c r="E756" s="4" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="757" spans="1:5">
@@ -86365,11 +86418,11 @@
       </c>
       <c r="B757" s="2"/>
       <c r="C757" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D757" s="4"/>
       <c r="E757" s="4" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="758" spans="1:5">
@@ -86380,7 +86433,7 @@
       <c r="C758" s="2"/>
       <c r="D758" s="4"/>
       <c r="E758" s="4" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="759" spans="1:5">
@@ -86389,11 +86442,11 @@
       </c>
       <c r="B759" s="2"/>
       <c r="C759" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D759" s="4"/>
       <c r="E759" s="4" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="760" spans="1:5">
@@ -86404,20 +86457,20 @@
       <c r="C760" s="2"/>
       <c r="D760" s="4"/>
       <c r="E760" s="5" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="761" spans="1:5">
       <c r="A761" s="2" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="B761" s="2"/>
       <c r="C761" s="2"/>
       <c r="D761" s="7" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="E761" s="4" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="762" spans="1:5">
@@ -86428,7 +86481,7 @@
       <c r="C762" s="2"/>
       <c r="D762" s="4"/>
       <c r="E762" s="5" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="763" spans="1:5">
@@ -86437,11 +86490,11 @@
       </c>
       <c r="B763" s="2"/>
       <c r="C763" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D763" s="4"/>
       <c r="E763" s="4" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="764" spans="1:5">
@@ -86450,11 +86503,11 @@
       </c>
       <c r="B764" s="2"/>
       <c r="C764" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D764" s="4"/>
       <c r="E764" s="4" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="765" spans="1:5">
@@ -86465,7 +86518,7 @@
       <c r="C765" s="2"/>
       <c r="D765" s="4"/>
       <c r="E765" s="5" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="766" spans="1:5">
@@ -86476,7 +86529,7 @@
       <c r="C766" s="2"/>
       <c r="D766" s="4"/>
       <c r="E766" s="4" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="767" spans="1:5">
@@ -86487,7 +86540,7 @@
       <c r="C767" s="2"/>
       <c r="D767" s="4"/>
       <c r="E767" s="5" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="768" spans="1:5">
@@ -86527,11 +86580,11 @@
       </c>
       <c r="B771" s="2"/>
       <c r="C771" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D771" s="4"/>
       <c r="E771" s="4" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="772" spans="1:5">
@@ -86542,7 +86595,7 @@
       <c r="C772" s="2"/>
       <c r="D772" s="4"/>
       <c r="E772" s="5" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="773" spans="1:5">
@@ -86553,7 +86606,7 @@
       <c r="C773" s="2"/>
       <c r="D773" s="4"/>
       <c r="E773" s="4" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="774" spans="1:5">
@@ -86586,7 +86639,7 @@
       <c r="C776" s="2"/>
       <c r="D776" s="4"/>
       <c r="E776" s="4" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="777" spans="1:5">
@@ -86597,7 +86650,7 @@
       <c r="C777" s="2"/>
       <c r="D777" s="4"/>
       <c r="E777" s="4" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="778" spans="1:5">
@@ -86608,7 +86661,7 @@
       <c r="C778" s="2"/>
       <c r="D778" s="4"/>
       <c r="E778" s="4" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="779" spans="1:5">
@@ -86619,7 +86672,7 @@
       <c r="C779" s="2"/>
       <c r="D779" s="4"/>
       <c r="E779" s="4" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="780" spans="1:5">
@@ -86628,11 +86681,11 @@
       </c>
       <c r="B780" s="2"/>
       <c r="C780" s="9" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="D780" s="4"/>
       <c r="E780" s="4" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="781" spans="1:5">
@@ -86643,7 +86696,7 @@
       <c r="C781" s="2"/>
       <c r="D781" s="4"/>
       <c r="E781" s="4" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="782" spans="1:5">
@@ -86652,11 +86705,11 @@
       </c>
       <c r="B782" s="2"/>
       <c r="C782" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D782" s="3"/>
       <c r="E782" s="4" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="783" spans="1:5">
@@ -86665,13 +86718,13 @@
       </c>
       <c r="B783" s="2"/>
       <c r="C783" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D783" s="7" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="E783" s="7" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="784" spans="1:5">
@@ -86682,7 +86735,7 @@
       <c r="C784" s="2"/>
       <c r="D784" s="4"/>
       <c r="E784" s="4" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="785" spans="1:5">
@@ -86693,7 +86746,7 @@
       <c r="C785" s="2"/>
       <c r="D785" s="4"/>
       <c r="E785" s="4" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="786" spans="1:5">
@@ -86713,7 +86766,7 @@
       </c>
       <c r="B787" s="2"/>
       <c r="C787" s="9" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="D787" s="4"/>
       <c r="E787" s="4" t="s">
@@ -86726,7 +86779,7 @@
       </c>
       <c r="B788" s="2"/>
       <c r="C788" s="9" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="D788" s="4"/>
       <c r="E788" s="5" t="s">
@@ -86739,7 +86792,7 @@
       </c>
       <c r="B789" s="2"/>
       <c r="C789" s="9" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="D789" s="4"/>
       <c r="E789" s="4"/>
@@ -86750,11 +86803,11 @@
       </c>
       <c r="B790" s="2"/>
       <c r="C790" s="9" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="D790" s="4"/>
       <c r="E790" s="4" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="791" spans="1:5">
@@ -86763,11 +86816,11 @@
       </c>
       <c r="B791" s="2"/>
       <c r="C791" s="9" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="D791" s="4"/>
       <c r="E791" s="4" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="792" spans="1:5">
@@ -86776,11 +86829,11 @@
       </c>
       <c r="B792" s="2"/>
       <c r="C792" s="9" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="D792" s="4"/>
       <c r="E792" s="4" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="793" spans="1:5">
@@ -86813,7 +86866,7 @@
       <c r="C795" s="2"/>
       <c r="D795" s="4"/>
       <c r="E795" s="4" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="796" spans="1:5">
@@ -86824,12 +86877,12 @@
       <c r="C796" s="2"/>
       <c r="D796" s="4"/>
       <c r="E796" s="4" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="797" spans="1:5">
       <c r="A797" s="2" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="B797" s="2"/>
       <c r="C797" s="2"/>
@@ -86846,7 +86899,7 @@
       <c r="C798" s="2"/>
       <c r="D798" s="4"/>
       <c r="E798" s="4" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="799" spans="1:5">
@@ -86855,11 +86908,11 @@
       </c>
       <c r="B799" s="2"/>
       <c r="C799" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D799" s="4"/>
       <c r="E799" s="4" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="800" spans="1:5">
@@ -86868,11 +86921,11 @@
       </c>
       <c r="B800" s="2"/>
       <c r="C800" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D800" s="4"/>
       <c r="E800" s="5" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="801" spans="1:5">
@@ -86881,13 +86934,13 @@
       </c>
       <c r="B801" s="2"/>
       <c r="C801" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D801" s="3" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="E801" s="7" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="802" spans="1:5">
@@ -86898,7 +86951,7 @@
       <c r="C802" s="2"/>
       <c r="D802" s="4"/>
       <c r="E802" s="4" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="803" spans="1:5">
@@ -86909,7 +86962,7 @@
       <c r="C803" s="2"/>
       <c r="D803" s="4"/>
       <c r="E803" s="5" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="804" spans="1:5">
@@ -86920,7 +86973,7 @@
       <c r="C804" s="2"/>
       <c r="D804" s="4"/>
       <c r="E804" s="4" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="805" spans="1:5">
@@ -86931,7 +86984,7 @@
       <c r="C805" s="2"/>
       <c r="D805" s="4"/>
       <c r="E805" s="5" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="806" spans="1:5">
@@ -86942,7 +86995,7 @@
       <c r="C806" s="2"/>
       <c r="D806" s="4"/>
       <c r="E806" s="4" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="807" spans="1:5">
@@ -86953,7 +87006,7 @@
       <c r="C807" s="2"/>
       <c r="D807" s="4"/>
       <c r="E807" s="4" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="808" spans="1:5">
@@ -86962,11 +87015,11 @@
       </c>
       <c r="B808" s="2"/>
       <c r="C808" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D808" s="4"/>
       <c r="E808" s="5" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="809" spans="1:5">
@@ -86984,11 +87037,11 @@
       </c>
       <c r="B810" s="2"/>
       <c r="C810" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D810" s="4"/>
       <c r="E810" s="5" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="811" spans="1:5">
@@ -86999,7 +87052,7 @@
       <c r="C811" s="2"/>
       <c r="D811" s="4"/>
       <c r="E811" s="4" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="812" spans="1:5">
@@ -87010,7 +87063,7 @@
       <c r="C812" s="2"/>
       <c r="D812" s="4"/>
       <c r="E812" s="5" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="813" spans="1:5">
@@ -87021,7 +87074,7 @@
       <c r="C813" s="2"/>
       <c r="D813" s="4"/>
       <c r="E813" s="4" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="814" spans="1:5">
@@ -87032,7 +87085,7 @@
       <c r="C814" s="2"/>
       <c r="D814" s="4"/>
       <c r="E814" s="5" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="815" spans="1:5">
@@ -87054,7 +87107,7 @@
       <c r="C816" s="2"/>
       <c r="D816" s="4"/>
       <c r="E816" s="4" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="817" spans="1:5">
@@ -87065,7 +87118,7 @@
       <c r="C817" s="2"/>
       <c r="D817" s="4"/>
       <c r="E817" s="4" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="818" spans="1:5">
@@ -87076,7 +87129,7 @@
       <c r="C818" s="2"/>
       <c r="D818" s="4"/>
       <c r="E818" s="5" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="819" spans="1:5">
@@ -87107,7 +87160,7 @@
       <c r="C821" s="2"/>
       <c r="D821" s="4"/>
       <c r="E821" s="4" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="822" spans="1:5">
@@ -87138,7 +87191,7 @@
       <c r="C824" s="2"/>
       <c r="D824" s="3"/>
       <c r="E824" s="4" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="825" spans="1:5">
@@ -87149,7 +87202,7 @@
       <c r="C825" s="2"/>
       <c r="D825" s="4"/>
       <c r="E825" s="4" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="826" spans="1:5">
@@ -87160,18 +87213,18 @@
       <c r="C826" s="2"/>
       <c r="D826" s="4"/>
       <c r="E826" s="4" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="827" spans="1:5">
       <c r="A827" s="8" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="B827" s="8"/>
       <c r="C827" s="8"/>
       <c r="D827" s="4"/>
       <c r="E827" s="7" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="828" spans="1:5">
@@ -87182,7 +87235,7 @@
       <c r="C828" s="8"/>
       <c r="D828" s="4"/>
       <c r="E828" s="5" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="829" spans="1:5">
@@ -87193,7 +87246,7 @@
       <c r="C829" s="8"/>
       <c r="D829" s="4"/>
       <c r="E829" s="5" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="830" spans="1:5">
@@ -87204,7 +87257,7 @@
       <c r="C830" s="8"/>
       <c r="D830" s="4"/>
       <c r="E830" s="5" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="831" spans="1:5">
@@ -87220,35 +87273,35 @@
     </row>
     <row r="832" spans="1:5">
       <c r="A832" s="8" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="B832" s="8"/>
       <c r="C832" s="8"/>
       <c r="D832" s="4"/>
       <c r="E832" s="4" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="833" spans="1:5">
       <c r="A833" s="8" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="B833" s="8"/>
       <c r="C833" s="8"/>
       <c r="D833" s="4"/>
       <c r="E833" s="4" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="834" spans="1:5">
       <c r="A834" s="8" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="B834" s="8"/>
       <c r="C834" s="8"/>
       <c r="D834" s="4"/>
       <c r="E834" s="4" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="835" spans="1:5">
@@ -87270,7 +87323,7 @@
       <c r="C836" s="8"/>
       <c r="D836" s="4"/>
       <c r="E836" s="5" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="837" spans="1:5">
@@ -87281,7 +87334,7 @@
       <c r="C837" s="8"/>
       <c r="D837" s="4"/>
       <c r="E837" s="4" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="838" spans="1:5">
@@ -87301,7 +87354,7 @@
       <c r="C839" s="8"/>
       <c r="D839" s="4"/>
       <c r="E839" s="4" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="840" spans="1:5">
@@ -87326,41 +87379,41 @@
     </row>
     <row r="842" spans="1:5">
       <c r="A842" s="7" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="B842" s="7"/>
       <c r="C842" s="7"/>
       <c r="D842" s="4"/>
       <c r="E842" s="7" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="843" spans="1:5">
       <c r="A843" s="1" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
       <c r="D843" s="1" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="E843" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="844" spans="1:5" ht="34">
       <c r="A844" s="11" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="B844" s="1"/>
       <c r="C844" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D844" s="7" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="E844" s="12" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="845" spans="1:5">
@@ -91336,6 +91389,7 @@
     <hyperlink ref="D844" r:id="rId80" xr:uid="{960EBD0F-E7EB-3946-8641-5C2574B22DD0}"/>
     <hyperlink ref="D600" r:id="rId81" xr:uid="{7834929F-4A95-3640-820D-B43D5F76391A}"/>
     <hyperlink ref="D599" r:id="rId82" display="https://hurzlmeier-rudi.de/" xr:uid="{58E365A7-80D7-A442-A85B-EDD369F3F970}"/>
+    <hyperlink ref="D178" r:id="rId83" xr:uid="{7E8C2DE0-9448-4441-8298-7F9D0729927B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/config/brand_info_config.xlsx
+++ b/config/brand_info_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wushan/models/SLBR-Visible-Watermark-Removal/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E354C3-D5D2-B742-9DBA-6C6A71753EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1043A03E-EA03-D346-A3B3-AF116F719379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{1B5E55EE-582A-EF4F-97A0-18A8C46CF48F}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2779" uniqueCount="1726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2779" uniqueCount="1727">
   <si>
     <t>Steel City Enterprises, Inc.</t>
   </si>
@@ -5465,6 +5465,10 @@
   </si>
   <si>
     <t>Richemont International</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rumored</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -14057,7 +14061,7 @@
     </row>
     <row r="568" spans="1:8">
       <c r="A568" s="11" t="s">
-        <v>107</v>
+        <v>1726</v>
       </c>
       <c r="B568" s="11"/>
       <c r="C568" s="11" t="s">

--- a/config/brand_info_config.xlsx
+++ b/config/brand_info_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wushan/models/SLBR-Visible-Watermark-Removal/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1043A03E-EA03-D346-A3B3-AF116F719379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0846572-9C0A-614D-89AF-10A1E1FDC540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{1B5E55EE-582A-EF4F-97A0-18A8C46CF48F}"/>
   </bookViews>

--- a/config/brand_info_config.xlsx
+++ b/config/brand_info_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wushan/models/SLBR-Visible-Watermark-Removal/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3838974D-5208-4741-88CA-0ABC37BBC355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC03145-C942-DD4A-9681-8E7888925460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{1B5E55EE-582A-EF4F-97A0-18A8C46CF48F}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2784" uniqueCount="1832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2788" uniqueCount="1836">
   <si>
     <t>Steel City Enterprises, Inc.</t>
   </si>
@@ -5926,12 +5926,68 @@
   <si>
     <t>圣诞精灵</t>
   </si>
+  <si>
+    <t>Cupshe</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>女装品牌</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cupshe </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是一个专注于女性泳装与度假服饰的时尚品牌，成立于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2015 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，总部位于美国加利福尼亚州。品牌主要面向年轻女性消费者，产品涵盖比基尼、连体泳衣、沙滩裙及度假服装等，设计风格以时尚、舒适和高性价比为特点。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> https://www.cupshe.com/
+</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.cupshe.com</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -6047,6 +6103,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="SimSun"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -6088,7 +6151,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6130,6 +6193,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -17348,12 +17414,20 @@
       <c r="G762" s="2"/>
       <c r="H762" s="2"/>
     </row>
-    <row r="763" spans="1:8">
-      <c r="A763" s="2"/>
+    <row r="763" spans="1:8" ht="45">
+      <c r="A763" s="2" t="s">
+        <v>1832</v>
+      </c>
       <c r="B763" s="2"/>
-      <c r="C763" s="2"/>
-      <c r="D763" s="4"/>
-      <c r="E763" s="4"/>
+      <c r="C763" s="8" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D763" s="6" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E763" s="16" t="s">
+        <v>1834</v>
+      </c>
       <c r="G763" s="2"/>
       <c r="H763" s="2"/>
     </row>
@@ -21503,6 +21577,7 @@
     <hyperlink ref="D727" r:id="rId38" xr:uid="{7447B0AA-4CFE-464F-AC40-4B40F32BB333}"/>
     <hyperlink ref="D65" r:id="rId39" xr:uid="{E562C7D0-87ED-5F4D-968F-8D948D28202C}"/>
     <hyperlink ref="D93" r:id="rId40" display="https://www.burberry.com/" xr:uid="{5B9D5595-7820-7C4F-9B99-6EA304B25C4A}"/>
+    <hyperlink ref="D763" r:id="rId41" display="https://www.cupshe.com/" xr:uid="{F9D58158-B11C-3041-9573-3C2DC455F89F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/config/brand_info_config.xlsx
+++ b/config/brand_info_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wushan/models/SLBR-Visible-Watermark-Removal/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC03145-C942-DD4A-9681-8E7888925460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4693CEB1-D1F6-4442-AE6D-D82555B011E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{1B5E55EE-582A-EF4F-97A0-18A8C46CF48F}"/>
   </bookViews>

--- a/config/brand_info_config.xlsx
+++ b/config/brand_info_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wushan/models/SLBR-Visible-Watermark-Removal/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4693CEB1-D1F6-4442-AE6D-D82555B011E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA15E583-A1D1-614A-AFA8-AC07D4C10FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{1B5E55EE-582A-EF4F-97A0-18A8C46CF48F}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2788" uniqueCount="1836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2788" uniqueCount="1837">
   <si>
     <t>Steel City Enterprises, Inc.</t>
   </si>
@@ -5981,6 +5981,10 @@
   </si>
   <si>
     <t>https://www.cupshe.com</t>
+  </si>
+  <si>
+    <t>Rubie`s Costume Company</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -14430,7 +14434,7 @@
     </row>
     <row r="549" spans="1:8">
       <c r="A549" s="11" t="s">
-        <v>178</v>
+        <v>1836</v>
       </c>
       <c r="B549" s="11"/>
       <c r="C549" s="11"/>

--- a/config/brand_info_config.xlsx
+++ b/config/brand_info_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wushan/models/SLBR-Visible-Watermark-Removal/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA15E583-A1D1-614A-AFA8-AC07D4C10FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6CFA13-7C8E-2942-9787-06D8510E9D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{1B5E55EE-582A-EF4F-97A0-18A8C46CF48F}"/>
   </bookViews>
@@ -2685,9 +2685,6 @@
   </si>
   <si>
     <t>https://www.royerbrands.com</t>
-  </si>
-  <si>
-    <t>Rubie's Costume Company是全球知名的-costume manufacturer和distributor，总部位于美国加利福尼亚州。公司成立于1951年，始终专注于设计、生产和销售为人士、家庭和企业提供的各种 costumes和accessories。Rubie's Costume Company拥有数万种不同的costume产品，包括 Halloween costumes、theatrical costumes、corporate costumes和party costumes等。公司的产品遍及全球，受到广泛的好评和欢迎。</t>
   </si>
   <si>
     <t>😊
@@ -5984,6 +5981,10 @@
   </si>
   <si>
     <t>Rubie`s Costume Company</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rubie`s Costume Company是全球知名的-costume manufacturer和distributor，总部位于美国加利福尼亚州。公司成立于1951年，始终专注于设计、生产和销售为人士、家庭和企业提供的各种 costumes和accessories。Rubie`s Costume Company拥有数万种不同的costume产品，包括 Halloween costumes、theatrical costumes、corporate costumes和party costumes等。公司的产品遍及全球，受到广泛的好评和欢迎。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6553,16 +6554,16 @@
         <v>694</v>
       </c>
       <c r="B1" s="12" t="s">
+        <v>911</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>912</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>913</v>
       </c>
       <c r="D1" s="12" t="s">
         <v>742</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -6570,70 +6571,70 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="11" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>765</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="11" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>754</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="11" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>755</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="11" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>759</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -6644,11 +6645,11 @@
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -6659,13 +6660,13 @@
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D7" s="14" t="s">
+        <v>925</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>926</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>927</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -6675,50 +6676,50 @@
         <v>751</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>766</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="11" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>767</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="11" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="D10" s="14" t="s">
+        <v>931</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>932</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>933</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -6729,11 +6730,11 @@
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -6748,22 +6749,22 @@
         <v>760</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="11" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="D13" s="14" t="s">
+        <v>935</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>936</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>937</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -6774,20 +6775,20 @@
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>768</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="11" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -6795,14 +6796,14 @@
         <v>752</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="11" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -6810,22 +6811,22 @@
         <v>756</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="11" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="11" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -6836,13 +6837,13 @@
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D18" s="14" t="s">
+        <v>941</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>942</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>943</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -6853,24 +6854,24 @@
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>769</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="11" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>761</v>
@@ -6883,7 +6884,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="11" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -6891,24 +6892,24 @@
         <v>770</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="11" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>695</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -6919,13 +6920,13 @@
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D23" s="14" t="s">
+        <v>947</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>948</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>949</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -6936,7 +6937,7 @@
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D24" s="11"/>
       <c r="E24" s="11" t="s">
@@ -6953,43 +6954,43 @@
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="11" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11" t="s">
         <v>771</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="11" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="B27" s="11" t="s">
+        <v>952</v>
+      </c>
+      <c r="C27" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="D27" s="14" t="s">
         <v>954</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="E27" s="11" t="s">
         <v>955</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>956</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -7000,43 +7001,43 @@
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>745</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="11" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="14" t="s">
+        <v>958</v>
+      </c>
+      <c r="E29" s="11" t="s">
         <v>959</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>960</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="11" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="14" t="s">
+        <v>960</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>961</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>962</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -7047,13 +7048,13 @@
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D31" s="14" t="s">
+        <v>962</v>
+      </c>
+      <c r="E31" s="11" t="s">
         <v>963</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>964</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -7064,28 +7065,28 @@
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D32" s="11"/>
       <c r="E32" s="11" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="11" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -7096,11 +7097,11 @@
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D34" s="11"/>
       <c r="E34" s="11" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -7111,11 +7112,11 @@
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D35" s="11"/>
       <c r="E35" s="11" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -7126,11 +7127,11 @@
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D36" s="11"/>
       <c r="E36" s="11" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -7141,11 +7142,11 @@
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D37" s="11"/>
       <c r="E37" s="11" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -7156,18 +7157,18 @@
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D38" s="11"/>
       <c r="E38" s="11" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="11" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -7175,37 +7176,37 @@
         <v>762</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="11" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="B41" s="11"/>
       <c r="C41" s="11" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>764</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -7216,7 +7217,7 @@
       </c>
       <c r="B42" s="11"/>
       <c r="C42" s="11" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>780</v>
@@ -7233,11 +7234,11 @@
       </c>
       <c r="B43" s="11"/>
       <c r="C43" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D43" s="11"/>
       <c r="E43" s="11" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -7248,61 +7249,61 @@
       </c>
       <c r="B44" s="11"/>
       <c r="C44" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="11" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="11" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
       <c r="E45" s="11" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="11" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B46" s="11"/>
       <c r="C46" s="11" t="s">
+        <v>978</v>
+      </c>
+      <c r="D46" s="14" t="s">
         <v>979</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="E46" s="11" t="s">
         <v>980</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>981</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="11" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
       <c r="E47" s="11" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="11" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
@@ -7325,7 +7326,7 @@
       </c>
       <c r="D49" s="11"/>
       <c r="E49" s="11" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -7336,11 +7337,11 @@
       </c>
       <c r="B50" s="11"/>
       <c r="C50" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D50" s="11"/>
       <c r="E50" s="11" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -7355,22 +7356,22 @@
         <v>782</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="11" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
       <c r="D52" s="14" t="s">
+        <v>995</v>
+      </c>
+      <c r="E52" s="11" t="s">
         <v>996</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>997</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -7381,13 +7382,13 @@
       </c>
       <c r="B53" s="11"/>
       <c r="C53" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D53" s="14" t="s">
+        <v>997</v>
+      </c>
+      <c r="E53" s="11" t="s">
         <v>998</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>999</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -7399,7 +7400,7 @@
       <c r="B54" s="11"/>
       <c r="C54" s="11"/>
       <c r="D54" s="14" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>316</v>
@@ -7409,7 +7410,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="11" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
@@ -7428,94 +7429,94 @@
       </c>
       <c r="B56" s="11"/>
       <c r="C56" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="11" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B57" s="11"/>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
       <c r="E57" s="11" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="11" t="s">
+        <v>985</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D58" s="11" t="s">
         <v>986</v>
       </c>
-      <c r="B58" s="11" t="s">
-        <v>1785</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>1738</v>
-      </c>
-      <c r="D58" s="11" t="s">
+      <c r="E58" s="11" t="s">
         <v>987</v>
-      </c>
-      <c r="E58" s="11" t="s">
-        <v>988</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="11" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B59" s="11"/>
       <c r="C59" s="11" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="11" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B60" s="11"/>
       <c r="C60" s="11" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="D60" s="11" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E60" s="11" t="s">
         <v>1007</v>
-      </c>
-      <c r="E60" s="11" t="s">
-        <v>1008</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="11" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B61" s="11"/>
       <c r="C61" s="11"/>
       <c r="D61" s="14" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E61" s="11" t="s">
         <v>1010</v>
-      </c>
-      <c r="E61" s="11" t="s">
-        <v>1011</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
@@ -7541,45 +7542,45 @@
       </c>
       <c r="B63" s="11"/>
       <c r="C63" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D63" s="11"/>
       <c r="E63" s="11" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
     </row>
     <row r="64" spans="1:8" ht="51">
       <c r="A64" s="11" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B64" s="11"/>
       <c r="C64" s="11" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="D64" s="14" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E64" s="15" t="s">
         <v>1017</v>
-      </c>
-      <c r="E64" s="15" t="s">
-        <v>1018</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="11" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B65" s="11"/>
       <c r="C65" s="11" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="D65" s="14" t="s">
+        <v>1780</v>
+      </c>
+      <c r="E65" s="11" t="s">
         <v>1781</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>1782</v>
       </c>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
@@ -7590,10 +7591,10 @@
       </c>
       <c r="B66" s="11"/>
       <c r="C66" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>776</v>
@@ -7607,13 +7608,13 @@
       </c>
       <c r="B67" s="11"/>
       <c r="C67" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D67" s="14" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E67" s="11" t="s">
         <v>1021</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>1022</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -7626,7 +7627,7 @@
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
       <c r="E68" s="11" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
@@ -7637,13 +7638,13 @@
       </c>
       <c r="B69" s="11"/>
       <c r="C69" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D69" s="11" t="s">
         <v>696</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -7656,7 +7657,7 @@
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
       <c r="E70" s="11" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -7667,7 +7668,7 @@
       </c>
       <c r="B71" s="11"/>
       <c r="C71" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D71" s="11"/>
       <c r="E71" s="11"/>
@@ -7676,15 +7677,15 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="11" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B72" s="11"/>
       <c r="C72" s="11"/>
       <c r="D72" s="14" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E72" s="11" t="s">
         <v>1027</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>1028</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -7695,11 +7696,11 @@
       </c>
       <c r="B73" s="11"/>
       <c r="C73" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D73" s="11"/>
       <c r="E73" s="11" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
@@ -7710,7 +7711,7 @@
       </c>
       <c r="B74" s="11"/>
       <c r="C74" s="11" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="D74" s="11" t="s">
         <v>785</v>
@@ -7723,77 +7724,77 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="11" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="B75" s="11"/>
       <c r="C75" s="11" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="11" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B76" s="11"/>
       <c r="C76" s="11"/>
       <c r="D76" s="14" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E76" s="11" t="s">
         <v>1034</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>1035</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="11" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="B77" s="11"/>
       <c r="C77" s="11" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="D77" s="11"/>
       <c r="E77" s="11" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="11" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B78" s="11"/>
       <c r="C78" s="11"/>
       <c r="D78" s="14" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E78" s="11" t="s">
         <v>1039</v>
-      </c>
-      <c r="E78" s="11" t="s">
-        <v>1040</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="11" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B79" s="11"/>
       <c r="C79" s="11"/>
       <c r="D79" s="14" t="s">
+        <v>989</v>
+      </c>
+      <c r="E79" s="11" t="s">
         <v>990</v>
-      </c>
-      <c r="E79" s="11" t="s">
-        <v>991</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
@@ -7804,13 +7805,13 @@
       </c>
       <c r="B80" s="11"/>
       <c r="C80" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D80" s="11" t="s">
         <v>697</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
@@ -7821,23 +7822,23 @@
       </c>
       <c r="B81" s="11"/>
       <c r="C81" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D81" s="11"/>
       <c r="E81" s="11" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="11" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B82" s="11"/>
       <c r="C82" s="11"/>
       <c r="D82" s="14" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E82" s="11" t="s">
         <v>300</v>
@@ -7847,28 +7848,28 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="11" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
       <c r="D83" s="14" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E83" s="11" t="s">
         <v>1046</v>
-      </c>
-      <c r="E83" s="11" t="s">
-        <v>1047</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="11" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B84" s="11"/>
       <c r="C84" s="11"/>
       <c r="D84" s="11"/>
       <c r="E84" s="11" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -7879,24 +7880,24 @@
       </c>
       <c r="B85" s="11"/>
       <c r="C85" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D85" s="11"/>
       <c r="E85" s="11" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B86" s="11"/>
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
       <c r="E86" s="11" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -7909,22 +7910,22 @@
       <c r="C87" s="11"/>
       <c r="D87" s="11"/>
       <c r="E87" s="11" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="11" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B88" s="11"/>
       <c r="C88" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D88" s="11"/>
       <c r="E88" s="11" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -7937,7 +7938,7 @@
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
       <c r="E89" s="11" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -7948,11 +7949,11 @@
       </c>
       <c r="B90" s="11"/>
       <c r="C90" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D90" s="11"/>
       <c r="E90" s="11" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -7965,7 +7966,7 @@
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
       <c r="E91" s="11" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -7980,26 +7981,26 @@
         <v>698</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="11" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>1723</v>
+      </c>
+      <c r="D93" s="6" t="s">
         <v>1786</v>
       </c>
-      <c r="B93" s="11" t="s">
-        <v>1788</v>
-      </c>
-      <c r="C93" s="11" t="s">
-        <v>1724</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>1787</v>
-      </c>
       <c r="E93" s="11" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -8009,24 +8010,24 @@
         <v>525</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D94" s="11"/>
       <c r="E94" s="11" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="11" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="D95" s="11" t="s">
         <v>791</v>
@@ -8039,15 +8040,15 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="11" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
       <c r="D96" s="14" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E96" s="11" t="s">
         <v>1069</v>
-      </c>
-      <c r="E96" s="11" t="s">
-        <v>1070</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -8058,28 +8059,28 @@
       </c>
       <c r="B97" s="11"/>
       <c r="C97" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D97" s="14" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E97" s="11" t="s">
         <v>1071</v>
-      </c>
-      <c r="E97" s="11" t="s">
-        <v>1072</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="11" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
       <c r="D98" s="14" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E98" s="11" t="s">
         <v>1074</v>
-      </c>
-      <c r="E98" s="11" t="s">
-        <v>1075</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
@@ -8092,14 +8093,14 @@
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
       <c r="E99" s="11" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
@@ -8114,13 +8115,13 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="11" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="D101" s="11" t="s">
         <v>793</v>
@@ -8133,7 +8134,7 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="11" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
@@ -8156,7 +8157,7 @@
         <v>699</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -8180,11 +8181,11 @@
       </c>
       <c r="B105" s="11"/>
       <c r="C105" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D105" s="11"/>
       <c r="E105" s="11" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -8197,7 +8198,7 @@
       <c r="C106" s="11"/>
       <c r="D106" s="11"/>
       <c r="E106" s="11" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -8207,7 +8208,7 @@
         <v>169</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="C107" s="11" t="s">
         <v>757</v>
@@ -8229,7 +8230,7 @@
       <c r="C108" s="11"/>
       <c r="D108" s="11"/>
       <c r="E108" s="11" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -8249,17 +8250,17 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="11" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="D110" s="11"/>
       <c r="E110" s="11" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
@@ -8272,14 +8273,14 @@
       <c r="C111" s="11"/>
       <c r="D111" s="11"/>
       <c r="E111" s="11" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="11" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B112" s="11"/>
       <c r="C112" s="11"/>
@@ -8287,20 +8288,20 @@
         <v>800</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="11" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B113" s="11"/>
       <c r="C113" s="11"/>
       <c r="D113" s="11"/>
       <c r="E113" s="11" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
@@ -8313,7 +8314,7 @@
       <c r="C114" s="11"/>
       <c r="D114" s="11"/>
       <c r="E114" s="11" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
@@ -8324,13 +8325,13 @@
       </c>
       <c r="B115" s="11"/>
       <c r="C115" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D115" s="11" t="s">
         <v>700</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
@@ -8343,7 +8344,7 @@
       <c r="C116" s="11"/>
       <c r="D116" s="11"/>
       <c r="E116" s="11" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
@@ -8356,7 +8357,7 @@
       <c r="C117" s="11"/>
       <c r="D117" s="11"/>
       <c r="E117" s="11" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
@@ -8369,7 +8370,7 @@
       <c r="C118" s="11"/>
       <c r="D118" s="11"/>
       <c r="E118" s="11" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
@@ -8382,22 +8383,22 @@
       <c r="C119" s="11"/>
       <c r="D119" s="11"/>
       <c r="E119" s="11" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="11" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B120" s="11"/>
       <c r="C120" s="11"/>
       <c r="D120" s="14" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E120" s="11" t="s">
         <v>1004</v>
-      </c>
-      <c r="E120" s="11" t="s">
-        <v>1005</v>
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
@@ -8408,18 +8409,18 @@
       </c>
       <c r="B121" s="11"/>
       <c r="C121" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D121" s="11"/>
       <c r="E121" s="11" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="11" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="B122" s="11"/>
       <c r="C122" s="11"/>
@@ -8440,7 +8441,7 @@
       <c r="C123" s="11"/>
       <c r="D123" s="11"/>
       <c r="E123" s="11" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
@@ -8451,11 +8452,11 @@
       </c>
       <c r="B124" s="11"/>
       <c r="C124" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D124" s="11"/>
       <c r="E124" s="11" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
@@ -8479,11 +8480,11 @@
       </c>
       <c r="B126" s="11"/>
       <c r="C126" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D126" s="11"/>
       <c r="E126" s="11" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -8505,26 +8506,26 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="11" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B128" s="11"/>
       <c r="C128" s="11"/>
       <c r="D128" s="11"/>
       <c r="E128" s="11" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="11" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="B129" s="11"/>
       <c r="C129" s="11"/>
       <c r="D129" s="11"/>
       <c r="E129" s="11" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -8537,14 +8538,14 @@
       <c r="C130" s="11"/>
       <c r="D130" s="11"/>
       <c r="E130" s="11" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="11" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="B131" s="11"/>
       <c r="C131" s="11"/>
@@ -8563,11 +8564,11 @@
       </c>
       <c r="B132" s="11"/>
       <c r="C132" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D132" s="11"/>
       <c r="E132" s="11" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
@@ -8580,35 +8581,35 @@
       <c r="C133" s="11"/>
       <c r="D133" s="11"/>
       <c r="E133" s="11" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="11" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B134" s="11"/>
       <c r="C134" s="11"/>
       <c r="D134" s="11"/>
       <c r="E134" s="11" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="11" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B135" s="11"/>
       <c r="C135" s="11"/>
       <c r="D135" s="14" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E135" s="11" t="s">
         <v>1105</v>
-      </c>
-      <c r="E135" s="11" t="s">
-        <v>1106</v>
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
@@ -8619,18 +8620,18 @@
       </c>
       <c r="B136" s="11"/>
       <c r="C136" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D136" s="11"/>
       <c r="E136" s="11" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="11" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="B137" s="11"/>
       <c r="C137" s="11"/>
@@ -8662,7 +8663,7 @@
       <c r="C139" s="11"/>
       <c r="D139" s="11"/>
       <c r="E139" s="11" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
@@ -8675,33 +8676,33 @@
       <c r="C140" s="11"/>
       <c r="D140" s="11"/>
       <c r="E140" s="11" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="11" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B141" s="11"/>
       <c r="C141" s="11"/>
       <c r="D141" s="11"/>
       <c r="E141" s="11" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="11" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B142" s="11"/>
       <c r="C142" s="11"/>
       <c r="D142" s="11"/>
       <c r="E142" s="11" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
@@ -8712,11 +8713,11 @@
       </c>
       <c r="B143" s="11"/>
       <c r="C143" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D143" s="11"/>
       <c r="E143" s="11" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
@@ -8742,20 +8743,20 @@
       <c r="C145" s="11"/>
       <c r="D145" s="11"/>
       <c r="E145" s="11" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="11" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B146" s="11"/>
       <c r="C146" s="11"/>
       <c r="D146" s="11"/>
       <c r="E146" s="11" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
@@ -8766,11 +8767,11 @@
       </c>
       <c r="B147" s="11"/>
       <c r="C147" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D147" s="11"/>
       <c r="E147" s="11" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
@@ -8792,13 +8793,13 @@
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="11" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="B149" s="11"/>
       <c r="C149" s="11"/>
       <c r="D149" s="11"/>
       <c r="E149" s="11" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
@@ -8811,20 +8812,20 @@
       <c r="C150" s="11"/>
       <c r="D150" s="11"/>
       <c r="E150" s="11" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="11" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B151" s="11"/>
       <c r="C151" s="11"/>
       <c r="D151" s="11"/>
       <c r="E151" s="11" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
@@ -8850,13 +8851,13 @@
       </c>
       <c r="B153" s="11"/>
       <c r="C153" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D153" s="11" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E153" s="11" t="s">
         <v>1126</v>
-      </c>
-      <c r="E153" s="11" t="s">
-        <v>1127</v>
       </c>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
@@ -8867,13 +8868,13 @@
       </c>
       <c r="B154" s="11"/>
       <c r="C154" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D154" s="11" t="s">
         <v>702</v>
       </c>
       <c r="E154" s="11" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
@@ -8884,11 +8885,11 @@
       </c>
       <c r="B155" s="11"/>
       <c r="C155" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D155" s="11"/>
       <c r="E155" s="11" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
@@ -8899,11 +8900,11 @@
       </c>
       <c r="B156" s="11"/>
       <c r="C156" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D156" s="11"/>
       <c r="E156" s="11" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
@@ -8914,13 +8915,13 @@
       </c>
       <c r="B157" s="11"/>
       <c r="C157" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D157" s="11" t="s">
         <v>703</v>
       </c>
       <c r="E157" s="11" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
@@ -8931,11 +8932,11 @@
       </c>
       <c r="B158" s="11"/>
       <c r="C158" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D158" s="11"/>
       <c r="E158" s="11" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
@@ -8946,26 +8947,26 @@
       </c>
       <c r="B159" s="11"/>
       <c r="C159" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D159" s="11"/>
       <c r="E159" s="11" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="11" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="B160" s="11"/>
       <c r="C160" s="11" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="D160" s="11"/>
       <c r="E160" s="11" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
@@ -8985,32 +8986,32 @@
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="11" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="B162" s="11"/>
       <c r="C162" s="11"/>
       <c r="D162" s="11" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E162" s="11" t="s">
         <v>1135</v>
-      </c>
-      <c r="E162" s="11" t="s">
-        <v>1136</v>
       </c>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="11" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B163" s="11" t="s">
         <v>1740</v>
-      </c>
-      <c r="B163" s="11" t="s">
-        <v>1741</v>
       </c>
       <c r="C163" s="11" t="s">
         <v>741</v>
       </c>
       <c r="D163" s="11"/>
       <c r="E163" s="11" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
@@ -9021,11 +9022,11 @@
       </c>
       <c r="B164" s="11"/>
       <c r="C164" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D164" s="11"/>
       <c r="E164" s="11" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
@@ -9038,7 +9039,7 @@
       <c r="C165" s="11"/>
       <c r="D165" s="11"/>
       <c r="E165" s="11" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
@@ -9049,7 +9050,7 @@
       </c>
       <c r="B166" s="11"/>
       <c r="C166" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D166" s="11"/>
       <c r="E166" s="11" t="s">
@@ -9066,7 +9067,7 @@
       <c r="C167" s="11"/>
       <c r="D167" s="11"/>
       <c r="E167" s="11" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
@@ -9081,7 +9082,7 @@
         <v>704</v>
       </c>
       <c r="E168" s="11" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
@@ -9094,24 +9095,24 @@
       <c r="C169" s="11"/>
       <c r="D169" s="11"/>
       <c r="E169" s="11" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="11" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B170" s="11" t="s">
         <v>1764</v>
       </c>
-      <c r="B170" s="11" t="s">
-        <v>1765</v>
-      </c>
       <c r="C170" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D170" s="11"/>
       <c r="E170" s="11" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
@@ -9122,7 +9123,7 @@
       </c>
       <c r="B171" s="11"/>
       <c r="C171" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D171" s="11"/>
       <c r="E171" s="11" t="s">
@@ -9133,13 +9134,13 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="11" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B172" s="11" t="s">
         <v>1766</v>
       </c>
-      <c r="B172" s="11" t="s">
-        <v>1767</v>
-      </c>
       <c r="C172" s="11" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="D172" s="11"/>
       <c r="E172" s="11" t="s">
@@ -9184,7 +9185,7 @@
       <c r="C175" s="11"/>
       <c r="D175" s="11"/>
       <c r="E175" s="11" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
@@ -9195,11 +9196,11 @@
       </c>
       <c r="B176" s="11"/>
       <c r="C176" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D176" s="11"/>
       <c r="E176" s="11" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
@@ -9210,11 +9211,11 @@
       </c>
       <c r="B177" s="11"/>
       <c r="C177" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D177" s="11"/>
       <c r="E177" s="11" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
@@ -9227,7 +9228,7 @@
       <c r="C178" s="11"/>
       <c r="D178" s="11"/>
       <c r="E178" s="11" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
@@ -9253,7 +9254,7 @@
       <c r="C180" s="11"/>
       <c r="D180" s="11"/>
       <c r="E180" s="11" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
@@ -9266,7 +9267,7 @@
       <c r="C181" s="11"/>
       <c r="D181" s="11"/>
       <c r="E181" s="11" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
@@ -9292,7 +9293,7 @@
       <c r="C183" s="11"/>
       <c r="D183" s="11"/>
       <c r="E183" s="11" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
@@ -9305,7 +9306,7 @@
       <c r="C184" s="11"/>
       <c r="D184" s="11"/>
       <c r="E184" s="11" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
@@ -9318,7 +9319,7 @@
       <c r="C185" s="11"/>
       <c r="D185" s="11"/>
       <c r="E185" s="11" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
@@ -9331,7 +9332,7 @@
       <c r="C186" s="11"/>
       <c r="D186" s="11"/>
       <c r="E186" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
@@ -9342,11 +9343,11 @@
       </c>
       <c r="B187" s="11"/>
       <c r="C187" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D187" s="11"/>
       <c r="E187" s="11" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
@@ -9359,7 +9360,7 @@
       <c r="C188" s="11"/>
       <c r="D188" s="11"/>
       <c r="E188" s="11" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
@@ -9370,26 +9371,26 @@
       </c>
       <c r="B189" s="11"/>
       <c r="C189" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D189" s="11"/>
       <c r="E189" s="11" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" s="11" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="B190" s="11"/>
       <c r="C190" s="11" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="D190" s="11"/>
       <c r="E190" s="11" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
@@ -9415,7 +9416,7 @@
       <c r="C192" s="11"/>
       <c r="D192" s="11"/>
       <c r="E192" s="11" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
@@ -9428,7 +9429,7 @@
       <c r="C193" s="11"/>
       <c r="D193" s="11"/>
       <c r="E193" s="11" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
@@ -9441,7 +9442,7 @@
       <c r="C194" s="11"/>
       <c r="D194" s="11"/>
       <c r="E194" s="11" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
@@ -9454,7 +9455,7 @@
       <c r="C195" s="11"/>
       <c r="D195" s="11"/>
       <c r="E195" s="11" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
@@ -9482,7 +9483,7 @@
       <c r="C197" s="11"/>
       <c r="D197" s="11"/>
       <c r="E197" s="11" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
@@ -9510,7 +9511,7 @@
       <c r="C199" s="11"/>
       <c r="D199" s="11"/>
       <c r="E199" s="11" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
@@ -9523,7 +9524,7 @@
       <c r="C200" s="11"/>
       <c r="D200" s="11"/>
       <c r="E200" s="11" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
@@ -9547,11 +9548,11 @@
       </c>
       <c r="B202" s="11"/>
       <c r="C202" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D202" s="11"/>
       <c r="E202" s="11" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
@@ -9577,7 +9578,7 @@
       <c r="C204" s="11"/>
       <c r="D204" s="11"/>
       <c r="E204" s="11" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
@@ -9590,7 +9591,7 @@
       <c r="C205" s="11"/>
       <c r="D205" s="11"/>
       <c r="E205" s="11" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
@@ -9603,7 +9604,7 @@
       <c r="C206" s="11"/>
       <c r="D206" s="11"/>
       <c r="E206" s="11" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
@@ -9614,11 +9615,11 @@
       </c>
       <c r="B207" s="11"/>
       <c r="C207" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D207" s="11"/>
       <c r="E207" s="11" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
@@ -9629,7 +9630,7 @@
       </c>
       <c r="B208" s="11"/>
       <c r="C208" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D208" s="11"/>
       <c r="E208" s="11" t="s">
@@ -9657,11 +9658,11 @@
       </c>
       <c r="B210" s="11"/>
       <c r="C210" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D210" s="11"/>
       <c r="E210" s="11" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
@@ -9672,11 +9673,11 @@
       </c>
       <c r="B211" s="11"/>
       <c r="C211" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D211" s="11"/>
       <c r="E211" s="11" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
@@ -9687,48 +9688,48 @@
       </c>
       <c r="B212" s="11"/>
       <c r="C212" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D212" s="11"/>
       <c r="E212" s="11" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" s="11" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="B213" s="11"/>
       <c r="C213" s="11" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="D213" s="11"/>
       <c r="E213" s="11" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" s="11" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="B214" s="11"/>
       <c r="C214" s="11" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="D214" s="11"/>
       <c r="E214" s="11" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
     </row>
     <row r="215" spans="1:8">
       <c r="A215" s="11" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="B215" s="11"/>
       <c r="C215" s="11"/>
@@ -9747,7 +9748,7 @@
       <c r="C216" s="11"/>
       <c r="D216" s="11"/>
       <c r="E216" s="11" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
@@ -9784,13 +9785,13 @@
     </row>
     <row r="219" spans="1:8">
       <c r="A219" s="11" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="B219" s="11"/>
       <c r="C219" s="11"/>
       <c r="D219" s="11"/>
       <c r="E219" s="11" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
@@ -9803,7 +9804,7 @@
       <c r="C220" s="11"/>
       <c r="D220" s="11"/>
       <c r="E220" s="11" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
@@ -9814,11 +9815,11 @@
       </c>
       <c r="B221" s="11"/>
       <c r="C221" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D221" s="11"/>
       <c r="E221" s="11" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
@@ -9829,11 +9830,11 @@
       </c>
       <c r="B222" s="11"/>
       <c r="C222" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D222" s="11"/>
       <c r="E222" s="11" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
@@ -9844,11 +9845,11 @@
       </c>
       <c r="B223" s="11"/>
       <c r="C223" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D223" s="11"/>
       <c r="E223" s="11" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
@@ -9859,11 +9860,11 @@
       </c>
       <c r="B224" s="11"/>
       <c r="C224" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D224" s="11"/>
       <c r="E224" s="11" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
@@ -9876,7 +9877,7 @@
       <c r="C225" s="11"/>
       <c r="D225" s="11"/>
       <c r="E225" s="11" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
@@ -9889,41 +9890,41 @@
       <c r="C226" s="11"/>
       <c r="D226" s="11"/>
       <c r="E226" s="11" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
     </row>
     <row r="227" spans="1:8">
       <c r="A227" s="11" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="B227" s="11"/>
       <c r="C227" s="11" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="D227" s="11" t="s">
         <v>708</v>
       </c>
       <c r="E227" s="11" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
     </row>
     <row r="228" spans="1:8">
       <c r="A228" s="11" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B228" s="11"/>
       <c r="C228" s="11" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="D228" s="11" t="s">
         <v>744</v>
       </c>
       <c r="E228" s="11" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
@@ -9936,7 +9937,7 @@
       <c r="C229" s="11"/>
       <c r="D229" s="11"/>
       <c r="E229" s="11" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
@@ -9949,7 +9950,7 @@
       <c r="C230" s="11"/>
       <c r="D230" s="11"/>
       <c r="E230" s="11" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
@@ -9962,7 +9963,7 @@
       <c r="C231" s="11"/>
       <c r="D231" s="11"/>
       <c r="E231" s="11" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
@@ -9975,7 +9976,7 @@
       <c r="C232" s="11"/>
       <c r="D232" s="11"/>
       <c r="E232" s="11" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
@@ -9988,7 +9989,7 @@
       <c r="C233" s="11"/>
       <c r="D233" s="11"/>
       <c r="E233" s="11" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
@@ -9999,7 +10000,7 @@
       </c>
       <c r="B234" s="11"/>
       <c r="C234" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D234" s="11"/>
       <c r="E234" s="11" t="s">
@@ -10027,7 +10028,7 @@
       </c>
       <c r="B236" s="11"/>
       <c r="C236" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D236" s="11"/>
       <c r="E236" s="11" t="s">
@@ -10044,7 +10045,7 @@
       <c r="C237" s="11"/>
       <c r="D237" s="11"/>
       <c r="E237" s="11" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
@@ -10057,7 +10058,7 @@
       <c r="C238" s="11"/>
       <c r="D238" s="11"/>
       <c r="E238" s="11" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
@@ -10070,7 +10071,7 @@
       <c r="C239" s="11"/>
       <c r="D239" s="11"/>
       <c r="E239" s="11" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="G239" s="2"/>
       <c r="H239" s="2"/>
@@ -10096,33 +10097,33 @@
       <c r="C241" s="11"/>
       <c r="D241" s="11"/>
       <c r="E241" s="11" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
     </row>
     <row r="242" spans="1:8">
       <c r="A242" s="11" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="B242" s="11"/>
       <c r="C242" s="11" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="D242" s="11"/>
       <c r="E242" s="11" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
     </row>
     <row r="243" spans="1:8">
       <c r="A243" s="11" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="B243" s="11"/>
       <c r="C243" s="11" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="D243" s="11" t="s">
         <v>824</v>
@@ -10135,15 +10136,15 @@
     </row>
     <row r="244" spans="1:8">
       <c r="A244" s="11" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="B244" s="11"/>
       <c r="C244" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D244" s="11"/>
       <c r="E244" s="11" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="G244" s="2"/>
       <c r="H244" s="2"/>
@@ -10163,30 +10164,30 @@
     </row>
     <row r="246" spans="1:8">
       <c r="A246" s="11" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="B246" s="11"/>
       <c r="C246" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D246" s="11"/>
       <c r="E246" s="11" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
     </row>
     <row r="247" spans="1:8">
       <c r="A247" s="11" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="B247" s="11"/>
       <c r="C247" s="11" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="D247" s="11"/>
       <c r="E247" s="11" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
@@ -10199,7 +10200,7 @@
       <c r="C248" s="11"/>
       <c r="D248" s="11"/>
       <c r="E248" s="11" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G248" s="2"/>
       <c r="H248" s="2"/>
@@ -10210,11 +10211,11 @@
       </c>
       <c r="B249" s="11"/>
       <c r="C249" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D249" s="11"/>
       <c r="E249" s="11" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="G249" s="2"/>
       <c r="H249" s="2"/>
@@ -10227,7 +10228,7 @@
       <c r="C250" s="11"/>
       <c r="D250" s="11"/>
       <c r="E250" s="11" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
@@ -10240,7 +10241,7 @@
       <c r="C251" s="11"/>
       <c r="D251" s="11"/>
       <c r="E251" s="11" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="G251" s="2"/>
       <c r="H251" s="2"/>
@@ -10253,7 +10254,7 @@
       <c r="C252" s="11"/>
       <c r="D252" s="11"/>
       <c r="E252" s="11" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="G252" s="2"/>
       <c r="H252" s="2"/>
@@ -10266,7 +10267,7 @@
       <c r="C253" s="11"/>
       <c r="D253" s="11"/>
       <c r="E253" s="11" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="G253" s="2"/>
       <c r="H253" s="2"/>
@@ -10277,11 +10278,11 @@
       </c>
       <c r="B254" s="11"/>
       <c r="C254" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D254" s="11"/>
       <c r="E254" s="11" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="G254" s="2"/>
       <c r="H254" s="2"/>
@@ -10292,7 +10293,7 @@
       </c>
       <c r="B255" s="11"/>
       <c r="C255" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D255" s="11"/>
       <c r="E255" s="11" t="s">
@@ -10307,11 +10308,11 @@
       </c>
       <c r="B256" s="11"/>
       <c r="C256" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D256" s="11"/>
       <c r="E256" s="11" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
@@ -10322,11 +10323,11 @@
       </c>
       <c r="B257" s="11"/>
       <c r="C257" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D257" s="11"/>
       <c r="E257" s="11" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="G257" s="2"/>
       <c r="H257" s="2"/>
@@ -10339,7 +10340,7 @@
       <c r="C258" s="11"/>
       <c r="D258" s="11"/>
       <c r="E258" s="11" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="G258" s="2"/>
       <c r="H258" s="2"/>
@@ -10350,33 +10351,33 @@
       </c>
       <c r="B259" s="11"/>
       <c r="C259" s="11" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="D259" s="11"/>
       <c r="E259" s="11" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="G259" s="2"/>
       <c r="H259" s="2"/>
     </row>
     <row r="260" spans="1:8">
       <c r="A260" s="11" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B260" s="11"/>
       <c r="C260" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D260" s="11"/>
       <c r="E260" s="11" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="G260" s="2"/>
       <c r="H260" s="2"/>
     </row>
     <row r="261" spans="1:8">
       <c r="A261" s="11" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B261" s="11"/>
       <c r="C261" s="11"/>
@@ -10384,24 +10385,24 @@
         <v>743</v>
       </c>
       <c r="E261" s="11" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="G261" s="2"/>
       <c r="H261" s="2"/>
     </row>
     <row r="262" spans="1:8">
       <c r="A262" s="11" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B262" s="11"/>
       <c r="C262" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D262" s="11" t="s">
         <v>748</v>
       </c>
       <c r="E262" s="11" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G262" s="2"/>
       <c r="H262" s="2"/>
@@ -10412,28 +10413,28 @@
       </c>
       <c r="B263" s="11"/>
       <c r="C263" s="11" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="D263" s="11" t="s">
         <v>749</v>
       </c>
       <c r="E263" s="11" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="G263" s="2"/>
       <c r="H263" s="2"/>
     </row>
     <row r="264" spans="1:8">
       <c r="A264" s="11" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="B264" s="11"/>
       <c r="C264" s="11" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="D264" s="11"/>
       <c r="E264" s="11" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="G264" s="2"/>
       <c r="H264" s="2"/>
@@ -10444,13 +10445,13 @@
       </c>
       <c r="B265" s="11"/>
       <c r="C265" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D265" s="11" t="s">
         <v>750</v>
       </c>
       <c r="E265" s="11" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="G265" s="2"/>
       <c r="H265" s="2"/>
@@ -10461,13 +10462,13 @@
       </c>
       <c r="B266" s="11"/>
       <c r="C266" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D266" s="11" t="s">
         <v>710</v>
       </c>
       <c r="E266" s="11" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="G266" s="2"/>
       <c r="H266" s="2"/>
@@ -10478,11 +10479,11 @@
       </c>
       <c r="B267" s="11"/>
       <c r="C267" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D267" s="11"/>
       <c r="E267" s="11" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="G267" s="2"/>
       <c r="H267" s="2"/>
@@ -10495,7 +10496,7 @@
       <c r="C268" s="11"/>
       <c r="D268" s="11"/>
       <c r="E268" s="11" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="G268" s="2"/>
       <c r="H268" s="2"/>
@@ -10508,7 +10509,7 @@
       <c r="C269" s="11"/>
       <c r="D269" s="11"/>
       <c r="E269" s="11" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G269" s="2"/>
       <c r="H269" s="2"/>
@@ -10528,13 +10529,13 @@
     </row>
     <row r="271" spans="1:8">
       <c r="A271" s="11" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="B271" s="11"/>
       <c r="C271" s="11"/>
       <c r="D271" s="11"/>
       <c r="E271" s="11" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="G271" s="2"/>
       <c r="H271" s="2"/>
@@ -10549,7 +10550,7 @@
         <v>711</v>
       </c>
       <c r="E272" s="11" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="G272" s="2"/>
       <c r="H272" s="2"/>
@@ -10575,7 +10576,7 @@
       <c r="C274" s="11"/>
       <c r="D274" s="11"/>
       <c r="E274" s="11" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="G274" s="2"/>
       <c r="H274" s="2"/>
@@ -10599,7 +10600,7 @@
       </c>
       <c r="B276" s="11"/>
       <c r="C276" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D276" s="11"/>
       <c r="E276" s="11" t="s">
@@ -10616,7 +10617,7 @@
       <c r="C277" s="11"/>
       <c r="D277" s="11"/>
       <c r="E277" s="11" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="G277" s="2"/>
       <c r="H277" s="2"/>
@@ -10629,7 +10630,7 @@
       <c r="C278" s="11"/>
       <c r="D278" s="11"/>
       <c r="E278" s="11" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="G278" s="2"/>
       <c r="H278" s="2"/>
@@ -10642,7 +10643,7 @@
       <c r="C279" s="11"/>
       <c r="D279" s="11"/>
       <c r="E279" s="11" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="G279" s="2"/>
       <c r="H279" s="2"/>
@@ -10653,7 +10654,7 @@
       </c>
       <c r="B280" s="11"/>
       <c r="C280" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D280" s="11"/>
       <c r="E280" s="11" t="s">
@@ -10664,13 +10665,13 @@
     </row>
     <row r="281" spans="1:8">
       <c r="A281" s="11" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B281" s="11"/>
       <c r="C281" s="11"/>
       <c r="D281" s="11"/>
       <c r="E281" s="11" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="G281" s="2"/>
       <c r="H281" s="2"/>
@@ -10692,13 +10693,13 @@
     </row>
     <row r="283" spans="1:8">
       <c r="A283" s="11" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="B283" s="11"/>
       <c r="C283" s="11"/>
       <c r="D283" s="11"/>
       <c r="E283" s="11" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="G283" s="2"/>
       <c r="H283" s="2"/>
@@ -10728,7 +10729,7 @@
         <v>712</v>
       </c>
       <c r="E285" s="11" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="G285" s="2"/>
       <c r="H285" s="2"/>
@@ -10741,20 +10742,20 @@
       <c r="C286" s="11"/>
       <c r="D286" s="11"/>
       <c r="E286" s="11" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="G286" s="2"/>
       <c r="H286" s="2"/>
     </row>
     <row r="287" spans="1:8">
       <c r="A287" s="11" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="B287" s="11"/>
       <c r="C287" s="11"/>
       <c r="D287" s="11"/>
       <c r="E287" s="11" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="G287" s="2"/>
       <c r="H287" s="2"/>
@@ -10782,14 +10783,14 @@
       <c r="C289" s="11"/>
       <c r="D289" s="11"/>
       <c r="E289" s="11" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="G289" s="2"/>
       <c r="H289" s="2"/>
     </row>
     <row r="290" spans="1:8">
       <c r="A290" s="11" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="B290" s="11"/>
       <c r="C290" s="11"/>
@@ -10819,26 +10820,26 @@
     </row>
     <row r="292" spans="1:8">
       <c r="A292" s="11" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="B292" s="11"/>
       <c r="C292" s="11"/>
       <c r="D292" s="11"/>
       <c r="E292" s="11" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="G292" s="2"/>
       <c r="H292" s="2"/>
     </row>
     <row r="293" spans="1:8">
       <c r="A293" s="11" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="B293" s="11"/>
       <c r="C293" s="11"/>
       <c r="D293" s="11"/>
       <c r="E293" s="11" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="G293" s="2"/>
       <c r="H293" s="2"/>
@@ -10849,11 +10850,11 @@
       </c>
       <c r="B294" s="11"/>
       <c r="C294" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D294" s="11"/>
       <c r="E294" s="11" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="G294" s="2"/>
       <c r="H294" s="2"/>
@@ -10866,7 +10867,7 @@
       <c r="C295" s="11"/>
       <c r="D295" s="11"/>
       <c r="E295" s="11" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="G295" s="2"/>
       <c r="H295" s="2"/>
@@ -10877,11 +10878,11 @@
       </c>
       <c r="B296" s="11"/>
       <c r="C296" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D296" s="11"/>
       <c r="E296" s="11" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="G296" s="2"/>
       <c r="H296" s="2"/>
@@ -10892,11 +10893,11 @@
       </c>
       <c r="B297" s="11"/>
       <c r="C297" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D297" s="11"/>
       <c r="E297" s="11" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="G297" s="2"/>
       <c r="H297" s="2"/>
@@ -10909,7 +10910,7 @@
       <c r="C298" s="11"/>
       <c r="D298" s="11"/>
       <c r="E298" s="11" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="G298" s="2"/>
       <c r="H298" s="2"/>
@@ -10935,7 +10936,7 @@
       <c r="C300" s="11"/>
       <c r="D300" s="11"/>
       <c r="E300" s="11" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="G300" s="2"/>
       <c r="H300" s="2"/>
@@ -10946,11 +10947,11 @@
       </c>
       <c r="B301" s="11"/>
       <c r="C301" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D301" s="11"/>
       <c r="E301" s="11" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="G301" s="2"/>
       <c r="H301" s="2"/>
@@ -10963,7 +10964,7 @@
       <c r="C302" s="11"/>
       <c r="D302" s="11"/>
       <c r="E302" s="11" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="G302" s="2"/>
       <c r="H302" s="2"/>
@@ -10976,7 +10977,7 @@
       <c r="C303" s="11"/>
       <c r="D303" s="11"/>
       <c r="E303" s="11" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="G303" s="2"/>
       <c r="H303" s="2"/>
@@ -10989,7 +10990,7 @@
       <c r="C304" s="11"/>
       <c r="D304" s="11"/>
       <c r="E304" s="11" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="G304" s="2"/>
       <c r="H304" s="2"/>
@@ -11013,7 +11014,7 @@
       <c r="C306" s="11"/>
       <c r="D306" s="11"/>
       <c r="E306" s="11" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="G306" s="2"/>
       <c r="H306" s="2"/>
@@ -11024,18 +11025,18 @@
       </c>
       <c r="B307" s="11"/>
       <c r="C307" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D307" s="11"/>
       <c r="E307" s="11" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="G307" s="2"/>
       <c r="H307" s="2"/>
     </row>
     <row r="308" spans="1:8">
       <c r="A308" s="11" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="B308" s="11"/>
       <c r="C308" s="11"/>
@@ -11043,7 +11044,7 @@
         <v>836</v>
       </c>
       <c r="E308" s="11" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="G308" s="2"/>
       <c r="H308" s="2"/>
@@ -11073,7 +11074,7 @@
         <v>713</v>
       </c>
       <c r="E310" s="11" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="G310" s="2"/>
       <c r="H310" s="2"/>
@@ -11086,14 +11087,14 @@
       <c r="C311" s="11"/>
       <c r="D311" s="11"/>
       <c r="E311" s="11" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="G311" s="2"/>
       <c r="H311" s="2"/>
     </row>
     <row r="312" spans="1:8">
       <c r="A312" s="11" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="B312" s="11"/>
       <c r="C312" s="11"/>
@@ -11114,46 +11115,46 @@
       <c r="C313" s="11"/>
       <c r="D313" s="11"/>
       <c r="E313" s="11" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="G313" s="2"/>
       <c r="H313" s="2"/>
     </row>
     <row r="314" spans="1:8">
       <c r="A314" s="11" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B314" s="11"/>
       <c r="C314" s="11"/>
       <c r="D314" s="11"/>
       <c r="E314" s="11" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G314" s="2"/>
       <c r="H314" s="2"/>
     </row>
     <row r="315" spans="1:8">
       <c r="A315" s="11" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B315" s="11"/>
       <c r="C315" s="11"/>
       <c r="D315" s="11"/>
       <c r="E315" s="11" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="G315" s="2"/>
       <c r="H315" s="2"/>
     </row>
     <row r="316" spans="1:8">
       <c r="A316" s="11" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B316" s="11"/>
       <c r="C316" s="11"/>
       <c r="D316" s="11"/>
       <c r="E316" s="11" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="G316" s="2"/>
       <c r="H316" s="2"/>
@@ -11164,11 +11165,11 @@
       </c>
       <c r="B317" s="11"/>
       <c r="C317" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D317" s="11"/>
       <c r="E317" s="11" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="G317" s="2"/>
       <c r="H317" s="2"/>
@@ -11179,11 +11180,11 @@
       </c>
       <c r="B318" s="11"/>
       <c r="C318" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D318" s="11"/>
       <c r="E318" s="11" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="G318" s="2"/>
       <c r="H318" s="2"/>
@@ -11198,7 +11199,7 @@
         <v>714</v>
       </c>
       <c r="E319" s="11" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="G319" s="2"/>
       <c r="H319" s="2"/>
@@ -11209,11 +11210,11 @@
       </c>
       <c r="B320" s="11"/>
       <c r="C320" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D320" s="11"/>
       <c r="E320" s="11" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="G320" s="2"/>
       <c r="H320" s="2"/>
@@ -11224,11 +11225,11 @@
       </c>
       <c r="B321" s="11"/>
       <c r="C321" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D321" s="11"/>
       <c r="E321" s="11" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G321" s="2"/>
       <c r="H321" s="2"/>
@@ -11243,7 +11244,7 @@
       </c>
       <c r="D322" s="11"/>
       <c r="E322" s="11" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="G322" s="2"/>
       <c r="H322" s="2"/>
@@ -11254,11 +11255,11 @@
       </c>
       <c r="B323" s="11"/>
       <c r="C323" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D323" s="11"/>
       <c r="E323" s="11" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G323" s="2"/>
       <c r="H323" s="2"/>
@@ -11269,11 +11270,11 @@
       </c>
       <c r="B324" s="11"/>
       <c r="C324" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D324" s="11"/>
       <c r="E324" s="11" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="G324" s="2"/>
       <c r="H324" s="2"/>
@@ -11284,11 +11285,11 @@
       </c>
       <c r="B325" s="11"/>
       <c r="C325" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D325" s="11"/>
       <c r="E325" s="11" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G325" s="2"/>
       <c r="H325" s="2"/>
@@ -11299,11 +11300,11 @@
       </c>
       <c r="B326" s="11"/>
       <c r="C326" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D326" s="11"/>
       <c r="E326" s="11" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="G326" s="2"/>
       <c r="H326" s="2"/>
@@ -11314,11 +11315,11 @@
       </c>
       <c r="B327" s="11"/>
       <c r="C327" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D327" s="11"/>
       <c r="E327" s="11" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="G327" s="2"/>
       <c r="H327" s="2"/>
@@ -11329,11 +11330,11 @@
       </c>
       <c r="B328" s="11"/>
       <c r="C328" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D328" s="11"/>
       <c r="E328" s="11" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="G328" s="2"/>
       <c r="H328" s="2"/>
@@ -11344,11 +11345,11 @@
       </c>
       <c r="B329" s="11"/>
       <c r="C329" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D329" s="11"/>
       <c r="E329" s="11" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="G329" s="2"/>
       <c r="H329" s="2"/>
@@ -11359,24 +11360,24 @@
       </c>
       <c r="B330" s="11"/>
       <c r="C330" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D330" s="11"/>
       <c r="E330" s="11" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="G330" s="2"/>
       <c r="H330" s="2"/>
     </row>
     <row r="331" spans="1:8">
       <c r="A331" s="11" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B331" s="11"/>
       <c r="C331" s="11"/>
       <c r="D331" s="11"/>
       <c r="E331" s="11" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="G331" s="2"/>
       <c r="H331" s="2"/>
@@ -11389,7 +11390,7 @@
       <c r="C332" s="11"/>
       <c r="D332" s="11"/>
       <c r="E332" s="11" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="G332" s="2"/>
       <c r="H332" s="2"/>
@@ -11400,7 +11401,7 @@
       </c>
       <c r="B333" s="11"/>
       <c r="C333" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D333" s="11"/>
       <c r="E333" s="11" t="s">
@@ -11415,11 +11416,11 @@
       </c>
       <c r="B334" s="11"/>
       <c r="C334" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D334" s="11"/>
       <c r="E334" s="11" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="G334" s="2"/>
       <c r="H334" s="2"/>
@@ -11432,7 +11433,7 @@
       <c r="C335" s="11"/>
       <c r="D335" s="11"/>
       <c r="E335" s="11" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="G335" s="2"/>
       <c r="H335" s="2"/>
@@ -11443,11 +11444,11 @@
       </c>
       <c r="B336" s="11"/>
       <c r="C336" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D336" s="11"/>
       <c r="E336" s="11" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="G336" s="2"/>
       <c r="H336" s="2"/>
@@ -11460,7 +11461,7 @@
       <c r="C337" s="11"/>
       <c r="D337" s="11"/>
       <c r="E337" s="11" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="G337" s="2"/>
       <c r="H337" s="2"/>
@@ -11471,11 +11472,11 @@
       </c>
       <c r="B338" s="11"/>
       <c r="C338" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D338" s="11"/>
       <c r="E338" s="11" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="G338" s="2"/>
       <c r="H338" s="2"/>
@@ -11486,11 +11487,11 @@
       </c>
       <c r="B339" s="11"/>
       <c r="C339" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D339" s="11"/>
       <c r="E339" s="11" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="G339" s="2"/>
       <c r="H339" s="2"/>
@@ -11501,11 +11502,11 @@
       </c>
       <c r="B340" s="11"/>
       <c r="C340" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D340" s="11"/>
       <c r="E340" s="11" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="G340" s="2"/>
       <c r="H340" s="2"/>
@@ -11516,31 +11517,31 @@
       </c>
       <c r="B341" s="11"/>
       <c r="C341" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D341" s="11"/>
       <c r="E341" s="11" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="G341" s="2"/>
       <c r="H341" s="2"/>
     </row>
     <row r="342" spans="1:8">
       <c r="A342" s="11" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B342" s="11"/>
       <c r="C342" s="11"/>
       <c r="D342" s="11"/>
       <c r="E342" s="11" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="G342" s="2"/>
       <c r="H342" s="2"/>
     </row>
     <row r="343" spans="1:8">
       <c r="A343" s="11" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B343" s="11"/>
       <c r="C343" s="11"/>
@@ -11559,7 +11560,7 @@
       <c r="C344" s="11"/>
       <c r="D344" s="11"/>
       <c r="E344" s="11" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="G344" s="2"/>
       <c r="H344" s="2"/>
@@ -11572,7 +11573,7 @@
       <c r="C345" s="11"/>
       <c r="D345" s="11"/>
       <c r="E345" s="11" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="G345" s="2"/>
       <c r="H345" s="2"/>
@@ -11583,11 +11584,11 @@
       </c>
       <c r="B346" s="11"/>
       <c r="C346" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D346" s="11"/>
       <c r="E346" s="11" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="G346" s="2"/>
       <c r="H346" s="2"/>
@@ -11600,7 +11601,7 @@
       <c r="C347" s="11"/>
       <c r="D347" s="11"/>
       <c r="E347" s="11" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="G347" s="2"/>
       <c r="H347" s="2"/>
@@ -11613,7 +11614,7 @@
       <c r="C348" s="11"/>
       <c r="D348" s="11"/>
       <c r="E348" s="11" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="G348" s="2"/>
       <c r="H348" s="2"/>
@@ -11624,11 +11625,11 @@
       </c>
       <c r="B349" s="11"/>
       <c r="C349" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D349" s="11"/>
       <c r="E349" s="11" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="G349" s="2"/>
       <c r="H349" s="2"/>
@@ -11639,13 +11640,13 @@
       </c>
       <c r="B350" s="11"/>
       <c r="C350" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D350" s="11" t="s">
         <v>715</v>
       </c>
       <c r="E350" s="11" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="G350" s="2"/>
       <c r="H350" s="2"/>
@@ -11656,7 +11657,7 @@
       </c>
       <c r="B351" s="11"/>
       <c r="C351" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D351" s="11"/>
       <c r="E351" s="11"/>
@@ -11665,13 +11666,13 @@
     </row>
     <row r="352" spans="1:8">
       <c r="A352" s="11" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B352" s="11"/>
       <c r="C352" s="11"/>
       <c r="D352" s="11"/>
       <c r="E352" s="11" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="G352" s="2"/>
       <c r="H352" s="2"/>
@@ -11697,11 +11698,11 @@
       </c>
       <c r="B354" s="11"/>
       <c r="C354" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D354" s="11"/>
       <c r="E354" s="11" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="G354" s="2"/>
       <c r="H354" s="2"/>
@@ -11712,11 +11713,11 @@
       </c>
       <c r="B355" s="11"/>
       <c r="C355" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D355" s="11"/>
       <c r="E355" s="11" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="G355" s="2"/>
       <c r="H355" s="2"/>
@@ -11729,7 +11730,7 @@
       <c r="C356" s="11"/>
       <c r="D356" s="11"/>
       <c r="E356" s="11" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="G356" s="2"/>
       <c r="H356" s="2"/>
@@ -11740,11 +11741,11 @@
       </c>
       <c r="B357" s="11"/>
       <c r="C357" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D357" s="11"/>
       <c r="E357" s="11" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="G357" s="2"/>
       <c r="H357" s="2"/>
@@ -11755,11 +11756,11 @@
       </c>
       <c r="B358" s="11"/>
       <c r="C358" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D358" s="11"/>
       <c r="E358" s="11" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="G358" s="2"/>
       <c r="H358" s="2"/>
@@ -11770,24 +11771,24 @@
       </c>
       <c r="B359" s="11"/>
       <c r="C359" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D359" s="11"/>
       <c r="E359" s="11" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="G359" s="2"/>
       <c r="H359" s="2"/>
     </row>
     <row r="360" spans="1:8">
       <c r="A360" s="11" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="B360" s="11"/>
       <c r="C360" s="11"/>
       <c r="D360" s="11"/>
       <c r="E360" s="11" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="G360" s="2"/>
       <c r="H360" s="2"/>
@@ -11798,11 +11799,11 @@
       </c>
       <c r="B361" s="11"/>
       <c r="C361" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D361" s="11"/>
       <c r="E361" s="11" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="G361" s="2"/>
       <c r="H361" s="2"/>
@@ -11813,39 +11814,39 @@
       </c>
       <c r="B362" s="11"/>
       <c r="C362" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D362" s="11"/>
       <c r="E362" s="11" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G362" s="2"/>
       <c r="H362" s="2"/>
     </row>
     <row r="363" spans="1:8">
       <c r="A363" s="11" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B363" s="11"/>
       <c r="C363" s="11"/>
       <c r="D363" s="11"/>
       <c r="E363" s="11" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="G363" s="2"/>
       <c r="H363" s="2"/>
     </row>
     <row r="364" spans="1:8">
       <c r="A364" s="11" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="B364" s="11"/>
       <c r="C364" s="11" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="D364" s="11"/>
       <c r="E364" s="11" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="G364" s="2"/>
       <c r="H364" s="2"/>
@@ -11856,24 +11857,24 @@
       </c>
       <c r="B365" s="11"/>
       <c r="C365" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D365" s="11"/>
       <c r="E365" s="11" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="G365" s="2"/>
       <c r="H365" s="2"/>
     </row>
     <row r="366" spans="1:8">
       <c r="A366" s="11" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B366" s="11"/>
       <c r="C366" s="11"/>
       <c r="D366" s="11"/>
       <c r="E366" s="11" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="G366" s="2"/>
       <c r="H366" s="2"/>
@@ -11886,7 +11887,7 @@
       <c r="C367" s="11"/>
       <c r="D367" s="11"/>
       <c r="E367" s="11" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="G367" s="2"/>
       <c r="H367" s="2"/>
@@ -11899,7 +11900,7 @@
       <c r="C368" s="11"/>
       <c r="D368" s="11"/>
       <c r="E368" s="11" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="G368" s="2"/>
       <c r="H368" s="2"/>
@@ -11910,11 +11911,11 @@
       </c>
       <c r="B369" s="11"/>
       <c r="C369" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D369" s="11"/>
       <c r="E369" s="11" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="G369" s="2"/>
       <c r="H369" s="2"/>
@@ -11927,7 +11928,7 @@
       <c r="C370" s="11"/>
       <c r="D370" s="11"/>
       <c r="E370" s="11" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="G370" s="2"/>
       <c r="H370" s="2"/>
@@ -11951,18 +11952,18 @@
       </c>
       <c r="B372" s="11"/>
       <c r="C372" s="11" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="D372" s="11"/>
       <c r="E372" s="11" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="G372" s="2"/>
       <c r="H372" s="2"/>
     </row>
     <row r="373" spans="1:8">
       <c r="A373" s="11" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="B373" s="11"/>
       <c r="C373" s="11"/>
@@ -11983,7 +11984,7 @@
       <c r="C374" s="11"/>
       <c r="D374" s="11"/>
       <c r="E374" s="11" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="G374" s="2"/>
       <c r="H374" s="2"/>
@@ -11996,7 +11997,7 @@
       <c r="C375" s="11"/>
       <c r="D375" s="11"/>
       <c r="E375" s="11" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="G375" s="2"/>
       <c r="H375" s="2"/>
@@ -12020,11 +12021,11 @@
       </c>
       <c r="B377" s="11"/>
       <c r="C377" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D377" s="11"/>
       <c r="E377" s="11" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="G377" s="2"/>
       <c r="H377" s="2"/>
@@ -12035,11 +12036,11 @@
       </c>
       <c r="B378" s="11"/>
       <c r="C378" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D378" s="11"/>
       <c r="E378" s="11" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="G378" s="2"/>
       <c r="H378" s="2"/>
@@ -12050,11 +12051,11 @@
       </c>
       <c r="B379" s="11"/>
       <c r="C379" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D379" s="11"/>
       <c r="E379" s="11" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="G379" s="2"/>
       <c r="H379" s="2"/>
@@ -12065,11 +12066,11 @@
       </c>
       <c r="B380" s="11"/>
       <c r="C380" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D380" s="11"/>
       <c r="E380" s="11" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="G380" s="2"/>
       <c r="H380" s="2"/>
@@ -12080,11 +12081,11 @@
       </c>
       <c r="B381" s="11"/>
       <c r="C381" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D381" s="11"/>
       <c r="E381" s="11" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="G381" s="2"/>
       <c r="H381" s="2"/>
@@ -12097,7 +12098,7 @@
       <c r="C382" s="11"/>
       <c r="D382" s="11"/>
       <c r="E382" s="11" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="G382" s="2"/>
       <c r="H382" s="2"/>
@@ -12125,7 +12126,7 @@
       <c r="C384" s="11"/>
       <c r="D384" s="11"/>
       <c r="E384" s="11" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="G384" s="2"/>
       <c r="H384" s="2"/>
@@ -12151,14 +12152,14 @@
       <c r="C386" s="11"/>
       <c r="D386" s="11"/>
       <c r="E386" s="11" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="G386" s="2"/>
       <c r="H386" s="2"/>
     </row>
     <row r="387" spans="1:8">
       <c r="A387" s="11" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="B387" s="11"/>
       <c r="C387" s="11"/>
@@ -12166,7 +12167,7 @@
         <v>716</v>
       </c>
       <c r="E387" s="11" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="G387" s="2"/>
       <c r="H387" s="2"/>
@@ -12179,7 +12180,7 @@
       <c r="C388" s="11"/>
       <c r="D388" s="11"/>
       <c r="E388" s="11" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="G388" s="2"/>
       <c r="H388" s="2"/>
@@ -12190,7 +12191,7 @@
       </c>
       <c r="B389" s="11"/>
       <c r="C389" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D389" s="11"/>
       <c r="E389" s="11" t="s">
@@ -12205,11 +12206,11 @@
       </c>
       <c r="B390" s="11"/>
       <c r="C390" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D390" s="11"/>
       <c r="E390" s="11" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="G390" s="2"/>
       <c r="H390" s="2"/>
@@ -12229,7 +12230,7 @@
     </row>
     <row r="392" spans="1:8">
       <c r="A392" s="11" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="B392" s="11"/>
       <c r="C392" s="11"/>
@@ -12248,7 +12249,7 @@
       <c r="C393" s="11"/>
       <c r="D393" s="11"/>
       <c r="E393" s="11" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="G393" s="2"/>
       <c r="H393" s="2"/>
@@ -12261,7 +12262,7 @@
       <c r="C394" s="11"/>
       <c r="D394" s="11"/>
       <c r="E394" s="11" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G394" s="2"/>
       <c r="H394" s="2"/>
@@ -12272,11 +12273,11 @@
       </c>
       <c r="B395" s="11"/>
       <c r="C395" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D395" s="11"/>
       <c r="E395" s="11" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="G395" s="2"/>
       <c r="H395" s="2"/>
@@ -12296,7 +12297,7 @@
     </row>
     <row r="397" spans="1:8">
       <c r="A397" s="11" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="B397" s="11"/>
       <c r="C397" s="11"/>
@@ -12326,11 +12327,11 @@
       </c>
       <c r="B399" s="11"/>
       <c r="C399" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D399" s="11"/>
       <c r="E399" s="11" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="G399" s="2"/>
       <c r="H399" s="2"/>
@@ -12341,11 +12342,11 @@
       </c>
       <c r="B400" s="11"/>
       <c r="C400" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D400" s="11"/>
       <c r="E400" s="11" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="G400" s="2"/>
       <c r="H400" s="2"/>
@@ -12358,7 +12359,7 @@
       <c r="C401" s="11"/>
       <c r="D401" s="11"/>
       <c r="E401" s="11" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="G401" s="2"/>
       <c r="H401" s="2"/>
@@ -12371,20 +12372,20 @@
       <c r="C402" s="11"/>
       <c r="D402" s="11"/>
       <c r="E402" s="11" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="G402" s="2"/>
       <c r="H402" s="2"/>
     </row>
     <row r="403" spans="1:8">
       <c r="A403" s="11" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B403" s="11"/>
       <c r="C403" s="11"/>
       <c r="D403" s="11"/>
       <c r="E403" s="11" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="G403" s="2"/>
       <c r="H403" s="2"/>
@@ -12397,20 +12398,20 @@
       <c r="C404" s="11"/>
       <c r="D404" s="11"/>
       <c r="E404" s="11" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="G404" s="2"/>
       <c r="H404" s="2"/>
     </row>
     <row r="405" spans="1:8">
       <c r="A405" s="11" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="B405" s="11"/>
       <c r="C405" s="11"/>
       <c r="D405" s="11"/>
       <c r="E405" s="11" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="G405" s="2"/>
       <c r="H405" s="2"/>
@@ -12423,35 +12424,35 @@
       <c r="C406" s="11"/>
       <c r="D406" s="11"/>
       <c r="E406" s="11" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="G406" s="2"/>
       <c r="H406" s="2"/>
     </row>
     <row r="407" spans="1:8">
       <c r="A407" s="11" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="B407" s="11"/>
       <c r="C407" s="11"/>
       <c r="D407" s="11"/>
       <c r="E407" s="11" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="G407" s="2"/>
       <c r="H407" s="2"/>
     </row>
     <row r="408" spans="1:8">
       <c r="A408" s="11" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B408" s="11"/>
       <c r="C408" s="11"/>
       <c r="D408" s="14" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E408" s="11" t="s">
         <v>1013</v>
-      </c>
-      <c r="E408" s="11" t="s">
-        <v>1014</v>
       </c>
       <c r="G408" s="2"/>
       <c r="H408" s="2"/>
@@ -12464,7 +12465,7 @@
       <c r="C409" s="11"/>
       <c r="D409" s="11"/>
       <c r="E409" s="11" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="G409" s="2"/>
       <c r="H409" s="2"/>
@@ -12477,7 +12478,7 @@
       <c r="C410" s="11"/>
       <c r="D410" s="11"/>
       <c r="E410" s="11" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="G410" s="2"/>
       <c r="H410" s="2"/>
@@ -12490,7 +12491,7 @@
       <c r="C411" s="11"/>
       <c r="D411" s="11"/>
       <c r="E411" s="11" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="G411" s="2"/>
       <c r="H411" s="2"/>
@@ -12505,7 +12506,7 @@
         <v>717</v>
       </c>
       <c r="E412" s="11" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="G412" s="2"/>
       <c r="H412" s="2"/>
@@ -12516,11 +12517,11 @@
       </c>
       <c r="B413" s="11"/>
       <c r="C413" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D413" s="11"/>
       <c r="E413" s="11" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="G413" s="2"/>
       <c r="H413" s="2"/>
@@ -12533,7 +12534,7 @@
       <c r="C414" s="11"/>
       <c r="D414" s="11"/>
       <c r="E414" s="11" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="G414" s="2"/>
       <c r="H414" s="2"/>
@@ -12553,13 +12554,13 @@
     </row>
     <row r="416" spans="1:8">
       <c r="A416" s="11" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B416" s="11"/>
       <c r="C416" s="11"/>
       <c r="D416" s="11"/>
       <c r="E416" s="11" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="G416" s="2"/>
       <c r="H416" s="2"/>
@@ -12570,11 +12571,11 @@
       </c>
       <c r="B417" s="11"/>
       <c r="C417" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D417" s="11"/>
       <c r="E417" s="11" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="G417" s="2"/>
       <c r="H417" s="2"/>
@@ -12585,11 +12586,11 @@
       </c>
       <c r="B418" s="11"/>
       <c r="C418" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D418" s="11"/>
       <c r="E418" s="11" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="G418" s="2"/>
       <c r="H418" s="2"/>
@@ -12600,11 +12601,11 @@
       </c>
       <c r="B419" s="11"/>
       <c r="C419" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D419" s="11"/>
       <c r="E419" s="11" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="G419" s="2"/>
       <c r="H419" s="2"/>
@@ -12615,11 +12616,11 @@
       </c>
       <c r="B420" s="11"/>
       <c r="C420" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D420" s="11"/>
       <c r="E420" s="11" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="G420" s="2"/>
       <c r="H420" s="2"/>
@@ -12630,11 +12631,11 @@
       </c>
       <c r="B421" s="11"/>
       <c r="C421" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D421" s="11"/>
       <c r="E421" s="11" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="G421" s="2"/>
       <c r="H421" s="2"/>
@@ -12645,11 +12646,11 @@
       </c>
       <c r="B422" s="11"/>
       <c r="C422" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D422" s="11"/>
       <c r="E422" s="11" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="G422" s="2"/>
       <c r="H422" s="2"/>
@@ -12660,11 +12661,11 @@
       </c>
       <c r="B423" s="11"/>
       <c r="C423" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D423" s="11"/>
       <c r="E423" s="11" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="G423" s="2"/>
       <c r="H423" s="2"/>
@@ -12675,7 +12676,7 @@
       </c>
       <c r="B424" s="11"/>
       <c r="C424" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D424" s="11"/>
       <c r="E424" s="11" t="s">
@@ -12690,11 +12691,11 @@
       </c>
       <c r="B425" s="11"/>
       <c r="C425" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D425" s="11"/>
       <c r="E425" s="11" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="G425" s="2"/>
       <c r="H425" s="2"/>
@@ -12707,7 +12708,7 @@
       <c r="C426" s="11"/>
       <c r="D426" s="11"/>
       <c r="E426" s="11" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="G426" s="2"/>
       <c r="H426" s="2"/>
@@ -12718,11 +12719,11 @@
       </c>
       <c r="B427" s="11"/>
       <c r="C427" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D427" s="11"/>
       <c r="E427" s="11" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="G427" s="2"/>
       <c r="H427" s="2"/>
@@ -12733,21 +12734,21 @@
       </c>
       <c r="B428" s="11"/>
       <c r="C428" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D428" s="11"/>
       <c r="E428" s="11" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="G428" s="2"/>
       <c r="H428" s="2"/>
     </row>
     <row r="429" spans="1:8">
       <c r="A429" s="11" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B429" s="11" t="s">
         <v>1814</v>
-      </c>
-      <c r="B429" s="11" t="s">
-        <v>1815</v>
       </c>
       <c r="C429" s="11"/>
       <c r="D429" s="11"/>
@@ -12763,11 +12764,11 @@
       </c>
       <c r="B430" s="11"/>
       <c r="C430" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D430" s="11"/>
       <c r="E430" s="11" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="G430" s="2"/>
       <c r="H430" s="2"/>
@@ -12778,11 +12779,11 @@
       </c>
       <c r="B431" s="11"/>
       <c r="C431" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D431" s="11"/>
       <c r="E431" s="11" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="G431" s="2"/>
       <c r="H431" s="2"/>
@@ -12804,15 +12805,15 @@
     </row>
     <row r="433" spans="1:8">
       <c r="A433" s="11" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="B433" s="11"/>
       <c r="C433" s="11"/>
       <c r="D433" s="14" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="E433" s="11" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="G433" s="2"/>
       <c r="H433" s="2"/>
@@ -12823,11 +12824,11 @@
       </c>
       <c r="B434" s="11"/>
       <c r="C434" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D434" s="11"/>
       <c r="E434" s="11" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="G434" s="2"/>
       <c r="H434" s="2"/>
@@ -12842,7 +12843,7 @@
         <v>718</v>
       </c>
       <c r="E435" s="11" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="G435" s="2"/>
       <c r="H435" s="2"/>
@@ -12855,14 +12856,14 @@
       <c r="C436" s="11"/>
       <c r="D436" s="11"/>
       <c r="E436" s="11" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="G436" s="2"/>
       <c r="H436" s="2"/>
     </row>
     <row r="437" spans="1:8">
       <c r="A437" s="11" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="B437" s="11"/>
       <c r="C437" s="11"/>
@@ -12879,11 +12880,11 @@
       </c>
       <c r="B438" s="11"/>
       <c r="C438" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D438" s="11"/>
       <c r="E438" s="11" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="G438" s="2"/>
       <c r="H438" s="2"/>
@@ -12894,11 +12895,11 @@
       </c>
       <c r="B439" s="11"/>
       <c r="C439" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D439" s="11"/>
       <c r="E439" s="11" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="G439" s="2"/>
       <c r="H439" s="2"/>
@@ -12909,11 +12910,11 @@
       </c>
       <c r="B440" s="11"/>
       <c r="C440" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D440" s="11"/>
       <c r="E440" s="11" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="G440" s="2"/>
       <c r="H440" s="2"/>
@@ -12948,43 +12949,43 @@
     </row>
     <row r="443" spans="1:8">
       <c r="A443" s="11" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="B443" s="11"/>
       <c r="C443" s="11"/>
       <c r="D443" s="11"/>
       <c r="E443" s="11" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="G443" s="2"/>
       <c r="H443" s="2"/>
     </row>
     <row r="444" spans="1:8">
       <c r="A444" s="11" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="B444" s="11"/>
       <c r="C444" s="11"/>
       <c r="D444" s="11"/>
       <c r="E444" s="11" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="G444" s="2"/>
       <c r="H444" s="2"/>
     </row>
     <row r="445" spans="1:8">
       <c r="A445" s="11" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B445" s="11" t="s">
         <v>1817</v>
       </c>
-      <c r="B445" s="11" t="s">
+      <c r="C445" s="11" t="s">
         <v>1818</v>
-      </c>
-      <c r="C445" s="11" t="s">
-        <v>1819</v>
       </c>
       <c r="D445" s="11"/>
       <c r="E445" s="11" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="G445" s="2"/>
       <c r="H445" s="2"/>
@@ -12995,11 +12996,11 @@
       </c>
       <c r="B446" s="11"/>
       <c r="C446" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D446" s="11"/>
       <c r="E446" s="11" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="G446" s="2"/>
       <c r="H446" s="2"/>
@@ -13010,11 +13011,11 @@
       </c>
       <c r="B447" s="11"/>
       <c r="C447" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D447" s="11"/>
       <c r="E447" s="11" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="G447" s="2"/>
       <c r="H447" s="2"/>
@@ -13029,7 +13030,7 @@
         <v>719</v>
       </c>
       <c r="E448" s="11" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="G448" s="2"/>
       <c r="H448" s="2"/>
@@ -13040,11 +13041,11 @@
       </c>
       <c r="B449" s="11"/>
       <c r="C449" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D449" s="11"/>
       <c r="E449" s="11" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="G449" s="2"/>
       <c r="H449" s="2"/>
@@ -13057,7 +13058,7 @@
       <c r="C450" s="11"/>
       <c r="D450" s="11"/>
       <c r="E450" s="11" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="G450" s="2"/>
       <c r="H450" s="2"/>
@@ -13070,14 +13071,14 @@
       <c r="C451" s="11"/>
       <c r="D451" s="11"/>
       <c r="E451" s="11" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="G451" s="2"/>
       <c r="H451" s="2"/>
     </row>
     <row r="452" spans="1:8">
       <c r="A452" s="11" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="B452" s="11"/>
       <c r="C452" s="11"/>
@@ -13094,11 +13095,11 @@
       </c>
       <c r="B453" s="11"/>
       <c r="C453" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D453" s="11"/>
       <c r="E453" s="11" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="G453" s="2"/>
       <c r="H453" s="2"/>
@@ -13111,14 +13112,14 @@
       <c r="C454" s="11"/>
       <c r="D454" s="11"/>
       <c r="E454" s="11" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="G454" s="2"/>
       <c r="H454" s="2"/>
     </row>
     <row r="455" spans="1:8">
       <c r="A455" s="11" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="B455" s="11"/>
       <c r="C455" s="11" t="s">
@@ -13126,7 +13127,7 @@
       </c>
       <c r="D455" s="11"/>
       <c r="E455" s="11" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="G455" s="2"/>
       <c r="H455" s="2"/>
@@ -13139,7 +13140,7 @@
       <c r="C456" s="11"/>
       <c r="D456" s="11"/>
       <c r="E456" s="11" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="G456" s="2"/>
       <c r="H456" s="2"/>
@@ -13150,7 +13151,7 @@
       </c>
       <c r="B457" s="11"/>
       <c r="C457" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D457" s="11"/>
       <c r="E457" s="11" t="s">
@@ -13161,13 +13162,13 @@
     </row>
     <row r="458" spans="1:8">
       <c r="A458" s="11" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="B458" s="11"/>
       <c r="C458" s="11"/>
       <c r="D458" s="11"/>
       <c r="E458" s="11" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="G458" s="2"/>
       <c r="H458" s="2"/>
@@ -13178,11 +13179,11 @@
       </c>
       <c r="B459" s="11"/>
       <c r="C459" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D459" s="11"/>
       <c r="E459" s="11" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="G459" s="2"/>
       <c r="H459" s="2"/>
@@ -13195,24 +13196,24 @@
       <c r="C460" s="11"/>
       <c r="D460" s="11"/>
       <c r="E460" s="11" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="G460" s="2"/>
       <c r="H460" s="2"/>
     </row>
     <row r="461" spans="1:8">
       <c r="A461" s="11" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="B461" s="11"/>
       <c r="C461" s="11" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="D461" s="11" t="s">
         <v>746</v>
       </c>
       <c r="E461" s="11" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="G461" s="2"/>
       <c r="H461" s="2"/>
@@ -13240,7 +13241,7 @@
         <v>720</v>
       </c>
       <c r="E463" s="11" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="G463" s="2"/>
       <c r="H463" s="2"/>
@@ -13266,7 +13267,7 @@
       <c r="C465" s="11"/>
       <c r="D465" s="11"/>
       <c r="E465" s="11" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="G465" s="2"/>
       <c r="H465" s="2"/>
@@ -13279,7 +13280,7 @@
       <c r="C466" s="11"/>
       <c r="D466" s="11"/>
       <c r="E466" s="11" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="G466" s="2"/>
       <c r="H466" s="2"/>
@@ -13290,11 +13291,11 @@
       </c>
       <c r="B467" s="11"/>
       <c r="C467" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D467" s="11"/>
       <c r="E467" s="11" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="G467" s="2"/>
       <c r="H467" s="2"/>
@@ -13307,17 +13308,17 @@
       <c r="C468" s="11"/>
       <c r="D468" s="11"/>
       <c r="E468" s="11" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="G468" s="2"/>
       <c r="H468" s="2"/>
     </row>
     <row r="469" spans="1:8">
       <c r="A469" s="11" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B469" s="11" t="s">
         <v>1778</v>
-      </c>
-      <c r="B469" s="11" t="s">
-        <v>1779</v>
       </c>
       <c r="C469" s="11"/>
       <c r="D469" s="11" t="s">
@@ -13335,11 +13336,11 @@
       </c>
       <c r="B470" s="11"/>
       <c r="C470" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D470" s="11"/>
       <c r="E470" s="11" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="G470" s="2"/>
       <c r="H470" s="2"/>
@@ -13352,7 +13353,7 @@
       <c r="C471" s="11"/>
       <c r="D471" s="11"/>
       <c r="E471" s="11" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="G471" s="2"/>
       <c r="H471" s="2"/>
@@ -13363,18 +13364,18 @@
       </c>
       <c r="B472" s="11"/>
       <c r="C472" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D472" s="11"/>
       <c r="E472" s="11" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="G472" s="2"/>
       <c r="H472" s="2"/>
     </row>
     <row r="473" spans="1:8">
       <c r="A473" s="11" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="B473" s="11"/>
       <c r="C473" s="11" t="s">
@@ -13382,14 +13383,14 @@
       </c>
       <c r="D473" s="11"/>
       <c r="E473" s="11" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="G473" s="2"/>
       <c r="H473" s="2"/>
     </row>
     <row r="474" spans="1:8">
       <c r="A474" s="11" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="B474" s="11"/>
       <c r="C474" s="11"/>
@@ -13397,7 +13398,7 @@
         <v>721</v>
       </c>
       <c r="E474" s="11" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="G474" s="2"/>
       <c r="H474" s="2"/>
@@ -13410,22 +13411,22 @@
       <c r="C475" s="11"/>
       <c r="D475" s="11"/>
       <c r="E475" s="11" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="G475" s="2"/>
       <c r="H475" s="2"/>
     </row>
     <row r="476" spans="1:8">
       <c r="A476" s="11" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="B476" s="11"/>
       <c r="C476" s="11"/>
       <c r="D476" s="14" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E476" s="11" t="s">
         <v>1411</v>
-      </c>
-      <c r="E476" s="11" t="s">
-        <v>1412</v>
       </c>
       <c r="G476" s="2"/>
       <c r="H476" s="2"/>
@@ -13437,10 +13438,10 @@
       <c r="B477" s="11"/>
       <c r="C477" s="11"/>
       <c r="D477" s="11" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E477" s="11" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="G477" s="2"/>
       <c r="H477" s="2"/>
@@ -13455,7 +13456,7 @@
         <v>722</v>
       </c>
       <c r="E478" s="11" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="G478" s="2"/>
       <c r="H478" s="2"/>
@@ -13466,10 +13467,10 @@
       </c>
       <c r="B479" s="11"/>
       <c r="C479" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D479" s="11" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E479" s="11" t="s">
         <v>240</v>
@@ -13483,13 +13484,13 @@
       </c>
       <c r="B480" s="11"/>
       <c r="C480" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D480" s="14" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E480" s="11" t="s">
         <v>1408</v>
-      </c>
-      <c r="E480" s="11" t="s">
-        <v>1409</v>
       </c>
       <c r="G480" s="2"/>
       <c r="H480" s="2"/>
@@ -13502,7 +13503,7 @@
       <c r="C481" s="11"/>
       <c r="D481" s="11"/>
       <c r="E481" s="11" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="G481" s="2"/>
       <c r="H481" s="2"/>
@@ -13514,7 +13515,7 @@
       <c r="B482" s="11"/>
       <c r="C482" s="11"/>
       <c r="D482" s="11" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E482" s="11" t="s">
         <v>865</v>
@@ -13524,15 +13525,15 @@
     </row>
     <row r="483" spans="1:8">
       <c r="A483" s="11" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="B483" s="11"/>
       <c r="C483" s="11" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="D483" s="11"/>
       <c r="E483" s="11" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="G483" s="2"/>
       <c r="H483" s="2"/>
@@ -13545,7 +13546,7 @@
       <c r="C484" s="11"/>
       <c r="D484" s="11"/>
       <c r="E484" s="11" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="G484" s="2"/>
       <c r="H484" s="2"/>
@@ -13558,7 +13559,7 @@
       <c r="C485" s="11"/>
       <c r="D485" s="11"/>
       <c r="E485" s="11" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G485" s="2"/>
       <c r="H485" s="2"/>
@@ -13571,7 +13572,7 @@
       <c r="C486" s="11"/>
       <c r="D486" s="11"/>
       <c r="E486" s="11" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="G486" s="2"/>
       <c r="H486" s="2"/>
@@ -13582,11 +13583,11 @@
       </c>
       <c r="B487" s="11"/>
       <c r="C487" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D487" s="11"/>
       <c r="E487" s="11" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="G487" s="2"/>
       <c r="H487" s="2"/>
@@ -13597,11 +13598,11 @@
       </c>
       <c r="B488" s="11"/>
       <c r="C488" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D488" s="11"/>
       <c r="E488" s="11" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="G488" s="2"/>
       <c r="H488" s="2"/>
@@ -13612,11 +13613,11 @@
       </c>
       <c r="B489" s="11"/>
       <c r="C489" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D489" s="11"/>
       <c r="E489" s="11" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="G489" s="2"/>
       <c r="H489" s="2"/>
@@ -13627,11 +13628,11 @@
       </c>
       <c r="B490" s="11"/>
       <c r="C490" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D490" s="11"/>
       <c r="E490" s="11" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="G490" s="2"/>
       <c r="H490" s="2"/>
@@ -13644,22 +13645,22 @@
       <c r="C491" s="11"/>
       <c r="D491" s="11"/>
       <c r="E491" s="11" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="G491" s="2"/>
       <c r="H491" s="2"/>
     </row>
     <row r="492" spans="1:8">
       <c r="A492" s="11" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="B492" s="11"/>
       <c r="C492" s="11" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="D492" s="11"/>
       <c r="E492" s="11" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="G492" s="2"/>
       <c r="H492" s="2"/>
@@ -13672,18 +13673,18 @@
       <c r="C493" s="11"/>
       <c r="D493" s="11"/>
       <c r="E493" s="11" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="G493" s="2"/>
       <c r="H493" s="2"/>
     </row>
     <row r="494" spans="1:8">
       <c r="A494" s="11" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="B494" s="11"/>
       <c r="C494" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D494" s="11"/>
       <c r="E494" s="11"/>
@@ -13698,7 +13699,7 @@
       <c r="C495" s="11"/>
       <c r="D495" s="11"/>
       <c r="E495" s="11" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="G495" s="2"/>
       <c r="H495" s="2"/>
@@ -13711,14 +13712,14 @@
       <c r="C496" s="11"/>
       <c r="D496" s="11"/>
       <c r="E496" s="11" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="G496" s="2"/>
       <c r="H496" s="2"/>
     </row>
     <row r="497" spans="1:8">
       <c r="A497" s="11" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B497" s="11"/>
       <c r="C497" s="11"/>
@@ -13737,7 +13738,7 @@
       <c r="C498" s="11"/>
       <c r="D498" s="11"/>
       <c r="E498" s="11" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="G498" s="2"/>
       <c r="H498" s="2"/>
@@ -13752,7 +13753,7 @@
         <v>723</v>
       </c>
       <c r="E499" s="11" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="G499" s="2"/>
       <c r="H499" s="2"/>
@@ -13765,20 +13766,20 @@
       <c r="C500" s="11"/>
       <c r="D500" s="11"/>
       <c r="E500" s="11" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="G500" s="2"/>
       <c r="H500" s="2"/>
     </row>
     <row r="501" spans="1:8">
       <c r="A501" s="11" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B501" s="11"/>
       <c r="C501" s="11"/>
       <c r="D501" s="11"/>
       <c r="E501" s="11" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="G501" s="2"/>
       <c r="H501" s="2"/>
@@ -13791,7 +13792,7 @@
       <c r="C502" s="11"/>
       <c r="D502" s="11"/>
       <c r="E502" s="11" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="G502" s="2"/>
       <c r="H502" s="2"/>
@@ -13804,7 +13805,7 @@
       <c r="C503" s="11"/>
       <c r="D503" s="11"/>
       <c r="E503" s="11" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="G503" s="2"/>
       <c r="H503" s="2"/>
@@ -13817,7 +13818,7 @@
       <c r="C504" s="11"/>
       <c r="D504" s="11"/>
       <c r="E504" s="11" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G504" s="2"/>
       <c r="H504" s="2"/>
@@ -13828,11 +13829,11 @@
       </c>
       <c r="B505" s="11"/>
       <c r="C505" s="11" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="D505" s="11"/>
       <c r="E505" s="11" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="G505" s="2"/>
       <c r="H505" s="2"/>
@@ -13845,14 +13846,14 @@
       <c r="C506" s="11"/>
       <c r="D506" s="11"/>
       <c r="E506" s="11" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="G506" s="2"/>
       <c r="H506" s="2"/>
     </row>
     <row r="507" spans="1:8">
       <c r="A507" s="11" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B507" s="11"/>
       <c r="C507" s="11"/>
@@ -13865,7 +13866,7 @@
     </row>
     <row r="508" spans="1:8">
       <c r="A508" s="11" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B508" s="11"/>
       <c r="C508" s="11"/>
@@ -13878,26 +13879,26 @@
     </row>
     <row r="509" spans="1:8">
       <c r="A509" s="11" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B509" s="11"/>
       <c r="C509" s="11"/>
       <c r="D509" s="11"/>
       <c r="E509" s="11" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="G509" s="2"/>
       <c r="H509" s="2"/>
     </row>
     <row r="510" spans="1:8">
       <c r="A510" s="11" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="B510" s="11"/>
       <c r="C510" s="11"/>
       <c r="D510" s="11"/>
       <c r="E510" s="11" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="G510" s="2"/>
       <c r="H510" s="2"/>
@@ -13908,18 +13909,18 @@
       </c>
       <c r="B511" s="11"/>
       <c r="C511" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D511" s="11"/>
       <c r="E511" s="11" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="G511" s="2"/>
       <c r="H511" s="2"/>
     </row>
     <row r="512" spans="1:8">
       <c r="A512" s="11" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="B512" s="11"/>
       <c r="C512" s="11"/>
@@ -13934,26 +13935,26 @@
     </row>
     <row r="513" spans="1:8">
       <c r="A513" s="11" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="B513" s="11"/>
       <c r="C513" s="11"/>
       <c r="D513" s="11"/>
       <c r="E513" s="11" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="G513" s="2"/>
       <c r="H513" s="2"/>
     </row>
     <row r="514" spans="1:8">
       <c r="A514" s="11" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="B514" s="11"/>
       <c r="C514" s="11"/>
       <c r="D514" s="11"/>
       <c r="E514" s="11" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="G514" s="2"/>
       <c r="H514" s="2"/>
@@ -13966,7 +13967,7 @@
       <c r="C515" s="11"/>
       <c r="D515" s="11"/>
       <c r="E515" s="11" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="G515" s="2"/>
       <c r="H515" s="2"/>
@@ -13979,7 +13980,7 @@
       <c r="C516" s="11"/>
       <c r="D516" s="11"/>
       <c r="E516" s="11" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="G516" s="2"/>
       <c r="H516" s="2"/>
@@ -13992,7 +13993,7 @@
       <c r="C517" s="11"/>
       <c r="D517" s="11"/>
       <c r="E517" s="11" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="G517" s="2"/>
       <c r="H517" s="2"/>
@@ -14018,7 +14019,7 @@
       <c r="C519" s="11"/>
       <c r="D519" s="11"/>
       <c r="E519" s="11" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G519" s="2"/>
       <c r="H519" s="2"/>
@@ -14046,7 +14047,7 @@
       <c r="C521" s="11"/>
       <c r="D521" s="11"/>
       <c r="E521" s="11" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="G521" s="2"/>
       <c r="H521" s="2"/>
@@ -14057,11 +14058,11 @@
       </c>
       <c r="B522" s="11"/>
       <c r="C522" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D522" s="11"/>
       <c r="E522" s="11" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="G522" s="2"/>
       <c r="H522" s="2"/>
@@ -14072,11 +14073,11 @@
       </c>
       <c r="B523" s="11"/>
       <c r="C523" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D523" s="11"/>
       <c r="E523" s="11" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G523" s="2"/>
       <c r="H523" s="2"/>
@@ -14087,11 +14088,11 @@
       </c>
       <c r="B524" s="11"/>
       <c r="C524" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D524" s="11"/>
       <c r="E524" s="11" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="G524" s="2"/>
       <c r="H524" s="2"/>
@@ -14102,11 +14103,11 @@
       </c>
       <c r="B525" s="11"/>
       <c r="C525" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D525" s="11"/>
       <c r="E525" s="11" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G525" s="2"/>
       <c r="H525" s="2"/>
@@ -14117,11 +14118,11 @@
       </c>
       <c r="B526" s="11"/>
       <c r="C526" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D526" s="11"/>
       <c r="E526" s="11" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="G526" s="2"/>
       <c r="H526" s="2"/>
@@ -14147,7 +14148,7 @@
       <c r="C528" s="11"/>
       <c r="D528" s="11"/>
       <c r="E528" s="11" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="G528" s="2"/>
       <c r="H528" s="2"/>
@@ -14160,7 +14161,7 @@
       <c r="C529" s="11"/>
       <c r="D529" s="11"/>
       <c r="E529" s="11" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="G529" s="2"/>
       <c r="H529" s="2"/>
@@ -14171,11 +14172,11 @@
       </c>
       <c r="B530" s="11"/>
       <c r="C530" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D530" s="11"/>
       <c r="E530" s="11" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G530" s="2"/>
       <c r="H530" s="2"/>
@@ -14186,11 +14187,11 @@
       </c>
       <c r="B531" s="11"/>
       <c r="C531" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D531" s="11"/>
       <c r="E531" s="11" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="G531" s="2"/>
       <c r="H531" s="2"/>
@@ -14203,7 +14204,7 @@
       <c r="C532" s="11"/>
       <c r="D532" s="11"/>
       <c r="E532" s="11" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="G532" s="2"/>
       <c r="H532" s="2"/>
@@ -14223,13 +14224,13 @@
     </row>
     <row r="534" spans="1:8">
       <c r="A534" s="11" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="B534" s="11"/>
       <c r="C534" s="11"/>
       <c r="D534" s="11"/>
       <c r="E534" s="11" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="G534" s="2"/>
       <c r="H534" s="2"/>
@@ -14257,7 +14258,7 @@
       <c r="C536" s="11"/>
       <c r="D536" s="11"/>
       <c r="E536" s="11" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="G536" s="2"/>
       <c r="H536" s="2"/>
@@ -14270,7 +14271,7 @@
       <c r="C537" s="11"/>
       <c r="D537" s="11"/>
       <c r="E537" s="11" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="G537" s="2"/>
       <c r="H537" s="2"/>
@@ -14281,11 +14282,11 @@
       </c>
       <c r="B538" s="11"/>
       <c r="C538" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D538" s="11"/>
       <c r="E538" s="11" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="G538" s="2"/>
       <c r="H538" s="2"/>
@@ -14296,24 +14297,24 @@
       </c>
       <c r="B539" s="11"/>
       <c r="C539" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D539" s="11"/>
       <c r="E539" s="11" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="G539" s="2"/>
       <c r="H539" s="2"/>
     </row>
     <row r="540" spans="1:8">
       <c r="A540" s="11" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B540" s="11"/>
       <c r="C540" s="11"/>
       <c r="D540" s="11"/>
       <c r="E540" s="11" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="G540" s="2"/>
       <c r="H540" s="2"/>
@@ -14324,13 +14325,13 @@
       </c>
       <c r="B541" s="11"/>
       <c r="C541" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D541" s="11" t="s">
         <v>724</v>
       </c>
       <c r="E541" s="11" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="G541" s="2"/>
       <c r="H541" s="2"/>
@@ -14343,20 +14344,20 @@
       <c r="C542" s="11"/>
       <c r="D542" s="11"/>
       <c r="E542" s="11" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="G542" s="2"/>
       <c r="H542" s="2"/>
     </row>
     <row r="543" spans="1:8">
       <c r="A543" s="11" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B543" s="11"/>
       <c r="C543" s="11"/>
       <c r="D543" s="11"/>
       <c r="E543" s="11" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="G543" s="2"/>
       <c r="H543" s="2"/>
@@ -14369,7 +14370,7 @@
       <c r="C544" s="11"/>
       <c r="D544" s="11"/>
       <c r="E544" s="11" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="G544" s="2"/>
       <c r="H544" s="2"/>
@@ -14382,7 +14383,7 @@
       <c r="C545" s="11"/>
       <c r="D545" s="11"/>
       <c r="E545" s="11" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="G545" s="2"/>
       <c r="H545" s="2"/>
@@ -14397,14 +14398,14 @@
         <v>725</v>
       </c>
       <c r="E546" s="11" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="G546" s="2"/>
       <c r="H546" s="2"/>
     </row>
     <row r="547" spans="1:8">
       <c r="A547" s="11" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="B547" s="11"/>
       <c r="C547" s="11"/>
@@ -14412,7 +14413,7 @@
         <v>726</v>
       </c>
       <c r="E547" s="11" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="G547" s="2"/>
       <c r="H547" s="2"/>
@@ -14434,47 +14435,47 @@
     </row>
     <row r="549" spans="1:8">
       <c r="A549" s="11" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="B549" s="11"/>
       <c r="C549" s="11"/>
       <c r="D549" s="11"/>
       <c r="E549" s="11" t="s">
-        <v>877</v>
+        <v>1836</v>
       </c>
       <c r="G549" s="2"/>
       <c r="H549" s="2"/>
     </row>
     <row r="550" spans="1:8">
       <c r="A550" s="11" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B550" s="11"/>
       <c r="C550" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D550" s="11" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E550" s="11" t="s">
         <v>1481</v>
-      </c>
-      <c r="E550" s="11" t="s">
-        <v>1482</v>
       </c>
       <c r="G550" s="2"/>
       <c r="H550" s="2"/>
     </row>
     <row r="551" spans="1:8">
       <c r="A551" s="11" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="B551" s="11"/>
       <c r="C551" s="11" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D551" s="11" t="s">
         <v>1483</v>
       </c>
-      <c r="D551" s="11" t="s">
+      <c r="E551" s="11" t="s">
         <v>1484</v>
-      </c>
-      <c r="E551" s="11" t="s">
-        <v>1485</v>
       </c>
       <c r="G551" s="2"/>
       <c r="H551" s="2"/>
@@ -14487,22 +14488,22 @@
       <c r="C552" s="11"/>
       <c r="D552" s="11"/>
       <c r="E552" s="11" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="G552" s="2"/>
       <c r="H552" s="2"/>
     </row>
     <row r="553" spans="1:8">
       <c r="A553" s="11" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="B553" s="11"/>
       <c r="C553" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D553" s="11"/>
       <c r="E553" s="11" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="G553" s="2"/>
       <c r="H553" s="2"/>
@@ -14515,7 +14516,7 @@
       <c r="C554" s="11"/>
       <c r="D554" s="11"/>
       <c r="E554" s="11" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="G554" s="2"/>
       <c r="H554" s="2"/>
@@ -14528,7 +14529,7 @@
       <c r="C555" s="11"/>
       <c r="D555" s="11"/>
       <c r="E555" s="11" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="G555" s="2"/>
       <c r="H555" s="2"/>
@@ -14541,7 +14542,7 @@
       <c r="C556" s="11"/>
       <c r="D556" s="11"/>
       <c r="E556" s="11" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="G556" s="2"/>
       <c r="H556" s="2"/>
@@ -14552,11 +14553,11 @@
       </c>
       <c r="B557" s="11"/>
       <c r="C557" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D557" s="11"/>
       <c r="E557" s="11" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="G557" s="2"/>
       <c r="H557" s="2"/>
@@ -14567,13 +14568,13 @@
       </c>
       <c r="B558" s="11"/>
       <c r="C558" s="11" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="D558" s="11" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E558" s="11" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="G558" s="2"/>
       <c r="H558" s="2"/>
@@ -14584,11 +14585,11 @@
       </c>
       <c r="B559" s="11"/>
       <c r="C559" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D559" s="11"/>
       <c r="E559" s="11" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="G559" s="2"/>
       <c r="H559" s="2"/>
@@ -14599,11 +14600,11 @@
       </c>
       <c r="B560" s="11"/>
       <c r="C560" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D560" s="11"/>
       <c r="E560" s="11" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="G560" s="2"/>
       <c r="H560" s="2"/>
@@ -14616,7 +14617,7 @@
       <c r="C561" s="11"/>
       <c r="D561" s="11"/>
       <c r="E561" s="11" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="G561" s="2"/>
       <c r="H561" s="2"/>
@@ -14627,11 +14628,11 @@
       </c>
       <c r="B562" s="11"/>
       <c r="C562" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D562" s="11"/>
       <c r="E562" s="11" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="G562" s="2"/>
       <c r="H562" s="2"/>
@@ -14642,11 +14643,11 @@
       </c>
       <c r="B563" s="11"/>
       <c r="C563" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D563" s="11"/>
       <c r="E563" s="11" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="G563" s="2"/>
       <c r="H563" s="2"/>
@@ -14657,26 +14658,26 @@
       </c>
       <c r="B564" s="11"/>
       <c r="C564" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D564" s="11"/>
       <c r="E564" s="11" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="G564" s="2"/>
       <c r="H564" s="2"/>
     </row>
     <row r="565" spans="1:8">
       <c r="A565" s="11" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="B565" s="11"/>
       <c r="C565" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D565" s="11"/>
       <c r="E565" s="11" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="G565" s="2"/>
       <c r="H565" s="2"/>
@@ -14687,11 +14688,11 @@
       </c>
       <c r="B566" s="11"/>
       <c r="C566" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D566" s="11"/>
       <c r="E566" s="11" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="G566" s="2"/>
       <c r="H566" s="2"/>
@@ -14704,7 +14705,7 @@
       <c r="C567" s="11"/>
       <c r="D567" s="11"/>
       <c r="E567" s="11" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="G567" s="2"/>
       <c r="H567" s="2"/>
@@ -14717,20 +14718,20 @@
       <c r="C568" s="11"/>
       <c r="D568" s="11"/>
       <c r="E568" s="11" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="G568" s="2"/>
       <c r="H568" s="2"/>
     </row>
     <row r="569" spans="1:8">
       <c r="A569" s="11" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="B569" s="11"/>
       <c r="C569" s="11"/>
       <c r="D569" s="11"/>
       <c r="E569" s="11" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="G569" s="2"/>
       <c r="H569" s="2"/>
@@ -14743,7 +14744,7 @@
       <c r="C570" s="11"/>
       <c r="D570" s="11"/>
       <c r="E570" s="11" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="G570" s="2"/>
       <c r="H570" s="2"/>
@@ -14754,7 +14755,7 @@
       </c>
       <c r="B571" s="11"/>
       <c r="C571" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D571" s="11"/>
       <c r="E571" s="11" t="s">
@@ -14771,7 +14772,7 @@
       <c r="C572" s="11"/>
       <c r="D572" s="11"/>
       <c r="E572" s="11" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="G572" s="2"/>
       <c r="H572" s="2"/>
@@ -14797,7 +14798,7 @@
       <c r="C574" s="11"/>
       <c r="D574" s="11"/>
       <c r="E574" s="11" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="G574" s="2"/>
       <c r="H574" s="2"/>
@@ -14823,7 +14824,7 @@
       <c r="C576" s="11"/>
       <c r="D576" s="11"/>
       <c r="E576" s="11" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="G576" s="2"/>
       <c r="H576" s="2"/>
@@ -14834,11 +14835,11 @@
       </c>
       <c r="B577" s="11"/>
       <c r="C577" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D577" s="11"/>
       <c r="E577" s="11" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="G577" s="2"/>
       <c r="H577" s="2"/>
@@ -14850,10 +14851,10 @@
       <c r="B578" s="11"/>
       <c r="C578" s="11"/>
       <c r="D578" s="11" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E578" s="11" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="G578" s="2"/>
       <c r="H578" s="2"/>
@@ -14866,7 +14867,7 @@
       <c r="C579" s="11"/>
       <c r="D579" s="11"/>
       <c r="E579" s="11" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="G579" s="2"/>
       <c r="H579" s="2"/>
@@ -14931,7 +14932,7 @@
       <c r="C584" s="11"/>
       <c r="D584" s="11"/>
       <c r="E584" s="11" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="G584" s="2"/>
       <c r="H584" s="2"/>
@@ -14956,10 +14957,10 @@
       <c r="B586" s="11"/>
       <c r="C586" s="11"/>
       <c r="D586" s="11" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E586" s="11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G586" s="2"/>
       <c r="H586" s="2"/>
@@ -14972,7 +14973,7 @@
       <c r="C587" s="11"/>
       <c r="D587" s="11"/>
       <c r="E587" s="11" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="G587" s="2"/>
       <c r="H587" s="2"/>
@@ -14985,7 +14986,7 @@
       <c r="C588" s="11"/>
       <c r="D588" s="11"/>
       <c r="E588" s="11" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="G588" s="2"/>
       <c r="H588" s="2"/>
@@ -15023,10 +15024,10 @@
       <c r="B591" s="11"/>
       <c r="C591" s="11"/>
       <c r="D591" s="11" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E591" s="11" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G591" s="2"/>
       <c r="H591" s="2"/>
@@ -15065,7 +15066,7 @@
       <c r="C594" s="11"/>
       <c r="D594" s="11"/>
       <c r="E594" s="11" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G594" s="2"/>
       <c r="H594" s="2"/>
@@ -15078,7 +15079,7 @@
       <c r="C595" s="11"/>
       <c r="D595" s="11"/>
       <c r="E595" s="11" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="G595" s="2"/>
       <c r="H595" s="2"/>
@@ -15098,13 +15099,13 @@
     </row>
     <row r="597" spans="1:8">
       <c r="A597" s="11" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="B597" s="11"/>
       <c r="C597" s="11"/>
       <c r="D597" s="11"/>
       <c r="E597" s="11" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="G597" s="2"/>
       <c r="H597" s="2"/>
@@ -15117,7 +15118,7 @@
       <c r="C598" s="11"/>
       <c r="D598" s="11"/>
       <c r="E598" s="11" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="G598" s="2"/>
       <c r="H598" s="2"/>
@@ -15130,7 +15131,7 @@
       <c r="C599" s="11"/>
       <c r="D599" s="11"/>
       <c r="E599" s="11" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="G599" s="2"/>
       <c r="H599" s="2"/>
@@ -15142,10 +15143,10 @@
       <c r="B600" s="11"/>
       <c r="C600" s="11"/>
       <c r="D600" s="11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E600" s="11" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G600" s="2"/>
       <c r="H600" s="2"/>
@@ -15157,10 +15158,10 @@
       <c r="B601" s="11"/>
       <c r="C601" s="11"/>
       <c r="D601" s="11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E601" s="11" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G601" s="2"/>
       <c r="H601" s="2"/>
@@ -15171,7 +15172,7 @@
       </c>
       <c r="B602" s="11"/>
       <c r="C602" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D602" s="11"/>
       <c r="E602" s="11" t="s">
@@ -15188,22 +15189,22 @@
       <c r="C603" s="11"/>
       <c r="D603" s="11"/>
       <c r="E603" s="11" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="G603" s="2"/>
       <c r="H603" s="2"/>
     </row>
     <row r="604" spans="1:8">
       <c r="A604" s="11" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B604" s="11"/>
       <c r="C604" s="11"/>
       <c r="D604" s="14" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E604" s="11" t="s">
         <v>1655</v>
-      </c>
-      <c r="E604" s="11" t="s">
-        <v>1656</v>
       </c>
       <c r="G604" s="2"/>
       <c r="H604" s="2"/>
@@ -15216,59 +15217,59 @@
       <c r="C605" s="11"/>
       <c r="D605" s="11"/>
       <c r="E605" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="G605" s="2"/>
       <c r="H605" s="2"/>
     </row>
     <row r="606" spans="1:8">
       <c r="A606" s="11" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="B606" s="11"/>
       <c r="C606" s="11"/>
       <c r="D606" s="11"/>
       <c r="E606" s="11" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="G606" s="2"/>
       <c r="H606" s="2"/>
     </row>
     <row r="607" spans="1:8">
       <c r="A607" s="11" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="B607" s="11"/>
       <c r="C607" s="11"/>
       <c r="D607" s="11"/>
       <c r="E607" s="11" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="G607" s="2"/>
       <c r="H607" s="2"/>
     </row>
     <row r="608" spans="1:8">
       <c r="A608" s="11" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="B608" s="11"/>
       <c r="C608" s="11"/>
       <c r="D608" s="11"/>
       <c r="E608" s="11" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="G608" s="2"/>
       <c r="H608" s="2"/>
     </row>
     <row r="609" spans="1:8">
       <c r="A609" s="11" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B609" s="11"/>
       <c r="C609" s="11"/>
       <c r="D609" s="11"/>
       <c r="E609" s="11" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="G609" s="2"/>
       <c r="H609" s="2"/>
@@ -15281,7 +15282,7 @@
       <c r="C610" s="11"/>
       <c r="D610" s="11"/>
       <c r="E610" s="11" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="G610" s="2"/>
       <c r="H610" s="2"/>
@@ -15294,7 +15295,7 @@
       <c r="C611" s="11"/>
       <c r="D611" s="11"/>
       <c r="E611" s="11" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="G611" s="2"/>
       <c r="H611" s="2"/>
@@ -15307,7 +15308,7 @@
       <c r="C612" s="11"/>
       <c r="D612" s="11"/>
       <c r="E612" s="11" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="G612" s="2"/>
       <c r="H612" s="2"/>
@@ -15320,22 +15321,22 @@
       <c r="C613" s="11"/>
       <c r="D613" s="11"/>
       <c r="E613" s="11" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="G613" s="2"/>
       <c r="H613" s="2"/>
     </row>
     <row r="614" spans="1:8">
       <c r="A614" s="11" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B614" s="11" t="s">
         <v>1772</v>
-      </c>
-      <c r="B614" s="11" t="s">
-        <v>1773</v>
       </c>
       <c r="C614" s="11"/>
       <c r="D614" s="11"/>
       <c r="E614" s="11" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="G614" s="2"/>
       <c r="H614" s="2"/>
@@ -15346,26 +15347,26 @@
       </c>
       <c r="B615" s="11"/>
       <c r="C615" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D615" s="11"/>
       <c r="E615" s="11" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="G615" s="2"/>
       <c r="H615" s="2"/>
     </row>
     <row r="616" spans="1:8">
       <c r="A616" s="11" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="B616" s="11"/>
       <c r="C616" s="11"/>
       <c r="D616" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="E616" s="11" t="s">
         <v>1320</v>
-      </c>
-      <c r="E616" s="11" t="s">
-        <v>1321</v>
       </c>
       <c r="G616" s="2"/>
       <c r="H616" s="2"/>
@@ -15380,7 +15381,7 @@
         <v>728</v>
       </c>
       <c r="E617" s="11" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="G617" s="2"/>
       <c r="H617" s="2"/>
@@ -15393,7 +15394,7 @@
       <c r="C618" s="11"/>
       <c r="D618" s="11"/>
       <c r="E618" s="11" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="G618" s="2"/>
       <c r="H618" s="2"/>
@@ -15406,24 +15407,24 @@
       <c r="C619" s="11"/>
       <c r="D619" s="11"/>
       <c r="E619" s="11" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="G619" s="2"/>
       <c r="H619" s="2"/>
     </row>
     <row r="620" spans="1:8">
       <c r="A620" s="11" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="B620" s="11"/>
       <c r="C620" s="11" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="D620" s="11" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E620" s="11" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G620" s="2"/>
       <c r="H620" s="2"/>
@@ -15436,7 +15437,7 @@
       <c r="C621" s="11"/>
       <c r="D621" s="11"/>
       <c r="E621" s="11" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G621" s="2"/>
       <c r="H621" s="2"/>
@@ -15449,7 +15450,7 @@
       <c r="C622" s="11"/>
       <c r="D622" s="11"/>
       <c r="E622" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G622" s="2"/>
       <c r="H622" s="2"/>
@@ -15462,7 +15463,7 @@
       <c r="C623" s="11"/>
       <c r="D623" s="11"/>
       <c r="E623" s="11" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="G623" s="2"/>
       <c r="H623" s="2"/>
@@ -15473,11 +15474,11 @@
       </c>
       <c r="B624" s="11"/>
       <c r="C624" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D624" s="11"/>
       <c r="E624" s="11" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G624" s="2"/>
       <c r="H624" s="2"/>
@@ -15490,7 +15491,7 @@
       <c r="C625" s="11"/>
       <c r="D625" s="11"/>
       <c r="E625" s="11" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="G625" s="2"/>
       <c r="H625" s="2"/>
@@ -15501,11 +15502,11 @@
       </c>
       <c r="B626" s="11"/>
       <c r="C626" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D626" s="11"/>
       <c r="E626" s="11" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G626" s="2"/>
       <c r="H626" s="2"/>
@@ -15516,24 +15517,24 @@
       </c>
       <c r="B627" s="11"/>
       <c r="C627" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D627" s="11"/>
       <c r="E627" s="11" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="G627" s="2"/>
       <c r="H627" s="2"/>
     </row>
     <row r="628" spans="1:8">
       <c r="A628" s="11" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="B628" s="11"/>
       <c r="C628" s="11"/>
       <c r="D628" s="11"/>
       <c r="E628" s="11" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="G628" s="2"/>
       <c r="H628" s="2"/>
@@ -15546,7 +15547,7 @@
       <c r="C629" s="11"/>
       <c r="D629" s="11"/>
       <c r="E629" s="11" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="G629" s="2"/>
       <c r="H629" s="2"/>
@@ -15559,22 +15560,22 @@
       <c r="C630" s="11"/>
       <c r="D630" s="11"/>
       <c r="E630" s="11" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="G630" s="2"/>
       <c r="H630" s="2"/>
     </row>
     <row r="631" spans="1:8">
       <c r="A631" s="11" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="B631" s="11"/>
       <c r="C631" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D631" s="11"/>
       <c r="E631" s="11" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="G631" s="2"/>
       <c r="H631" s="2"/>
@@ -15587,7 +15588,7 @@
       <c r="C632" s="11"/>
       <c r="D632" s="11"/>
       <c r="E632" s="11" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="G632" s="2"/>
       <c r="H632" s="2"/>
@@ -15598,11 +15599,11 @@
       </c>
       <c r="B633" s="11"/>
       <c r="C633" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D633" s="11"/>
       <c r="E633" s="11" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="G633" s="2"/>
       <c r="H633" s="2"/>
@@ -15613,11 +15614,11 @@
       </c>
       <c r="B634" s="11"/>
       <c r="C634" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D634" s="11"/>
       <c r="E634" s="11" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="G634" s="2"/>
       <c r="H634" s="2"/>
@@ -15630,7 +15631,7 @@
       <c r="C635" s="11"/>
       <c r="D635" s="11"/>
       <c r="E635" s="11" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="G635" s="2"/>
       <c r="H635" s="2"/>
@@ -15643,7 +15644,7 @@
       <c r="C636" s="11"/>
       <c r="D636" s="11"/>
       <c r="E636" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G636" s="2"/>
       <c r="H636" s="2"/>
@@ -15656,7 +15657,7 @@
       <c r="C637" s="11"/>
       <c r="D637" s="11"/>
       <c r="E637" s="11" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="G637" s="2"/>
       <c r="H637" s="2"/>
@@ -15667,11 +15668,11 @@
       </c>
       <c r="B638" s="11"/>
       <c r="C638" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D638" s="11"/>
       <c r="E638" s="11" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="G638" s="2"/>
       <c r="H638" s="2"/>
@@ -15682,11 +15683,11 @@
       </c>
       <c r="B639" s="11"/>
       <c r="C639" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D639" s="11"/>
       <c r="E639" s="11" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="G639" s="2"/>
       <c r="H639" s="2"/>
@@ -15697,11 +15698,11 @@
       </c>
       <c r="B640" s="11"/>
       <c r="C640" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D640" s="11"/>
       <c r="E640" s="11" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="G640" s="2"/>
       <c r="H640" s="2"/>
@@ -15714,7 +15715,7 @@
       <c r="C641" s="11"/>
       <c r="D641" s="11"/>
       <c r="E641" s="11" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="G641" s="2"/>
       <c r="H641" s="2"/>
@@ -15727,7 +15728,7 @@
       <c r="C642" s="11"/>
       <c r="D642" s="11"/>
       <c r="E642" s="11" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="G642" s="2"/>
       <c r="H642" s="2"/>
@@ -15740,7 +15741,7 @@
       <c r="C643" s="11"/>
       <c r="D643" s="11"/>
       <c r="E643" s="11" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="G643" s="2"/>
       <c r="H643" s="2"/>
@@ -15753,7 +15754,7 @@
       <c r="C644" s="11"/>
       <c r="D644" s="11"/>
       <c r="E644" s="11" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="G644" s="2"/>
       <c r="H644" s="2"/>
@@ -15766,7 +15767,7 @@
       <c r="C645" s="11"/>
       <c r="D645" s="11"/>
       <c r="E645" s="11" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="G645" s="2"/>
       <c r="H645" s="2"/>
@@ -15777,11 +15778,11 @@
       </c>
       <c r="B646" s="11"/>
       <c r="C646" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D646" s="11"/>
       <c r="E646" s="11" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="G646" s="2"/>
       <c r="H646" s="2"/>
@@ -15792,11 +15793,11 @@
       </c>
       <c r="B647" s="11"/>
       <c r="C647" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D647" s="11"/>
       <c r="E647" s="11" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="G647" s="2"/>
       <c r="H647" s="2"/>
@@ -15807,11 +15808,11 @@
       </c>
       <c r="B648" s="11"/>
       <c r="C648" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D648" s="11"/>
       <c r="E648" s="11" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="G648" s="2"/>
       <c r="H648" s="2"/>
@@ -15826,7 +15827,7 @@
         <v>730</v>
       </c>
       <c r="E649" s="11" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="G649" s="2"/>
       <c r="H649" s="2"/>
@@ -15839,7 +15840,7 @@
       <c r="C650" s="11"/>
       <c r="D650" s="11"/>
       <c r="E650" s="11" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G650" s="2"/>
       <c r="H650" s="2"/>
@@ -15852,7 +15853,7 @@
       <c r="C651" s="11"/>
       <c r="D651" s="11"/>
       <c r="E651" s="11" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="G651" s="2"/>
       <c r="H651" s="2"/>
@@ -15865,7 +15866,7 @@
       <c r="C652" s="11"/>
       <c r="D652" s="11"/>
       <c r="E652" s="11" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="G652" s="2"/>
       <c r="H652" s="2"/>
@@ -15878,7 +15879,7 @@
       <c r="C653" s="11"/>
       <c r="D653" s="11"/>
       <c r="E653" s="11" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="G653" s="2"/>
       <c r="H653" s="2"/>
@@ -15889,11 +15890,11 @@
       </c>
       <c r="B654" s="11"/>
       <c r="C654" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D654" s="11"/>
       <c r="E654" s="11" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="G654" s="2"/>
       <c r="H654" s="2"/>
@@ -15906,35 +15907,35 @@
       <c r="C655" s="11"/>
       <c r="D655" s="11"/>
       <c r="E655" s="11" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="G655" s="2"/>
       <c r="H655" s="2"/>
     </row>
     <row r="656" spans="1:8">
       <c r="A656" s="11" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B656" s="11" t="s">
         <v>1830</v>
-      </c>
-      <c r="B656" s="11" t="s">
-        <v>1831</v>
       </c>
       <c r="C656" s="11"/>
       <c r="D656" s="11"/>
       <c r="E656" s="11" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="G656" s="2"/>
       <c r="H656" s="2"/>
     </row>
     <row r="657" spans="1:8">
       <c r="A657" s="11" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="B657" s="11"/>
       <c r="C657" s="11"/>
       <c r="D657" s="11"/>
       <c r="E657" s="11" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="G657" s="2"/>
       <c r="H657" s="2"/>
@@ -15945,28 +15946,28 @@
       </c>
       <c r="B658" s="11"/>
       <c r="C658" s="11" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="D658" s="11"/>
       <c r="E658" s="11" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G658" s="2"/>
       <c r="H658" s="2"/>
     </row>
     <row r="659" spans="1:8">
       <c r="A659" s="11" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="B659" s="11" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="C659" s="11" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="D659" s="11"/>
       <c r="E659" s="11" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="G659" s="2"/>
       <c r="H659" s="2"/>
@@ -15979,33 +15980,33 @@
       <c r="C660" s="11"/>
       <c r="D660" s="11"/>
       <c r="E660" s="11" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="G660" s="2"/>
       <c r="H660" s="2"/>
     </row>
     <row r="661" spans="1:8">
       <c r="A661" s="11" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="B661" s="11"/>
       <c r="C661" s="11"/>
       <c r="D661" s="11"/>
       <c r="E661" s="11" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="G661" s="2"/>
       <c r="H661" s="2"/>
     </row>
     <row r="662" spans="1:8">
       <c r="A662" s="11" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="B662" s="11"/>
       <c r="C662" s="11"/>
       <c r="D662" s="11"/>
       <c r="E662" s="11" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="G662" s="2"/>
       <c r="H662" s="2"/>
@@ -16018,20 +16019,20 @@
       <c r="C663" s="11"/>
       <c r="D663" s="11"/>
       <c r="E663" s="11" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="G663" s="2"/>
       <c r="H663" s="2"/>
     </row>
     <row r="664" spans="1:8">
       <c r="A664" s="11" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="B664" s="11"/>
       <c r="C664" s="11"/>
       <c r="D664" s="11"/>
       <c r="E664" s="11" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="G664" s="2"/>
       <c r="H664" s="2"/>
@@ -16042,11 +16043,11 @@
       </c>
       <c r="B665" s="11"/>
       <c r="C665" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D665" s="11"/>
       <c r="E665" s="11" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="G665" s="2"/>
       <c r="H665" s="2"/>
@@ -16057,11 +16058,11 @@
       </c>
       <c r="B666" s="11"/>
       <c r="C666" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D666" s="11"/>
       <c r="E666" s="11" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="G666" s="2"/>
       <c r="H666" s="2"/>
@@ -16072,11 +16073,11 @@
       </c>
       <c r="B667" s="11"/>
       <c r="C667" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D667" s="11"/>
       <c r="E667" s="11" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="G667" s="2"/>
       <c r="H667" s="2"/>
@@ -16087,11 +16088,11 @@
       </c>
       <c r="B668" s="11"/>
       <c r="C668" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D668" s="11"/>
       <c r="E668" s="11" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="G668" s="2"/>
       <c r="H668" s="2"/>
@@ -16102,11 +16103,11 @@
       </c>
       <c r="B669" s="11"/>
       <c r="C669" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D669" s="11"/>
       <c r="E669" s="11" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="G669" s="2"/>
       <c r="H669" s="2"/>
@@ -16118,10 +16119,10 @@
       <c r="B670" s="11"/>
       <c r="C670" s="11"/>
       <c r="D670" s="11" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E670" s="11" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="G670" s="2"/>
       <c r="H670" s="2"/>
@@ -16136,7 +16137,7 @@
         <v>699</v>
       </c>
       <c r="E671" s="11" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="G671" s="2"/>
       <c r="H671" s="2"/>
@@ -16148,10 +16149,10 @@
       <c r="B672" s="11"/>
       <c r="C672" s="11"/>
       <c r="D672" s="11" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E672" s="11" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G672" s="2"/>
       <c r="H672" s="2"/>
@@ -16164,7 +16165,7 @@
       <c r="C673" s="11"/>
       <c r="D673" s="11"/>
       <c r="E673" s="11" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="G673" s="2"/>
       <c r="H673" s="2"/>
@@ -16177,26 +16178,26 @@
       <c r="C674" s="11"/>
       <c r="D674" s="11"/>
       <c r="E674" s="11" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="G674" s="2"/>
       <c r="H674" s="2"/>
     </row>
     <row r="675" spans="1:8">
       <c r="A675" s="11" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B675" s="11" t="s">
         <v>1700</v>
       </c>
-      <c r="B675" s="11" t="s">
+      <c r="C675" s="11" t="s">
         <v>1701</v>
       </c>
-      <c r="C675" s="11" t="s">
-        <v>1702</v>
-      </c>
       <c r="D675" s="11" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E675" s="11" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="G675" s="2"/>
       <c r="H675" s="2"/>
@@ -16209,7 +16210,7 @@
       <c r="C676" s="11"/>
       <c r="D676" s="11"/>
       <c r="E676" s="11" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="G676" s="2"/>
       <c r="H676" s="2"/>
@@ -16220,26 +16221,26 @@
       </c>
       <c r="B677" s="11"/>
       <c r="C677" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D677" s="11"/>
       <c r="E677" s="11" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="G677" s="2"/>
       <c r="H677" s="2"/>
     </row>
     <row r="678" spans="1:8">
       <c r="A678" s="11" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B678" s="11"/>
       <c r="C678" s="11"/>
       <c r="D678" s="11" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E678" s="11" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="G678" s="2"/>
       <c r="H678" s="2"/>
@@ -16250,11 +16251,11 @@
       </c>
       <c r="B679" s="11"/>
       <c r="C679" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D679" s="11"/>
       <c r="E679" s="11" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="G679" s="2"/>
       <c r="H679" s="2"/>
@@ -16265,11 +16266,11 @@
       </c>
       <c r="B680" s="11"/>
       <c r="C680" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D680" s="11"/>
       <c r="E680" s="11" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="G680" s="2"/>
       <c r="H680" s="2"/>
@@ -16282,7 +16283,7 @@
       <c r="C681" s="11"/>
       <c r="D681" s="11"/>
       <c r="E681" s="11" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="G681" s="2"/>
       <c r="H681" s="2"/>
@@ -16297,19 +16298,19 @@
         <v>729</v>
       </c>
       <c r="E682" s="11" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="G682" s="2"/>
       <c r="H682" s="2"/>
     </row>
     <row r="683" spans="1:8">
       <c r="A683" s="11" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B683" s="11"/>
       <c r="C683" s="11"/>
       <c r="D683" s="14" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E683" s="11"/>
       <c r="G683" s="2"/>
@@ -16323,7 +16324,7 @@
       <c r="C684" s="11"/>
       <c r="D684" s="11"/>
       <c r="E684" s="11" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="G684" s="2"/>
       <c r="H684" s="2"/>
@@ -16335,10 +16336,10 @@
       <c r="B685" s="11"/>
       <c r="C685" s="11"/>
       <c r="D685" s="11" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E685" s="11" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G685" s="2"/>
       <c r="H685" s="2"/>
@@ -16366,7 +16367,7 @@
         <v>731</v>
       </c>
       <c r="E687" s="11" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="G687" s="2"/>
       <c r="H687" s="2"/>
@@ -16379,20 +16380,20 @@
       <c r="C688" s="11"/>
       <c r="D688" s="11"/>
       <c r="E688" s="11" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="G688" s="2"/>
       <c r="H688" s="2"/>
     </row>
     <row r="689" spans="1:8">
       <c r="A689" s="11" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B689" s="11"/>
       <c r="C689" s="11"/>
       <c r="D689" s="11"/>
       <c r="E689" s="11" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G689" s="2"/>
       <c r="H689" s="2"/>
@@ -16405,7 +16406,7 @@
       <c r="C690" s="11"/>
       <c r="D690" s="11"/>
       <c r="E690" s="11" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="G690" s="2"/>
       <c r="H690" s="2"/>
@@ -16418,7 +16419,7 @@
       <c r="C691" s="11"/>
       <c r="D691" s="11"/>
       <c r="E691" s="11" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="G691" s="2"/>
       <c r="H691" s="2"/>
@@ -16431,7 +16432,7 @@
       <c r="C692" s="11"/>
       <c r="D692" s="11"/>
       <c r="E692" s="11" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="G692" s="2"/>
       <c r="H692" s="2"/>
@@ -16444,7 +16445,7 @@
       <c r="C693" s="11"/>
       <c r="D693" s="11"/>
       <c r="E693" s="11" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="G693" s="2"/>
       <c r="H693" s="2"/>
@@ -16457,7 +16458,7 @@
       <c r="C694" s="11"/>
       <c r="D694" s="11"/>
       <c r="E694" s="11" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G694" s="2"/>
       <c r="H694" s="2"/>
@@ -16470,7 +16471,7 @@
       <c r="C695" s="11"/>
       <c r="D695" s="11"/>
       <c r="E695" s="11" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="G695" s="2"/>
       <c r="H695" s="2"/>
@@ -16483,7 +16484,7 @@
       <c r="C696" s="11"/>
       <c r="D696" s="11"/>
       <c r="E696" s="11" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="G696" s="2"/>
       <c r="H696" s="2"/>
@@ -16496,7 +16497,7 @@
       <c r="C697" s="11"/>
       <c r="D697" s="11"/>
       <c r="E697" s="11" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="G697" s="2"/>
       <c r="H697" s="2"/>
@@ -16507,11 +16508,11 @@
       </c>
       <c r="B698" s="11"/>
       <c r="C698" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D698" s="11"/>
       <c r="E698" s="11" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="G698" s="2"/>
       <c r="H698" s="2"/>
@@ -16522,11 +16523,11 @@
       </c>
       <c r="B699" s="11"/>
       <c r="C699" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D699" s="11"/>
       <c r="E699" s="11" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="G699" s="2"/>
       <c r="H699" s="2"/>
@@ -16539,7 +16540,7 @@
       <c r="C700" s="11"/>
       <c r="D700" s="11"/>
       <c r="E700" s="11" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="G700" s="2"/>
       <c r="H700" s="2"/>
@@ -16550,11 +16551,11 @@
       </c>
       <c r="B701" s="11"/>
       <c r="C701" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D701" s="11"/>
       <c r="E701" s="11" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="G701" s="2"/>
       <c r="H701" s="2"/>
@@ -16567,14 +16568,14 @@
       <c r="C702" s="11"/>
       <c r="D702" s="11"/>
       <c r="E702" s="11" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="G702" s="2"/>
       <c r="H702" s="2"/>
     </row>
     <row r="703" spans="1:8">
       <c r="A703" s="11" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="B703" s="11"/>
       <c r="C703" s="11"/>
@@ -16582,7 +16583,7 @@
         <v>732</v>
       </c>
       <c r="E703" s="11" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="G703" s="2"/>
       <c r="H703" s="2"/>
@@ -16594,10 +16595,10 @@
       <c r="B704" s="11"/>
       <c r="C704" s="11"/>
       <c r="D704" s="11" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E704" s="11" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G704" s="2"/>
       <c r="H704" s="2"/>
@@ -16608,11 +16609,11 @@
       </c>
       <c r="B705" s="11"/>
       <c r="C705" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D705" s="11"/>
       <c r="E705" s="11" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="G705" s="2"/>
       <c r="H705" s="2"/>
@@ -16623,24 +16624,24 @@
       </c>
       <c r="B706" s="11"/>
       <c r="C706" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D706" s="11"/>
       <c r="E706" s="11" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="G706" s="2"/>
       <c r="H706" s="2"/>
     </row>
     <row r="707" spans="1:8">
       <c r="A707" s="11" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="B707" s="11"/>
       <c r="C707" s="11"/>
       <c r="D707" s="11"/>
       <c r="E707" s="11" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="G707" s="2"/>
       <c r="H707" s="2"/>
@@ -16653,7 +16654,7 @@
       <c r="C708" s="11"/>
       <c r="D708" s="11"/>
       <c r="E708" s="11" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="G708" s="2"/>
       <c r="H708" s="2"/>
@@ -16666,7 +16667,7 @@
       <c r="C709" s="11"/>
       <c r="D709" s="11"/>
       <c r="E709" s="11" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G709" s="2"/>
       <c r="H709" s="2"/>
@@ -16677,26 +16678,26 @@
       </c>
       <c r="B710" s="11"/>
       <c r="C710" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D710" s="11"/>
       <c r="E710" s="11" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="G710" s="2"/>
       <c r="H710" s="2"/>
     </row>
     <row r="711" spans="1:8">
       <c r="A711" s="11" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="B711" s="11"/>
       <c r="C711" s="11"/>
       <c r="D711" s="11" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E711" s="11" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="G711" s="2"/>
       <c r="H711" s="2"/>
@@ -16709,7 +16710,7 @@
       <c r="C712" s="11"/>
       <c r="D712" s="11"/>
       <c r="E712" s="11" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="G712" s="2"/>
       <c r="H712" s="2"/>
@@ -16720,7 +16721,7 @@
       </c>
       <c r="B713" s="11"/>
       <c r="C713" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D713" s="11"/>
       <c r="E713" s="11" t="s">
@@ -16731,11 +16732,11 @@
     </row>
     <row r="714" spans="1:8">
       <c r="A714" s="11" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="B714" s="11"/>
       <c r="C714" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D714" s="11"/>
       <c r="E714" s="11"/>
@@ -16750,7 +16751,7 @@
       <c r="C715" s="11"/>
       <c r="D715" s="11"/>
       <c r="E715" s="11" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="G715" s="2"/>
       <c r="H715" s="2"/>
@@ -16763,7 +16764,7 @@
       <c r="C716" s="11"/>
       <c r="D716" s="11"/>
       <c r="E716" s="11" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="G716" s="2"/>
       <c r="H716" s="2"/>
@@ -16776,22 +16777,22 @@
       <c r="C717" s="11"/>
       <c r="D717" s="11"/>
       <c r="E717" s="11" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="G717" s="2"/>
       <c r="H717" s="2"/>
     </row>
     <row r="718" spans="1:8">
       <c r="A718" s="11" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="B718" s="11"/>
       <c r="C718" s="11" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="D718" s="11"/>
       <c r="E718" s="11" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G718" s="2"/>
       <c r="H718" s="2"/>
@@ -16815,11 +16816,11 @@
       </c>
       <c r="B720" s="11"/>
       <c r="C720" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D720" s="11"/>
       <c r="E720" s="11" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="G720" s="2"/>
       <c r="H720" s="2"/>
@@ -16830,41 +16831,41 @@
       </c>
       <c r="B721" s="11"/>
       <c r="C721" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D721" s="11" t="s">
         <v>733</v>
       </c>
       <c r="E721" s="11" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="G721" s="2"/>
       <c r="H721" s="2"/>
     </row>
     <row r="722" spans="1:8">
       <c r="A722" s="11" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="B722" s="11"/>
       <c r="C722" s="11"/>
       <c r="D722" s="11"/>
       <c r="E722" s="11" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="G722" s="2"/>
       <c r="H722" s="2"/>
     </row>
     <row r="723" spans="1:8">
       <c r="A723" s="11" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="B723" s="11"/>
       <c r="C723" s="11" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="D723" s="11"/>
       <c r="E723" s="11" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G723" s="2"/>
       <c r="H723" s="2"/>
@@ -16877,7 +16878,7 @@
       <c r="C724" s="11"/>
       <c r="D724" s="11"/>
       <c r="E724" s="11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="G724" s="2"/>
       <c r="H724" s="2"/>
@@ -16888,7 +16889,7 @@
       </c>
       <c r="B725" s="11"/>
       <c r="C725" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D725" s="11"/>
       <c r="E725" s="11" t="s">
@@ -16903,7 +16904,7 @@
       </c>
       <c r="B726" s="11"/>
       <c r="C726" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D726" s="11"/>
       <c r="E726" s="11" t="s">
@@ -16914,19 +16915,19 @@
     </row>
     <row r="727" spans="1:8">
       <c r="A727" s="11" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B727" s="11" t="s">
         <v>1693</v>
-      </c>
-      <c r="B727" s="11" t="s">
-        <v>1694</v>
       </c>
       <c r="C727" s="11" t="s">
         <v>757</v>
       </c>
       <c r="D727" s="14" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="E727" s="11" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="G727" s="2"/>
       <c r="H727" s="2"/>
@@ -16937,7 +16938,7 @@
       </c>
       <c r="B728" s="11"/>
       <c r="C728" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D728" s="11"/>
       <c r="E728" s="11"/>
@@ -16950,11 +16951,11 @@
       </c>
       <c r="B729" s="11"/>
       <c r="C729" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D729" s="11"/>
       <c r="E729" s="11" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="G729" s="2"/>
       <c r="H729" s="2"/>
@@ -16965,11 +16966,11 @@
       </c>
       <c r="B730" s="11"/>
       <c r="C730" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D730" s="11"/>
       <c r="E730" s="11" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="G730" s="2"/>
       <c r="H730" s="2"/>
@@ -16980,11 +16981,11 @@
       </c>
       <c r="B731" s="11"/>
       <c r="C731" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D731" s="11"/>
       <c r="E731" s="11" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="G731" s="2"/>
       <c r="H731" s="2"/>
@@ -16995,7 +16996,7 @@
       </c>
       <c r="B732" s="11"/>
       <c r="C732" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D732" s="11"/>
       <c r="E732" s="11" t="s">
@@ -17010,26 +17011,26 @@
       </c>
       <c r="B733" s="11"/>
       <c r="C733" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D733" s="11"/>
       <c r="E733" s="11" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="G733" s="2"/>
       <c r="H733" s="2"/>
     </row>
     <row r="734" spans="1:8">
       <c r="A734" s="11" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="B734" s="11"/>
       <c r="C734" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D734" s="11"/>
       <c r="E734" s="11" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="G734" s="2"/>
       <c r="H734" s="2"/>
@@ -17053,39 +17054,39 @@
       </c>
       <c r="B736" s="11"/>
       <c r="C736" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D736" s="11" t="s">
         <v>747</v>
       </c>
       <c r="E736" s="11" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="G736" s="2"/>
       <c r="H736" s="2"/>
     </row>
     <row r="737" spans="1:8">
       <c r="A737" s="11" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="B737" s="11"/>
       <c r="C737" s="11"/>
       <c r="D737" s="11"/>
       <c r="E737" s="11" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="G737" s="2"/>
       <c r="H737" s="2"/>
     </row>
     <row r="738" spans="1:8">
       <c r="A738" s="11" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B738" s="11"/>
       <c r="C738" s="11"/>
       <c r="D738" s="11"/>
       <c r="E738" s="11" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="G738" s="2"/>
       <c r="H738" s="2"/>
@@ -17098,7 +17099,7 @@
       <c r="C739" s="11"/>
       <c r="D739" s="11"/>
       <c r="E739" s="11" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="G739" s="2"/>
       <c r="H739" s="2"/>
@@ -17111,7 +17112,7 @@
       <c r="C740" s="11"/>
       <c r="D740" s="11"/>
       <c r="E740" s="11" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="G740" s="2"/>
       <c r="H740" s="2"/>
@@ -17124,7 +17125,7 @@
       <c r="C741" s="11"/>
       <c r="D741" s="11"/>
       <c r="E741" s="11" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="G741" s="2"/>
       <c r="H741" s="2"/>
@@ -17137,7 +17138,7 @@
       <c r="C742" s="11"/>
       <c r="D742" s="11"/>
       <c r="E742" s="11" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="G742" s="2"/>
       <c r="H742" s="2"/>
@@ -17148,11 +17149,11 @@
       </c>
       <c r="B743" s="11"/>
       <c r="C743" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D743" s="11"/>
       <c r="E743" s="11" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="G743" s="2"/>
       <c r="H743" s="2"/>
@@ -17165,20 +17166,20 @@
       <c r="C744" s="11"/>
       <c r="D744" s="11"/>
       <c r="E744" s="11" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="G744" s="2"/>
       <c r="H744" s="2"/>
     </row>
     <row r="745" spans="1:8">
       <c r="A745" s="11" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="B745" s="11"/>
       <c r="C745" s="11"/>
       <c r="D745" s="11"/>
       <c r="E745" s="11" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="G745" s="2"/>
       <c r="H745" s="2"/>
@@ -17189,7 +17190,7 @@
       </c>
       <c r="B746" s="11"/>
       <c r="C746" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D746" s="11"/>
       <c r="E746" s="11"/>
@@ -17202,11 +17203,11 @@
       </c>
       <c r="B747" s="11"/>
       <c r="C747" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D747" s="11"/>
       <c r="E747" s="11" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="G747" s="2"/>
       <c r="H747" s="2"/>
@@ -17219,7 +17220,7 @@
       <c r="C748" s="11"/>
       <c r="D748" s="11"/>
       <c r="E748" s="11" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="G748" s="2"/>
       <c r="H748" s="2"/>
@@ -17232,7 +17233,7 @@
       <c r="C749" s="11"/>
       <c r="D749" s="11"/>
       <c r="E749" s="11" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="G749" s="2"/>
       <c r="H749" s="2"/>
@@ -17245,7 +17246,7 @@
       <c r="C750" s="11"/>
       <c r="D750" s="11"/>
       <c r="E750" s="11" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="G750" s="2"/>
       <c r="H750" s="2"/>
@@ -17256,7 +17257,7 @@
       </c>
       <c r="B751" s="11"/>
       <c r="C751" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D751" s="11"/>
       <c r="E751" s="11" t="s">
@@ -17273,7 +17274,7 @@
       <c r="C752" s="11"/>
       <c r="D752" s="11"/>
       <c r="E752" s="11" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="G752" s="2"/>
       <c r="H752" s="2"/>
@@ -17286,7 +17287,7 @@
       <c r="C753" s="11"/>
       <c r="D753" s="11"/>
       <c r="E753" s="11" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="G753" s="2"/>
       <c r="H753" s="2"/>
@@ -17299,7 +17300,7 @@
       <c r="C754" s="11"/>
       <c r="D754" s="11"/>
       <c r="E754" s="11" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="G754" s="2"/>
       <c r="H754" s="2"/>
@@ -17312,20 +17313,20 @@
       <c r="C755" s="11"/>
       <c r="D755" s="11"/>
       <c r="E755" s="11" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="G755" s="2"/>
       <c r="H755" s="2"/>
     </row>
     <row r="756" spans="1:8">
       <c r="A756" s="11" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="B756" s="11"/>
       <c r="C756" s="11"/>
       <c r="D756" s="11"/>
       <c r="E756" s="11" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="G756" s="2"/>
       <c r="H756" s="2"/>
@@ -17338,7 +17339,7 @@
       <c r="C757" s="11"/>
       <c r="D757" s="11"/>
       <c r="E757" s="11" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="G757" s="2"/>
       <c r="H757" s="2"/>
@@ -17362,45 +17363,45 @@
       </c>
       <c r="B759" s="11"/>
       <c r="C759" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D759" s="11"/>
       <c r="E759" s="11" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="G759" s="2"/>
       <c r="H759" s="2"/>
     </row>
     <row r="760" spans="1:8">
       <c r="A760" s="11" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B760" s="11" t="s">
         <v>1687</v>
       </c>
-      <c r="B760" s="11" t="s">
+      <c r="C760" s="11" t="s">
         <v>1688</v>
       </c>
-      <c r="C760" s="11" t="s">
+      <c r="D760" s="14" t="s">
         <v>1689</v>
       </c>
-      <c r="D760" s="14" t="s">
+      <c r="E760" s="11" t="s">
         <v>1690</v>
-      </c>
-      <c r="E760" s="11" t="s">
-        <v>1691</v>
       </c>
       <c r="G760" s="2"/>
       <c r="H760" s="2"/>
     </row>
     <row r="761" spans="1:8">
       <c r="A761" s="11" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B761" s="11" t="s">
         <v>1685</v>
-      </c>
-      <c r="B761" s="11" t="s">
-        <v>1686</v>
       </c>
       <c r="C761" s="11"/>
       <c r="D761" s="11"/>
       <c r="E761" s="11" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="G761" s="2"/>
       <c r="H761" s="2"/>
@@ -17413,24 +17414,24 @@
       <c r="C762" s="11"/>
       <c r="D762" s="11"/>
       <c r="E762" s="11" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="G762" s="2"/>
       <c r="H762" s="2"/>
     </row>
     <row r="763" spans="1:8" ht="45">
       <c r="A763" s="2" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="B763" s="2"/>
       <c r="C763" s="8" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D763" s="6" t="s">
+        <v>1834</v>
+      </c>
+      <c r="E763" s="16" t="s">
         <v>1833</v>
-      </c>
-      <c r="D763" s="6" t="s">
-        <v>1835</v>
-      </c>
-      <c r="E763" s="16" t="s">
-        <v>1834</v>
       </c>
       <c r="G763" s="2"/>
       <c r="H763" s="2"/>
@@ -21663,7 +21664,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="11" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -21684,7 +21685,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="11" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -21705,7 +21706,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="11" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -21740,7 +21741,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="11" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -21775,7 +21776,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="11" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -21789,7 +21790,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="11" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -21817,7 +21818,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="11" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
@@ -21866,7 +21867,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -21906,7 +21907,7 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="11" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
@@ -21914,7 +21915,7 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="11" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
@@ -21922,7 +21923,7 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="11" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
@@ -21962,7 +21963,7 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="11" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
@@ -22002,7 +22003,7 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="11" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B56" s="11"/>
       <c r="C56" s="11"/>
@@ -22010,7 +22011,7 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="11" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B57" s="11"/>
       <c r="C57" s="11"/>
@@ -22018,7 +22019,7 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="11" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B58" s="11"/>
       <c r="C58" s="11"/>
@@ -22026,7 +22027,7 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="11" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
@@ -22034,7 +22035,7 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="11" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
@@ -22058,7 +22059,7 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="11" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
@@ -22066,7 +22067,7 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="11" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
@@ -22120,7 +22121,7 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="11" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
@@ -22148,28 +22149,28 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="11" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B75" s="11"/>
       <c r="C75" s="11"/>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="11" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B76" s="11"/>
       <c r="C76" s="11"/>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="11" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B77" s="11"/>
       <c r="C77" s="11"/>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="11" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B78" s="11"/>
       <c r="C78" s="11"/>
@@ -22190,21 +22191,21 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="11" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B81" s="11"/>
       <c r="C81" s="11"/>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="11" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B82" s="11"/>
       <c r="C82" s="11"/>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="11" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
@@ -22218,7 +22219,7 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B85" s="11"/>
       <c r="C85" s="11"/>
@@ -22232,7 +22233,7 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="11" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B87" s="11"/>
       <c r="C87" s="11"/>
@@ -22281,7 +22282,7 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="11" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B94" s="11"/>
       <c r="C94" s="11"/>
@@ -22295,7 +22296,7 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="11" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
@@ -22309,7 +22310,7 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="11" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
@@ -22393,7 +22394,7 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="11" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B110" s="11"/>
       <c r="C110" s="11"/>
@@ -22421,14 +22422,14 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="11" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B114" s="11"/>
       <c r="C114" s="11"/>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="11" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B115" s="11"/>
       <c r="C115" s="11"/>
@@ -22477,7 +22478,7 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="11" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B122" s="11"/>
       <c r="C122" s="11"/>
@@ -22533,7 +22534,7 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="11" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B130" s="11"/>
       <c r="C130" s="11"/>
@@ -22575,14 +22576,14 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="11" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B136" s="11"/>
       <c r="C136" s="11"/>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="11" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B137" s="11"/>
       <c r="C137" s="11"/>
@@ -22594,7 +22595,7 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="11" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -22614,12 +22615,12 @@
     </row>
     <row r="143" spans="1:3">
       <c r="A143" s="11" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" s="11" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="145" spans="1:1">
@@ -22639,7 +22640,7 @@
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="11" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="149" spans="1:1">
@@ -22654,7 +22655,7 @@
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="11" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="152" spans="1:1">
@@ -22669,7 +22670,7 @@
     </row>
     <row r="154" spans="1:1">
       <c r="A154" s="11" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="155" spans="1:1">
@@ -22764,7 +22765,7 @@
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="11" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="174" spans="1:1">
@@ -23064,7 +23065,7 @@
     </row>
     <row r="233" spans="1:1">
       <c r="A233" s="11" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="234" spans="1:1">
@@ -23149,7 +23150,7 @@
     </row>
     <row r="250" spans="1:1">
       <c r="A250" s="11" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="251" spans="1:1">
@@ -23224,17 +23225,17 @@
     </row>
     <row r="265" spans="1:1">
       <c r="A265" s="11" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="11" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" s="11" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="268" spans="1:1">
@@ -23279,12 +23280,12 @@
     </row>
     <row r="276" spans="1:1">
       <c r="A276" s="11" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" s="11" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="278" spans="1:1">
@@ -23334,7 +23335,7 @@
     </row>
     <row r="287" spans="1:1">
       <c r="A287" s="11" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="288" spans="1:1">
@@ -23344,7 +23345,7 @@
     </row>
     <row r="289" spans="1:1">
       <c r="A289" s="11" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="290" spans="1:1">
@@ -23364,7 +23365,7 @@
     </row>
     <row r="293" spans="1:1">
       <c r="A293" s="11" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="294" spans="1:1">
@@ -23379,7 +23380,7 @@
     </row>
     <row r="296" spans="1:1">
       <c r="A296" s="11" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="297" spans="1:1">
@@ -23389,12 +23390,12 @@
     </row>
     <row r="298" spans="1:1">
       <c r="A298" s="11" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="299" spans="1:1">
       <c r="A299" s="11" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="300" spans="1:1">
@@ -23499,17 +23500,17 @@
     </row>
     <row r="320" spans="1:1">
       <c r="A320" s="11" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="321" spans="1:1">
       <c r="A321" s="11" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="322" spans="1:1">
       <c r="A322" s="11" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="323" spans="1:1">
@@ -23584,7 +23585,7 @@
     </row>
     <row r="337" spans="1:1">
       <c r="A337" s="11" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="338" spans="1:1">
@@ -23639,12 +23640,12 @@
     </row>
     <row r="348" spans="1:1">
       <c r="A348" s="11" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="349" spans="1:1">
       <c r="A349" s="11" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="350" spans="1:1">
@@ -23689,7 +23690,7 @@
     </row>
     <row r="358" spans="1:1">
       <c r="A358" s="11" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="359" spans="1:1">
@@ -23739,17 +23740,17 @@
     </row>
     <row r="368" spans="1:1">
       <c r="A368" s="11" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="369" spans="1:1">
       <c r="A369" s="11" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="370" spans="1:1">
       <c r="A370" s="11" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="371" spans="1:1">
@@ -23764,7 +23765,7 @@
     </row>
     <row r="373" spans="1:1">
       <c r="A373" s="11" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="374" spans="1:1">
@@ -23919,7 +23920,7 @@
     </row>
     <row r="404" spans="1:1">
       <c r="A404" s="11" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="405" spans="1:1">
@@ -23949,7 +23950,7 @@
     </row>
     <row r="410" spans="1:1">
       <c r="A410" s="11" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="411" spans="1:1">
@@ -23959,7 +23960,7 @@
     </row>
     <row r="412" spans="1:1">
       <c r="A412" s="11" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="413" spans="1:1">
@@ -23974,7 +23975,7 @@
     </row>
     <row r="415" spans="1:1">
       <c r="A415" s="11" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="416" spans="1:1">
@@ -24014,7 +24015,7 @@
     </row>
     <row r="423" spans="1:1">
       <c r="A423" s="11" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="424" spans="1:1">
@@ -24104,7 +24105,7 @@
     </row>
     <row r="441" spans="1:1">
       <c r="A441" s="11" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="442" spans="1:1">
@@ -24129,7 +24130,7 @@
     </row>
     <row r="446" spans="1:1">
       <c r="A446" s="11" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="447" spans="1:1">
@@ -24169,7 +24170,7 @@
     </row>
     <row r="454" spans="1:1">
       <c r="A454" s="11" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="455" spans="1:1">
@@ -24234,7 +24235,7 @@
     </row>
     <row r="467" spans="1:1">
       <c r="A467" s="11" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="468" spans="1:1">
@@ -24249,7 +24250,7 @@
     </row>
     <row r="470" spans="1:1">
       <c r="A470" s="11" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="471" spans="1:1">
@@ -24319,7 +24320,7 @@
     </row>
     <row r="484" spans="1:1">
       <c r="A484" s="11" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="485" spans="1:1">
@@ -24354,7 +24355,7 @@
     </row>
     <row r="491" spans="1:1">
       <c r="A491" s="11" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="492" spans="1:1">
@@ -24409,7 +24410,7 @@
     </row>
     <row r="502" spans="1:1">
       <c r="A502" s="11" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="503" spans="1:1">
@@ -24424,7 +24425,7 @@
     </row>
     <row r="505" spans="1:1">
       <c r="A505" s="11" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="506" spans="1:1">
@@ -24444,7 +24445,7 @@
     </row>
     <row r="509" spans="1:1">
       <c r="A509" s="11" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="510" spans="1:1">
@@ -24479,22 +24480,22 @@
     </row>
     <row r="516" spans="1:1">
       <c r="A516" s="11" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="517" spans="1:1">
       <c r="A517" s="11" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="518" spans="1:1">
       <c r="A518" s="11" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="519" spans="1:1">
       <c r="A519" s="11" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="520" spans="1:1">
@@ -24609,7 +24610,7 @@
     </row>
     <row r="542" spans="1:1">
       <c r="A542" s="11" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="543" spans="1:1">
@@ -24639,7 +24640,7 @@
     </row>
     <row r="548" spans="1:1">
       <c r="A548" s="11" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="549" spans="1:1">
@@ -24654,7 +24655,7 @@
     </row>
     <row r="551" spans="1:1">
       <c r="A551" s="11" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="552" spans="1:1">
@@ -24679,7 +24680,7 @@
     </row>
     <row r="556" spans="1:1">
       <c r="A556" s="11" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="557" spans="1:1">
@@ -24694,7 +24695,7 @@
     </row>
     <row r="559" spans="1:1">
       <c r="A559" s="11" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="560" spans="1:1">
@@ -24714,7 +24715,7 @@
     </row>
     <row r="563" spans="1:1">
       <c r="A563" s="11" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="564" spans="1:1">
@@ -24769,7 +24770,7 @@
     </row>
     <row r="574" spans="1:1">
       <c r="A574" s="11" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="575" spans="1:1">
@@ -24949,7 +24950,7 @@
     </row>
     <row r="610" spans="1:1">
       <c r="A610" s="11" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="611" spans="1:1">
@@ -24979,7 +24980,7 @@
     </row>
     <row r="616" spans="1:1">
       <c r="A616" s="11" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="617" spans="1:1">
@@ -25004,7 +25005,7 @@
     </row>
     <row r="621" spans="1:1">
       <c r="A621" s="11" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="622" spans="1:1">
@@ -25039,7 +25040,7 @@
     </row>
     <row r="628" spans="1:1">
       <c r="A628" s="11" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="629" spans="1:1">
@@ -25119,7 +25120,7 @@
     </row>
     <row r="644" spans="1:1">
       <c r="A644" s="11" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="645" spans="1:1">
@@ -25244,7 +25245,7 @@
     </row>
     <row r="669" spans="1:1">
       <c r="A669" s="11" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="670" spans="1:1">
@@ -25359,7 +25360,7 @@
     </row>
     <row r="692" spans="1:1">
       <c r="A692" s="11" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="693" spans="1:1">
@@ -25379,7 +25380,7 @@
     </row>
     <row r="696" spans="1:1">
       <c r="A696" s="11" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="697" spans="1:1">
@@ -25409,7 +25410,7 @@
     </row>
     <row r="702" spans="1:1">
       <c r="A702" s="11" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="703" spans="1:1">
@@ -25479,7 +25480,7 @@
     </row>
     <row r="716" spans="1:1">
       <c r="A716" s="11" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="717" spans="1:1">
@@ -25499,7 +25500,7 @@
     </row>
     <row r="720" spans="1:1">
       <c r="A720" s="11" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="721" spans="1:1">
@@ -25559,7 +25560,7 @@
     </row>
     <row r="732" spans="1:1">
       <c r="A732" s="11" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="733" spans="1:1">
@@ -25604,7 +25605,7 @@
     </row>
     <row r="741" spans="1:1">
       <c r="A741" s="11" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="742" spans="1:1">
@@ -25664,7 +25665,7 @@
     </row>
     <row r="753" spans="1:1">
       <c r="A753" s="11" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="754" spans="1:1">
@@ -25749,7 +25750,7 @@
     </row>
     <row r="770" spans="1:1">
       <c r="A770" s="11" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="771" spans="1:1">
@@ -25769,17 +25770,17 @@
     </row>
     <row r="774" spans="1:1">
       <c r="A774" s="11" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="775" spans="1:1">
       <c r="A775" s="11" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="776" spans="1:1">
       <c r="A776" s="11" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="777" spans="1:1">
